--- a/workspaces/nasdaq_hourly_24hrs/roc/roc_12.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/roc/roc_12.xlsx
@@ -618,1969 +618,1969 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.03373</t>
+          <t>X ≈ -0.03369</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>28</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1020919092108983</v>
+        <v>-0.06905299825097444</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.4358132703338171</v>
+        <v>-0.4023690749936719</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12.32898880999582</v>
+        <v>12.36421136520652</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.576966390234539</v>
+        <v>-2.541010838701382</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.26389615529709</v>
+        <v>11.32926476319861</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.901479808500852</v>
+        <v>7.966644755682282</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.68838949786325</v>
+        <v>10.75450079770193</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.41428265743446</v>
+        <v>10.48075057839222</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>14.01407333895355</v>
+        <v>14.08054874144024</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.691161329104041</v>
+        <v>9.758546286577655</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.52494082836459</v>
+        <v>13.59206238997285</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.80928432183794</v>
+        <v>16.87677958497677</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>19.253106621055</v>
+        <v>19.32195114956088</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.47742037846412</v>
+        <v>15.54654276166028</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>18.38703160226473</v>
+        <v>18.45696409830662</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>11.86040782437085</v>
+        <v>11.92966509670474</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>11.73041947493839</v>
+        <v>11.79986903665164</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>8.064222633859387</v>
+        <v>8.133823723908563</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>8.282467158951157</v>
+        <v>8.351855721689184</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>8.471694811290874</v>
+        <v>8.540904519344195</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>11.4998302730883</v>
+        <v>11.56971498171492</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>11.42745168768641</v>
+        <v>11.49746261801759</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>15.27597319774873</v>
+        <v>15.3457025611178</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>18.77610693400167</v>
+        <v>18.84596128170895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.03129</t>
+          <t>X ≈ -0.03125</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>25</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.795182562321955</v>
+        <v>-5.893325778607625</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.970155884164292</v>
+        <v>-6.24647159866015</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-15.35252516995129</v>
+        <v>-13.53914014614687</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-12.09026079788854</v>
+        <v>-10.30616721327193</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.5261269303864182</v>
+        <v>-2.69942783191108</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.317997821355505</v>
+        <v>-4.252917928098569</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.10860897943391</v>
+        <v>-1.042574927052748</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.34745272622618</v>
+        <v>-9.281104526513971</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-9.309059554767614</v>
+        <v>-9.242715467061956</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-10.08240313814628</v>
+        <v>-10.01512323342756</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.140547536570324</v>
+        <v>2.207612309459357</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.848322742822617</v>
+        <v>5.91576789494075</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>20.67587560159944</v>
+        <v>20.74472466294271</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.48576075133132</v>
+        <v>12.55487052464595</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>11.83274408163073</v>
+        <v>11.90265364943819</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>8.439695431125351</v>
+        <v>8.508940992339404</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>16.29172860336632</v>
+        <v>16.36118851523482</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>8.206581883068537</v>
+        <v>8.276181791531798</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>20.40667228827167</v>
+        <v>20.47608201716151</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>16.60448351189825</v>
+        <v>16.67370427706483</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>16.06691924424837</v>
+        <v>16.1368083886557</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>11.99842041611523</v>
+        <v>12.06843134515301</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>12.27681096327418</v>
+        <v>12.34653905235662</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>12.2046783625731</v>
+        <v>12.27453271028038</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.02884</t>
+          <t>X ≈ -0.02881</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>40</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-11.09880419692156</v>
+        <v>-11.06913775519786</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.499671132829981</v>
+        <v>-1.467077850823785</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.930954709608528</v>
+        <v>-2.896781813514693</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.782585020693737</v>
+        <v>8.821262066527296</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.936086141864422</v>
+        <v>6.003395952731339</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.124553763551432</v>
+        <v>6.189696122391631</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.3576291285789</v>
+        <v>5.423697395118133</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.082319240318242</v>
+        <v>5.14874574797436</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.636574657677428</v>
+        <v>2.702978137382544</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.600886225396323</v>
+        <v>-5.533590564113339</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.819745934721517</v>
+        <v>-7.752735049969495</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.100556916723427</v>
+        <v>-8.033178950410345</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.241093101434622</v>
+        <v>-4.172348898930451</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-9.447450654788099</v>
+        <v>-9.378426186176377</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-2.627824855798266</v>
+        <v>-2.557966804637346</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-7.022621396421023</v>
+        <v>-6.95342503972492</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-4.663783450280107</v>
+        <v>-4.594380360902882</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-7.265125166530453</v>
+        <v>-7.195562256642603</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.54781354825618</v>
+        <v>-9.478461161319153</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-9.363926817861731</v>
+        <v>-9.294746115287509</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-4.913987872567127</v>
+        <v>-4.844123154087136</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.005661004861757135</v>
+        <v>0.07566233258212662</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.2804304372475244</v>
+        <v>0.3501537296182988</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-2.295321637426909</v>
+        <v>-2.225467289719631</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.0264</t>
+          <t>X ≈ -0.02636</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>50</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.311008900900838</v>
+        <v>1.276087134646666</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.982310560772881</v>
+        <v>-3.951311035454523</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.427186030485842</v>
+        <v>-3.393204949150309</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.150535683705392</v>
+        <v>-2.115268746081497</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.514684248116708</v>
+        <v>-2.450015947051163</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.328809501230637</v>
+        <v>-2.263734404327245</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.8806372834906355</v>
+        <v>0.9466678834958557</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.6040244800077232</v>
+        <v>0.6704153508648432</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.335750545813205</v>
+        <v>-3.269389977213628</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.115485141568634</v>
+        <v>-2.048180564336839</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.818889664478917</v>
+        <v>-7.7518886858984</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.122192442241804</v>
+        <v>-2.054795742741781</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.230444773659492</v>
+        <v>-7.161721009274459</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.459147747625146</v>
+        <v>-5.390115813370912</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.112202623724322</v>
+        <v>-8.042369877921622</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-5.525904117809844</v>
+        <v>-5.456709181341445</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-9.652592064613032</v>
+        <v>-9.583207602212198</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-7.763821680808888</v>
+        <v>-7.694264586698658</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.433842409965081</v>
+        <v>2.503214097381381</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.6238846153842204</v>
+        <v>0.6930776785304289</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.916682737126784</v>
+        <v>-1.846816673596329</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.005655839838389909</v>
+        <v>0.07565592637964613</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2.279799522699093</v>
+        <v>2.349522985772261</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.2046783625735529</v>
+        <v>0.2745327102808304</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.02395</t>
+          <t>X ≈ -0.02392</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>53</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8372528872663807</v>
+        <v>-0.9473677139666208</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7027609378535047</v>
+        <v>-1.288076319856614</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.146741575967582</v>
+        <v>-0.8935334112144346</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.936621243508093</v>
+        <v>6.928061744987303</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.677030620339764</v>
+        <v>-3.612771701024329</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.136579284772985</v>
+        <v>2.201673199963039</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.36838164519304</v>
+        <v>1.434404045844133</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.091986554307397</v>
+        <v>1.158369503762692</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.7438536075249331</v>
+        <v>-0.6774892789121196</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.242760114543643</v>
+        <v>2.310078401275398</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.878355061516672</v>
+        <v>-6.811361070279766</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.520480958681141</v>
+        <v>-1.453090591040748</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-6.40238675923036</v>
+        <v>-6.333669309926002</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.624723921830373</v>
+        <v>-6.555705383849244</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-7.283667221405793</v>
+        <v>-7.213839992941551</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.928310176965255</v>
+        <v>-2.859113867902252</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-3.062820223476976</v>
+        <v>-2.993424044299545</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.285153335234682</v>
+        <v>-1.215586212513763</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.070152083116056</v>
+        <v>-1.000790849942625</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.000726957689494</v>
+        <v>1.069917756447722</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>2.343451635186824</v>
+        <v>2.413320491993673</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.268360761764754</v>
+        <v>2.338361192632497</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.54383957888242</v>
+        <v>2.613562469623531</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.355621758799082</v>
+        <v>4.425476106506359</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.02151</t>
+          <t>X ≈ -0.02148</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>68</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.434213026439579</v>
+        <v>-4.406880013604372</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-14.99516481544265</v>
+        <v>-14.98098150873174</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-12.71561956123826</v>
+        <v>-13.50638374021335</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-13.43031910127425</v>
+        <v>-14.22366675346061</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-12.33525418195573</v>
+        <v>-13.10127291991757</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.843057229738207</v>
+        <v>-5.599720037243785</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2366819176140709</v>
+        <v>0.3026822161168141</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.428922770233648</v>
+        <v>-4.362590402221919</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.38854685877471</v>
+        <v>-4.322219053210851</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-8.087956236002157</v>
+        <v>-8.020710310858604</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.423470135235519</v>
+        <v>-3.356471712160491</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.168640038742168</v>
+        <v>-5.101279339837475</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.825613610349656</v>
+        <v>-4.756901013110692</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.581656778092132</v>
+        <v>-3.512636626086042</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.239613823510126</v>
+        <v>-4.169785445001473</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-12.44821730774272</v>
+        <v>-12.37906115307301</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-6.716839940772452</v>
+        <v>-6.64746167268909</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.888191022370577</v>
+        <v>-3.818636298255683</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-5.142279904156617</v>
+        <v>-5.072932000788555</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-2.019825382785044</v>
+        <v>-1.950643192938237</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.093914698981656</v>
+        <v>-1.024052727414571</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>3.238808425093545</v>
+        <v>3.308807980461893</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.984740562407431</v>
+        <v>5.05446365276579</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.910560715514272</v>
+        <v>4.98041506322155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01906</t>
+          <t>X ≈ -0.01903</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.337479163921856</v>
+        <v>-6.376580128237833</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-9.459477340864382</v>
+        <v>-8.469664372585157</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.614257130540175</v>
+        <v>-4.710216725639107</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.569701282195219</v>
+        <v>-3.691972773789658</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-8.501983222971447</v>
+        <v>-7.532759792030532</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.753867575935303</v>
+        <v>-3.842733451289995</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-10.87828606994454</v>
+        <v>-9.870240562670098</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-11.17393238952783</v>
+        <v>-10.16491621181515</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-12.91573051135615</v>
+        <v>-11.87518385580895</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-11.94341171774229</v>
+        <v>-10.93220310836072</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.328707551492087</v>
+        <v>-5.411220156334899</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.610568648224927</v>
+        <v>-5.692416222841736</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-9.552089866766501</v>
+        <v>-8.60036985198542</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-6.22375806418156</v>
+        <v>-5.333736556425926</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-8.690719981478615</v>
+        <v>-7.767872239882863</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-9.864990041353764</v>
+        <v>-8.911552731655618</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-13.5707816120759</v>
+        <v>-12.55424252687396</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-10.82939972175347</v>
+        <v>-10.91512477762708</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-9.546422016605725</v>
+        <v>-12.44071810950417</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-9.362945616034125</v>
+        <v>-12.24633371697542</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-4.556829069405275</v>
+        <v>-7.548999961935003</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-2.84969080534443</v>
+        <v>-4.826052945740329</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-4.360975650462997</v>
+        <v>-5.262113741755023</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.9189640768588063</v>
+        <v>-0.07634448270248129</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01662</t>
+          <t>X ≈ -0.01659</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.043060927955501</v>
+        <v>3.528021981387994</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.123131768649522</v>
+        <v>0.5702563553460607</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-8.069930754262835</v>
+        <v>-8.73562730890275</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-8.789992089959682</v>
+        <v>-9.452437865852794</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-9.162355183393238</v>
+        <v>-9.792635809836774</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-10.26701592493632</v>
+        <v>-10.91137923132523</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-12.3419967392053</v>
+        <v>-12.99895433353306</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-12.62853567266534</v>
+        <v>-13.2854334182534</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-7.41839373887543</v>
+        <v>-8.00743876014387</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.733592629322594</v>
+        <v>-2.23689532858193</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-9.222788541537241</v>
+        <v>-9.82871858300097</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.326349238291165</v>
+        <v>-4.863964494119479</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.168509522463161</v>
+        <v>-4.6881025698721</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5067491599674412</v>
+        <v>-0.975110263445913</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>4.009842110944398</v>
+        <v>3.610220080249363</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.5747981155643913</v>
+        <v>-1.04339969157224</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.007902253739935</v>
+        <v>-2.49356942112513</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.70752954684707</v>
+        <v>-5.229309018963576</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.892154726618962</v>
+        <v>-1.065492607085368</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.229242646804288</v>
+        <v>-2.189980268836464</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-4.070121226975331</v>
+        <v>-4.05452456024166</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-9.338713327153869</v>
+        <v>-9.392222637882782</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-6.470591150165212</v>
+        <v>-6.480945864011566</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.353763195868751</v>
+        <v>-0.5149409739298534</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01418</t>
+          <t>X ≈ -0.01415</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.432870920167815</v>
+        <v>0.3589213613364493</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-6.078262890839355</v>
+        <v>-6.938943700101731</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.400346224081083</v>
+        <v>-2.399056871226627</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.142619006722853</v>
+        <v>-3.109695638354211</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.512251138518714</v>
+        <v>-3.442840108255616</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.272827938648206</v>
+        <v>-1.267814009097847</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-7.156093233294222</v>
+        <v>-6.016378644604131</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.360249061886769</v>
+        <v>-3.308349034369108</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.32011745346675</v>
+        <v>-3.268383713602319</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-5.100577728988704</v>
+        <v>-4.039794047278676</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.7166236141024882</v>
+        <v>0.2182958532966879</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.051382378282376</v>
+        <v>-2.05463750135295</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.100465412764841</v>
+        <v>-0.1838995217564658</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.409539813867468</v>
+        <v>-3.397439137248838</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-3.01747902254268</v>
+        <v>-2.059605505341338</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-2.420669591067721</v>
+        <v>-1.466522234833718</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.5320316739613489</v>
+        <v>1.394982384553558</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.455634875755131</v>
+        <v>2.289603439852016</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.442588432868142</v>
+        <v>-1.491416203495298</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-4.312090239076049</v>
+        <v>-3.304553391582246</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-4.861221994868401</v>
+        <v>-3.848263787569294</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-4.939382600133122</v>
+        <v>-3.924109748978395</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-7.139665118328566</v>
+        <v>-6.649635036496349</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-8.248929884849346</v>
+        <v>-7.725467289719397</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.01173</t>
+          <t>X ≈ -0.01171</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.521812692116022</v>
+        <v>5.842402762787103</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.112798778203505</v>
+        <v>-1.734181898654292</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.732811082121287</v>
+        <v>-2.273147555559824</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.937177828952159</v>
+        <v>2.440535216229613</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.906093458896692</v>
+        <v>-3.326422389393166</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.631102666639855</v>
+        <v>-4.041982857500763</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.496593676821625</v>
+        <v>-3.913217023923721</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.951006426701888</v>
+        <v>-1.479405823920295</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.910160772992796</v>
+        <v>-1.438423385443976</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.7749327470097</v>
+        <v>-2.216167989731183</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.414582052655739</v>
+        <v>-1.9416226581505</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-6.354818035690478</v>
+        <v>-6.753190439534819</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.66527445966004</v>
+        <v>2.088818387938751</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.358508775884552</v>
+        <v>2.773950106218948</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.695601940985945</v>
+        <v>0.2974147047421383</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.377449779406419</v>
+        <v>-0.01339332229621704</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>3.626035886824482</v>
+        <v>0.7599041682517793</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>8.103299541496895</v>
+        <v>7.013141542550031</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>8.318961205727398</v>
+        <v>6.326187706358432</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>8.505697335546401</v>
+        <v>7.426728016951969</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>5.215630658279316</v>
+        <v>4.697190757885245</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.3609887282261184</v>
+        <v>-0.83320065806911</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.8307412193082158</v>
+        <v>0.350364963503452</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.997156499812434</v>
+        <v>-2.452740016992763</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.009288</t>
+          <t>X ≈ -0.009267</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-6.056201259106395</v>
+        <v>-5.883762530506132</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.387009727720944</v>
+        <v>5.094249730077159</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>6.779605656568251</v>
+        <v>7.431979108776794</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.747404335260171</v>
+        <v>4.45903325735361</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7.227556267172616</v>
+        <v>7.896280670488721</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>9.743314048145052</v>
+        <v>10.34215447174694</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9.72742109660097</v>
+        <v>8.821091575938858</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>9.446030063451559</v>
+        <v>7.793155349124049</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.945699249357489</v>
+        <v>6.328367109193813</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.83870793721028</v>
+        <v>4.051267164075767</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>5.119624314453162</v>
+        <v>3.570719327549988</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.292146714692123</v>
+        <v>2.53821860456658</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.927230785646614</v>
+        <v>1.417638840162581</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.476949788089023</v>
+        <v>2.709204671315966</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3.579512567326688</v>
+        <v>4.321812322915072</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>5.733416668244722</v>
+        <v>7.186576820102133</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>5.599322974095799</v>
+        <v>7.055322087942031</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.720843883972094</v>
+        <v>4.681977868294595</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.396768196534133</v>
+        <v>4.899476044226184</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.365798288290712</v>
+        <v>5.08822177433612</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.496502792003398</v>
+        <v>3.788099848794332</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>4.656780744018981</v>
+        <v>4.469829644960818</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>4.159760842625545</v>
+        <v>3.229152842291874</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.6697946416430369</v>
+        <v>-1.392133956386118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.006843</t>
+          <t>X ≈ -0.006821</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.252808777387784</v>
+        <v>2.382332482675999</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.275720096126996</v>
+        <v>-2.00674000003535</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.322427416050736</v>
+        <v>-5.077995134541538</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.059456316313835</v>
+        <v>-2.558220572088331</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.027720097648285</v>
+        <v>-4.520498412300235</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-10.01084419950295</v>
+        <v>-11.610658373004</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.609599097812385</v>
+        <v>-7.538238286518279</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-10.28997313069863</v>
+        <v>-10.25280920437763</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7.393836719587732</v>
+        <v>-7.785636829358047</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.57940326272189</v>
+        <v>-6.9527640429489</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.507614910079475</v>
+        <v>-5.867694461782946</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-7.388399332419709</v>
+        <v>-7.773537028525205</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.323733578658832</v>
+        <v>-5.18211189246437</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.94922296907535</v>
+        <v>-4.594752731300019</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-3.814824744555303</v>
+        <v>-4.447161235566021</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.939089848307859</v>
+        <v>-3.85151104212806</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.27318354245697</v>
+        <v>-2.362752005705786</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.5781669585522522</v>
+        <v>-1.655746448186456</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3620437956206146</v>
+        <v>-2.250237071566765</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.775000000000006</v>
+        <v>-3.208156643993512</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.7182004089981362</v>
+        <v>-2.124686551796941</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.60584453535926</v>
+        <v>0.2384918770378661</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.519380298158431</v>
+        <v>-4.365082190968081</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-3.795321637426895</v>
+        <v>-2.814898184028571</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004399</t>
+          <t>X ≈ -0.004379</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.780024845884334</v>
+        <v>-2.517837811487389</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.425613872933418</v>
+        <v>3.191981296199337</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5680615553727222</v>
+        <v>0.3427611412281877</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.627220310490223</v>
+        <v>-3.632654610538673</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.793782320147834</v>
+        <v>-3.045121792913932</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.54374358157024</v>
+        <v>-3.786092943028684</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.851943374392029</v>
+        <v>-4.101203757238466</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.08242245694630412</v>
+        <v>0.5430556085151537</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.686469443873051</v>
+        <v>-1.938361689005319</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7535519246988756</v>
+        <v>1.478814942380559</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.435458350526886</v>
+        <v>3.151907604608063</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4.032338219988247</v>
+        <v>4.738561026867906</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.783869687951544</v>
+        <v>5.479058496908998</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.216586082835157</v>
+        <v>2.927630670494608</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>3.715615360286428</v>
+        <v>3.668620291795747</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.493774001457105</v>
+        <v>1.931912320132113</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.359680307308295</v>
+        <v>1.79879535950014</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1537538130123437</v>
+        <v>-0.1742007042954228</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.06236934991947152</v>
+        <v>0.787810402204407</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.2494131455399042</v>
+        <v>0.9746562121724338</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.584147008842422</v>
+        <v>2.30126892271096</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.508191953199812</v>
+        <v>2.225422961301973</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.313483551606829</v>
+        <v>1.565318234531688</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.584960052713946</v>
+        <v>3.825934579439249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001955</t>
+          <t>X ≈ -0.001936</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>211</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8872502370481499</v>
+        <v>-1.3262833983012</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.556238978830869</v>
+        <v>3.062644124809921</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.570214328545518</v>
+        <v>1.605502972093731</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5691644797341127</v>
+        <v>-0.5330380870423923</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.834354150824026</v>
+        <v>-2.768749923158772</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.227088221820928</v>
+        <v>-0.6875473232363518</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.432265700493197</v>
+        <v>-2.888183928498783</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.856043630407669</v>
+        <v>-5.058047719011107</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-5.762071776612594</v>
+        <v>-5.963678744009037</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.04709256410148</v>
+        <v>-10.53088194531298</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-9.302835889833446</v>
+        <v>-9.783259407008245</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-8.639859335280697</v>
+        <v>-8.839941170474781</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-8.349212287342546</v>
+        <v>-8.546898458404002</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.446782639934888</v>
+        <v>-5.650499817138687</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-6.57964752826107</v>
+        <v>-6.313431145596176</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-4.088852881483405</v>
+        <v>-4.299709052985186</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-6.118681172788726</v>
+        <v>-6.331424065132019</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-9.0672664846186</v>
+        <v>-8.523620687272768</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-6.481475075241285</v>
+        <v>-6.41199470919215</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-9.138033175355453</v>
+        <v>-9.068750794958611</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-10.6291008829315</v>
+        <v>-10.55916426150274</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-10.23112228928522</v>
+        <v>-10.16107657362296</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-9.482413473513773</v>
+        <v>-9.412668211851688</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-10.98015576064954</v>
+        <v>-10.91030141294226</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0004898</t>
+          <t>X ≈ 0.0005068</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.190774728241188</v>
+        <v>-2.144804709769346</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.525849614225642</v>
+        <v>-2.909467788387204</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1314349554805148</v>
+        <v>-0.05036670316523839</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.711552880499653</v>
+        <v>1.81548440946262</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.476246423944218</v>
+        <v>3.627997729273048</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.23897200811264</v>
+        <v>2.955806414279245</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.890487853611646</v>
+        <v>2.611591302599642</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3770131753921433</v>
+        <v>-0.6777717922720115</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.798144761263558</v>
+        <v>1.51365934052027</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2594173186167907</v>
+        <v>-0.5530339851277049</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.442884871561688</v>
+        <v>0.1519718912585901</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.425835829739299</v>
+        <v>-4.001838886212219</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-5.407708001703725</v>
+        <v>-5.987217122689799</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-8.620517804191174</v>
+        <v>-9.22238854049607</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-6.287996051775579</v>
+        <v>-6.872560599011024</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.547636856855156</v>
+        <v>-6.879406410299644</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-7.109080978354399</v>
+        <v>-7.448441692881438</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-6.786713967099253</v>
+        <v>-7.122247913944001</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-7.425291658868204</v>
+        <v>-7.768425498536715</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-8.092948717948723</v>
+        <v>-8.443648654086125</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-8.636149126946769</v>
+        <v>-8.986194822052155</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-8.284753755238761</v>
+        <v>-8.631006300702538</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-8.864679443457668</v>
+        <v>-9.218600553737829</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-8.513270355375717</v>
+        <v>-8.863398324202478</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.002934</t>
+          <t>X ≈ 0.002949</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.688871321723965</v>
+        <v>3.669404090665303</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.354019643983328</v>
+        <v>3.692907770510054</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.9787820899051098</v>
+        <v>-0.6174525308587988</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.138316445740124</v>
+        <v>-2.765774883472893</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.78767820287235</v>
+        <v>-2.390780909212999</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.404263538596354</v>
+        <v>-3.991045190501666</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.170349270060946</v>
+        <v>-2.980256247791864</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.533183179313198</v>
+        <v>-4.336197381919668</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.130889495096376</v>
+        <v>-3.936750639009411</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.02223456410173</v>
+        <v>-1.85626114195076</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.275280434911089</v>
+        <v>-3.871298815962014</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.112111344468758</v>
+        <v>-2.718730462999645</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.463248129446299</v>
+        <v>-5.276103574791996</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.240561619180937</v>
+        <v>-4.065703956576868</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-5.621514518868054</v>
+        <v>-5.445534277067331</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-4.66544363892168</v>
+        <v>-4.491153247008334</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-3.355494011771043</v>
+        <v>-2.972789733914581</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.821488258191238</v>
+        <v>-3.436053376803869</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.605365095259501</v>
+        <v>-3.220161995879621</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-4.140342960288812</v>
+        <v>-3.750162064047714</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-5.044554199611667</v>
+        <v>-4.65113117108185</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-6.203541746229014</v>
+        <v>-5.802245949695205</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-5.206744919097062</v>
+        <v>-4.810925359076997</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-5.28268625836553</v>
+        <v>-4.886757612300272</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.005378</t>
+          <t>X ≈ 0.005392</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.188243347512241</v>
+        <v>-2.33504090576772</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.044354955750457</v>
+        <v>-1.556523680507752</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.32676362868834</v>
+        <v>1.834148692845545</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.203023070864347</v>
+        <v>3.720870208526151</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.360001734601852</v>
+        <v>1.90183418451911</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.807296086139395</v>
+        <v>1.346165994869203</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>6.586497744115817</v>
+        <v>6.143418749073895</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.45829848000043</v>
+        <v>4.38206291286275</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.239925129094104</v>
+        <v>5.165779830517828</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.096767362522705</v>
+        <v>4.024025633196828</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.408982533363528</v>
+        <v>1.32613254446467</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.240999740999747</v>
+        <v>2.162004709068952</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3649729589688775</v>
+        <v>-0.44632328560796</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5247813411078752</v>
+        <v>0.4471687536460252</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.236220472440948</v>
+        <v>0.1589644354975945</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.8312805220623289</v>
+        <v>0.7533513574405859</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.067557198283772</v>
+        <v>0.991181432358978</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.9625737821884925</v>
+        <v>0.8863407285378315</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.784266017842661</v>
+        <v>-1.871745585705128</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.106481481481438</v>
+        <v>2.032572343222007</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4521699613724195</v>
+        <v>0.003037327672338108</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.3645258350109302</v>
+        <v>-0.8163030575286285</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.94160252038062</v>
+        <v>-2.028817192630179</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.276803118908418</v>
+        <v>-1.732902233957546</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.007822</t>
+          <t>X ≈ 0.007836</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>291</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.09945907021700862</v>
+        <v>0.2771626634423896</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.7755903895734235</v>
+        <v>-0.3985678372667678</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.209313312503348</v>
+        <v>1.588008029512523</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.257919785315416</v>
+        <v>-1.878389138320443</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.601934240386129</v>
+        <v>-1.192931849384607</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.245418077393801</v>
+        <v>-2.036355716473913</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.644251544577372</v>
+        <v>-1.434809517358623</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.1336716613579796</v>
+        <v>-0.005025759125942386</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.206922234229495</v>
+        <v>0.7253599917511906</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4287845685407419</v>
+        <v>0.1528731321086099</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.256252483726271</v>
+        <v>1.113679794644206</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.008086415302913</v>
+        <v>1.521677411569875</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.289093478602709</v>
+        <v>2.799438901051509</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.75502189093605</v>
+        <v>3.265376146475667</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3.096090651898798</v>
+        <v>2.822514046504416</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.285652419733189</v>
+        <v>1.011402686660418</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.8079161139004185</v>
+        <v>0.5338429379991396</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.421145756224419</v>
+        <v>2.147215292597195</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.9190558607369965</v>
+        <v>0.6448936151022835</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.449742268041277</v>
+        <v>1.175382036754115</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>5.030253199249508</v>
+        <v>5.100189820678118</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>4.610655531923008</v>
+        <v>4.680701247585127</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>4.198145475037407</v>
+        <v>3.924248125015673</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>4.122204135769017</v>
+        <v>4.192058483476245</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.01027</t>
+          <t>X ≈ 0.01028</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.325878594249275</v>
+        <v>2.162724315139485</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.990703079604884</v>
+        <v>1.827947516789649</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.217669282185426</v>
+        <v>3.06849989633011</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.837209302325583</v>
+        <v>7.712688734030252</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7.916383961746007</v>
+        <v>7.82332683291142</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8.992437463641636</v>
+        <v>8.903150161865995</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9.108460220476566</v>
+        <v>9.024058620832768</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>8.385461130513519</v>
+        <v>8.299418604651109</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.426977195536146</v>
+        <v>4.7694772151373</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.764252895877853</v>
+        <v>3.103704396243735</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.705278829659832</v>
+        <v>5.609906895548498</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.981740481740481</v>
+        <v>5.331157492100502</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.190582596586673</v>
+        <v>5.54728113953005</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.858114674441204</v>
+        <v>6.219059405940598</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>4.754738990959417</v>
+        <v>5.114487536931414</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.016465707247512</v>
+        <v>4.369588744588739</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.549038679765275</v>
+        <v>2.896385893325579</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.444055263669917</v>
+        <v>2.791545189504319</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.215733982157296</v>
+        <v>2.561007999000076</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.7083333333333357</v>
+        <v>-0.3771461910318408</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.9706884798908817</v>
+        <v>1.31245049814499</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.783622313137215</v>
+        <v>2.129461679593071</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.169508590730423</v>
+        <v>1.511079249217907</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.315789473684205</v>
+        <v>3.667389853137514</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.01271</t>
+          <t>X ≈ 0.01272</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4367113338083897</v>
+        <v>-0.4493577517298846</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7718868484526737</v>
+        <v>-0.7841345500796564</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.211587312538853</v>
+        <v>-2.22215359911069</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.205956165300321</v>
+        <v>-2.225887760397356</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.29065041075598</v>
+        <v>-3.270898091100584</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.981183639475809</v>
+        <v>-5.920811337627356</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-6.03462531109826</v>
+        <v>-5.983540163361717</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.71605765445851</v>
+        <v>-2.715652317334651</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.674541589435876</v>
+        <v>-2.674165135419948</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.02644314367955</v>
+        <v>2.935897911947777</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.893442193521658</v>
+        <v>-3.88224102745054</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.01426271570157</v>
+        <v>-2.033330856430453</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.419329473757053</v>
+        <v>-2.447273065130538</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.201837363928092</v>
+        <v>-1.249912225265078</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-2.580193063397054</v>
+        <v>-2.617275381001654</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.173140367519288</v>
+        <v>0.1047711154094131</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.6803777870613317</v>
+        <v>-0.7383658797241708</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.6534877177067457</v>
+        <v>0.5752331327667548</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.589035341070215</v>
+        <v>1.500344371847099</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>4.65377697841727</v>
+        <v>4.524069614439284</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.391152108987654</v>
+        <v>3.272303588317229</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.876348132481745</v>
+        <v>1.778017910596063</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.309396680258878</v>
+        <v>4.180152197546242</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.355757499263746</v>
+        <v>1.267440511698815</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.01515</t>
+          <t>X ≈ 0.01516</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.983536251906862</v>
+        <v>3.631880159295306</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.945658034559834</v>
+        <v>0.5698306336727157</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.307759372275498</v>
+        <v>0.949993402823587</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5939660590823408</v>
+        <v>1.14613029247176</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2286962740582936</v>
+        <v>0.8103398199244296</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.217662688866881</v>
+        <v>2.815487824203686</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.3570052449888976</v>
+        <v>0.2253573221314582</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.067142812195193</v>
+        <v>1.765327695560259</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.811361579920529</v>
+        <v>4.534087604747683</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.0375261691511</v>
+        <v>3.761171928711192</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.510083634464742</v>
+        <v>2.217049752691359</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.372613872613918</v>
+        <v>-1.698063287120277</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.298906892902814</v>
+        <v>-4.639407172158272</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-6.322065505738969</v>
+        <v>-6.678667866786682</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-4.278294042073576</v>
+        <v>-3.7004475280036</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.782333091551287</v>
+        <v>-2.196969696969695</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.2137240829975084</v>
+        <v>0.3963858933256148</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.3187074990927883</v>
+        <v>0.2915451895044328</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.805287038863625</v>
+        <v>-2.219836156843975</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-3.51914414414415</v>
+        <v>-2.942081255966912</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.359641850439395</v>
+        <v>-0.757354696660208</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-2.336497806982905</v>
+        <v>-1.742291567160223</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.061722640500832</v>
+        <v>-1.467816854678112</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-3.939465781571052</v>
+        <v>-3.361830926083208</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.0176</t>
+          <t>X ≈ 0.01761</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>112</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.781264262893657</v>
+        <v>-1.855132827717711</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.902154063252269</v>
+        <v>-4.86848105463887</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-7.234711670195544</v>
+        <v>-7.199357246527057</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-5.269933554817278</v>
+        <v>-6.126596980255513</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.063774768412777</v>
+        <v>-1.998101738517043</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.09089586969169972</v>
+        <v>-0.02542126670538636</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.542333430317157</v>
+        <v>-3.475941379167111</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.6433976384500255</v>
+        <v>1.602990033222596</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.363485132044076</v>
+        <v>4.323048643708731</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.589649721274647</v>
+        <v>3.550132967672241</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.328294702675649</v>
+        <v>8.288478324119801</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.156343656343708</v>
+        <v>7.11687177781468</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.817566723570799</v>
+        <v>7.779423996672897</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.917638483965014</v>
+        <v>4.87977369165489</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>3.25870724492777</v>
+        <v>3.328773251217179</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.853767294549051</v>
+        <v>3.923160173160127</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>7.291102171828797</v>
+        <v>7.360671607611266</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>6.293261612876321</v>
+        <v>6.362973760932945</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>6.509384775808094</v>
+        <v>6.578865141857229</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>6.696428571428626</v>
+        <v>6.765710951825298</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.260371019573476</v>
+        <v>5.330307641002157</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>8.75584453535938</v>
+        <v>8.825890251021541</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>7.244905416127388</v>
+        <v>7.314650677789317</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.276106934001668</v>
+        <v>6.345961281708902</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.02004</t>
+          <t>X ≈ 0.02005</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.01558482038493736</v>
+        <v>-0.5544273603455139</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.009296920395158</v>
+        <v>-3.358339961164525</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-11.54655836009101</v>
+        <v>-10.96919851636833</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-8.601815087918318</v>
+        <v>-7.978448832107368</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.650011702210655</v>
+        <v>-2.141399798481871</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.634713886405912</v>
+        <v>4.218405893788386</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2033111689860405</v>
+        <v>-0.257246493805674</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.363780913711338</v>
+        <v>1.933677863910418</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.063833564099831</v>
+        <v>5.678868749528831</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.16804693381821</v>
+        <v>9.844224678430621</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>14.1009427862994</v>
+        <v>13.82198802429628</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>12.60233668770255</v>
+        <v>12.30867071961367</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.47784546921536</v>
+        <v>11.18550865275753</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>11.25648865818101</v>
+        <v>10.96442977631094</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>9.378045224021683</v>
+        <v>9.071718577495808</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>9.973105273643249</v>
+        <v>9.666105499438913</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.741450603884431</v>
+        <v>3.35934885628852</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.855979382911173</v>
+        <v>4.489076053701908</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>7.51112693608686</v>
+        <v>7.174103237095402</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>7.698170731707251</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>9.593994712953254</v>
+        <v>9.287538681566467</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>9.51803965731073</v>
+        <v>9.21169272015748</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>8.573302628670795</v>
+        <v>8.251599531404921</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>3.619312508914561</v>
+        <v>3.237495673243338</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.02248</t>
+          <t>X ≈ 0.02249</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>69</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.296893087002786</v>
+        <v>4.330167379321615</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.410992934677381</v>
+        <v>5.444665943290723</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.420567832910052</v>
+        <v>5.455922256578539</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.156049882035724</v>
+        <v>6.192243599454628</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.006321352263640279</v>
+        <v>0.05935167763203708</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.180843260743103</v>
+        <v>0.2463178637293737</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5920228713109239</v>
+        <v>-0.525630820160977</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-5.218403603786008</v>
+        <v>-5.151668351870576</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-6.626162901082211</v>
+        <v>-6.559456532274709</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-5.950722949532803</v>
+        <v>-5.883096845992362</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.125639044736303</v>
+        <v>-7.058312566149276</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.607631498935845</v>
+        <v>-1.539960520321912</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.514254094171257</v>
+        <v>4.583254224416216</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.292897283136902</v>
+        <v>4.362175347969625</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6.532516768737288</v>
+        <v>6.602582775026754</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.779750731402096</v>
+        <v>2.849143610013172</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.54420776189086</v>
+        <v>5.613777197673386</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>9.787050432752096</v>
+        <v>9.85676258080872</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>12.90172432032164</v>
+        <v>12.97120468637078</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>10.19021739130434</v>
+        <v>10.25949977170107</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>9.64701698230639</v>
+        <v>9.716953603735043</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>9.571061926663781</v>
+        <v>9.641107642325942</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>15.64293854242123</v>
+        <v>15.71268380408331</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>11.21917111619629</v>
+        <v>11.28902546390356</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>69</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>11.54326989859707</v>
+        <v>11.5765441909159</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.512442210039659</v>
+        <v>2.546115218653</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.86984319522891</v>
+        <v>6.905197618897397</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.539602291877308</v>
+        <v>-2.503408574458405</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.892229372374018</v>
+        <v>2.957902402269696</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-5.616258188532257</v>
+        <v>-5.550783585545986</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.8572524910078982</v>
+        <v>0.9236445421578452</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.477248570127067</v>
+        <v>3.543983822042499</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.6202139105120139</v>
+        <v>0.6869202793195157</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1536215002574366</v>
+        <v>-0.08599539671699574</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.019288491495558</v>
+        <v>3.086614970082586</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.740194588020685</v>
+        <v>2.807865566634618</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.615703369533513</v>
+        <v>1.684703499778472</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.5042041661385</v>
+        <v>-1.434926101305777</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>2.184690681780715</v>
+        <v>2.254756688070181</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>4.229026093720933</v>
+        <v>4.298418972332009</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.094932399572009</v>
+        <v>4.164501835354535</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>2.540673621157872</v>
+        <v>2.610385769214496</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.206072146408566</v>
+        <v>4.275552512457701</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.943840579710141</v>
+        <v>3.01312296010687</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.9513648083933575</v>
+        <v>1.02130142982201</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>5.223235839707264</v>
+        <v>5.293281555369425</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>8.396561730827081</v>
+        <v>8.466306992489166</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>8.320620391558613</v>
+        <v>8.39047473926589</v>
       </c>
     </row>
     <row r="31">
@@ -2675,76 +2675,76 @@
         <v>38</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.042542458382378</v>
+        <v>-1.009268166063549</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.148597816446944</v>
+        <v>9.182270825060286</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.445739457623958</v>
+        <v>2.481093881292445</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.995104039167686</v>
+        <v>7.031297756586589</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.261413201511985</v>
+        <v>9.327086231407662</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>17.3433146566241</v>
+        <v>17.40878925961037</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.30729062983328</v>
+        <v>11.37368268098323</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.02873598431464</v>
+        <v>11.09547123623007</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>16.33340994407412</v>
+        <v>16.40011631288162</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.92799558593631</v>
+        <v>12.99562168947675</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.939196958314838</v>
+        <v>8.006523436901865</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.028524107471476</v>
+        <v>5.096195086085409</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.272453941615915</v>
+        <v>1.341454071860873</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.314255025318367</v>
+        <v>6.38353309015109</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>5.655323786281109</v>
+        <v>5.725389792570574</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>6.250383835902447</v>
+        <v>6.319776714513523</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>6.116290141753524</v>
+        <v>6.18585957753605</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.011306725658315</v>
+        <v>6.081018873714939</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.595850941221634</v>
+        <v>3.665331307270769</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.782894736842103</v>
+        <v>3.852177117238831</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.6081153804757307</v>
+        <v>0.6780520019043834</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.5321603248331215</v>
+        <v>0.6022060404952825</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.824643456053167</v>
+        <v>-1.754898194391082</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.7309941520468115</v>
+        <v>0.800848499754089</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>38</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.148597816447023</v>
+        <v>9.182270825060364</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.708897352360843</v>
+        <v>7.74425177602933</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.363525091799289</v>
+        <v>4.399718809218193</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.26141320151207</v>
+        <v>9.327086231407748</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.816998867150389</v>
+        <v>6.882473470136659</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11.30729062983324</v>
+        <v>11.37368268098319</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.397157036946226</v>
+        <v>8.463892288861658</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.807094154600492</v>
+        <v>5.873800523407994</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>15.55957453330472</v>
+        <v>15.62720063684516</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>15.83393380042006</v>
+        <v>15.90126027900708</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.92326094957674</v>
+        <v>12.99093192819068</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.7987697310896</v>
+        <v>11.86776986133456</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.94583397268682</v>
+        <v>9.015112037519543</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>8.286902733649477</v>
+        <v>8.356968739938942</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>6.25038383590249</v>
+        <v>6.319776714513566</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>6.116290141753566</v>
+        <v>6.185859577536093</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>6.011306725658244</v>
+        <v>6.081018873714868</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.595850941221634</v>
+        <v>3.665331307270769</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.782894736842124</v>
+        <v>3.852177117238853</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>5.87127327521258</v>
+        <v>5.941209896641233</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>5.795318219569971</v>
+        <v>5.865363935232132</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.438514438683633</v>
+        <v>3.508259700345718</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>8.625730994151972</v>
+        <v>8.69558534185925</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>21</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.468735737106343</v>
+        <v>3.502010029425172</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.628344539442736</v>
+        <v>-1.594671530829395</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.693859758375879</v>
+        <v>1.729214182044366</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.9800664451826862</v>
+        <v>1.01626016260159</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.147108101746014</v>
+        <v>-4.081435071850336</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.8019612731654959</v>
+        <v>0.8674358761517666</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.732809620793319</v>
+        <v>-4.666417569643372</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.011364266311816</v>
+        <v>-4.944629014396384</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.731752963194047</v>
+        <v>-9.665046594386546</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-5.743683612058675</v>
+        <v>-5.676057508518234</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.469324344943338</v>
+        <v>-5.401997866356311</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.74841824841824</v>
+        <v>-5.680747269804307</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.87290946690532</v>
+        <v>-6.803909336660361</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.332361516034915</v>
+        <v>-2.263083451202192</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-7.753197516976975</v>
+        <v>-7.68313151068751</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-11.92004222926032</v>
+        <v>-11.85064935064925</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-12.05413592340925</v>
+        <v>-11.98456648762672</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-7.397214577599797</v>
+        <v>-7.327502429543173</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-7.181091414667982</v>
+        <v>-7.111611048618848</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-2.232142857142897</v>
+        <v>-2.162860476746168</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-7.537248028045568</v>
+        <v>-7.467311406616915</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-7.613203083688177</v>
+        <v>-7.543157368026016</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-7.338427917205983</v>
+        <v>-7.268682655543898</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.109440267335074</v>
+        <v>2.179294615042352</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>13</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1720324404029938</v>
+        <v>0.205306732721823</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.855450766548969</v>
+        <v>-7.821777757935628</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.089464153980281</v>
+        <v>6.124818577648767</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.37567084078718</v>
+        <v>5.411864558206084</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>20.39501644037847</v>
+        <v>20.46068947027415</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.88987336107766</v>
+        <v>12.95534796406393</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.11700722902352</v>
+        <v>12.18339928017347</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.146144891197331</v>
+        <v>4.212880143112763</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.187660956219908</v>
+        <v>4.25436732502741</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-4.278482146857165</v>
+        <v>-4.210856043316724</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-4.004122879741828</v>
+        <v>-3.936796401154801</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.28321678321678</v>
+        <v>-4.215545804602847</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-5.40770800170398</v>
+        <v>-5.338707871459022</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-5.629064812738335</v>
+        <v>-5.559786747905612</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-6.287996051775579</v>
+        <v>-6.217930045486113</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-5.692936002154255</v>
+        <v>-5.623543123543179</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.865277996004515</v>
+        <v>1.934847431787041</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.760294579909349</v>
+        <v>1.830006727965973</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.976417742841164</v>
+        <v>2.045898108890299</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.163461538461597</v>
+        <v>2.232743918858326</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.620261129463586</v>
+        <v>1.690197750892239</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>1.544306073821033</v>
+        <v>1.614351789483194</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>1.819081240303163</v>
+        <v>1.888826501965248</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1.743139901034581</v>
+        <v>1.812994248741859</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1969 +3180,1969 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.03495</t>
+          <t>X &gt; -0.03491</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3339</v>
+        <v>3343</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01558482038493736</v>
+        <v>-0.01636701836363841</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.126523936164233</v>
+        <v>-0.1271840900878729</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1513783368622086</v>
+        <v>-0.1520496195523648</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1937522933874334</v>
+        <v>-0.1943935904250083</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.09566024446142052</v>
+        <v>-0.09712867826382166</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07041627481530099</v>
+        <v>-0.0719104068422709</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.02198607802699115</v>
+        <v>-0.02356042678623993</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.04507372625085537</v>
+        <v>-0.04662932628065874</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.04608978915874218</v>
+        <v>-0.04764394541744821</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.08705770491084763</v>
+        <v>-0.08858570120728615</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.06388054451147696</v>
+        <v>-0.0654293891442137</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1168370573025896</v>
+        <v>-0.1183315434541683</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1493842359174735</v>
+        <v>-0.1508724510654105</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2037943531292186</v>
+        <v>-0.2052248171432112</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.09830760402262229</v>
+        <v>-0.09988341431299119</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1724928958132708</v>
+        <v>-0.1739643525677508</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.07963901167394027</v>
+        <v>-0.08122604697295088</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.07712062073460402</v>
+        <v>-0.0787145895341439</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.08237872385009126</v>
+        <v>-0.0839612790336588</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1766751420879444</v>
+        <v>-0.1781406850350038</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1336402653713762</v>
+        <v>-0.135173530545984</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1019076346495424</v>
+        <v>-0.1034819462878147</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.108601855044661</v>
+        <v>-0.1101613522858145</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1367412241295085</v>
+        <v>-0.1382701613917732</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.03251</t>
+          <t>X &gt; -0.03247</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3311</v>
+        <v>3315</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.0148532593800681</v>
+        <v>-0.01592200857876236</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1239083815412414</v>
+        <v>-0.1248597523571462</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2569205537489623</v>
+        <v>-0.2577676610525828</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.173598262970124</v>
+        <v>-0.1745729922495158</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1917241463621266</v>
+        <v>-0.1936412020529445</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1378318865135384</v>
+        <v>-0.1398077053492699</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1125600786687784</v>
+        <v>-0.1145968413520606</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1335249430262095</v>
+        <v>-0.1355483722326483</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1649918029271333</v>
+        <v>-0.1669770963170052</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1697487749659459</v>
+        <v>-0.1717590633967205</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1787965814913974</v>
+        <v>-0.1807867857702377</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2599755044834779</v>
+        <v>-0.2618799934077316</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3134644968643912</v>
+        <v>-0.315348789170244</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3364050485338055</v>
+        <v>-0.3382714211270681</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.2546318256402671</v>
+        <v>-0.2566230011465791</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2742510414385109</v>
+        <v>-0.2761971201634168</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1795126563810214</v>
+        <v>-0.1815791879507742</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1459691894838073</v>
+        <v>-0.1480814289840353</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1531173782501085</v>
+        <v>-0.1552140319809325</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2498114630467541</v>
+        <v>-0.2517857124023095</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2320205659080301</v>
+        <v>-0.2340383505590538</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1994075020688726</v>
+        <v>-0.2014688083694196</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.2387039696560223</v>
+        <v>-0.2407086191260248</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2966807434371717</v>
+        <v>-0.2986196275778426</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.03006</t>
+          <t>X &gt; -0.03003</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3286</v>
+        <v>3290</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.0139076148054329</v>
+        <v>0.02873911429379916</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.07942993127782927</v>
+        <v>-0.07834294501441263</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1420726793104166</v>
+        <v>-0.1568453777312016</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.08293588823702436</v>
+        <v>-0.09758519421743728</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1891799985834908</v>
+        <v>-0.174600270215123</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1060290416045078</v>
+        <v>-0.1085530683982796</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1049821046824277</v>
+        <v>-0.1075453361415626</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.06342506640417866</v>
+        <v>-0.06605326467732198</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.09542342380479596</v>
+        <v>-0.09801251903170538</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.09433296270803027</v>
+        <v>-0.09696146332049693</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1964422305941227</v>
+        <v>-0.1989357150652893</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3064476457441785</v>
+        <v>-0.3088226065410709</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4731521117340236</v>
+        <v>-0.4753797424537751</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.4339565229697868</v>
+        <v>-0.436243624362433</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.3465929935288159</v>
+        <v>-0.3490187203759447</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.340547043207863</v>
+        <v>-0.3429534887994521</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.3048264212908549</v>
+        <v>-0.3072841097075099</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.209515682732075</v>
+        <v>-0.2120955871946464</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.3095369587927195</v>
+        <v>-0.3119867983118141</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.3780395136778054</v>
+        <v>-0.3803988582189319</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.3560234555166488</v>
+        <v>-0.3584368820120574</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.2922089926210987</v>
+        <v>-0.2947051317244558</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.3339224338444708</v>
+        <v>-0.3363563977847051</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.3917915096119273</v>
+        <v>-0.3941602988381661</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02762</t>
+          <t>X &gt; -0.02759</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3246</v>
+        <v>3250</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1508479944940007</v>
+        <v>0.16532836807216</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.06192849934249267</v>
+        <v>-0.06125082309676344</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1077056795531988</v>
+        <v>-0.1231230831369388</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1921844515017312</v>
+        <v>-0.2073556220419874</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2646607889771815</v>
+        <v>-0.2506371468052322</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1828076343975624</v>
+        <v>-0.1860699815156934</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1722970921533076</v>
+        <v>-0.1756221697570695</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1268353474481998</v>
+        <v>-0.1302354063714901</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1290894506868909</v>
+        <v>-0.1324862501875756</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.02647648380860801</v>
+        <v>-0.03004910515689119</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1025013346714232</v>
+        <v>-0.1059658770972405</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2104019369212722</v>
+        <v>-0.2137536053857616</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4267203065621032</v>
+        <v>-0.4298785836048324</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3228845065579762</v>
+        <v>-0.3261859928324071</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.3184816951644436</v>
+        <v>-0.3218316670311907</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.2582047837720864</v>
+        <v>-0.2615938389419057</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.2511116088572152</v>
+        <v>-0.2545198481543309</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.1225704025866889</v>
+        <v>-0.1261452281860471</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1956949798714263</v>
+        <v>-0.1991686523055591</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2673076923076962</v>
+        <v>-0.2706838150550155</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2998563031192276</v>
+        <v>-0.3032284355865116</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2958796025716026</v>
+        <v>-0.2992635005159201</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.341493017591759</v>
+        <v>-0.3448057531989051</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.3683345764287509</v>
+        <v>-0.3716211358734682</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.02517</t>
+          <t>X &gt; -0.02514</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3196</v>
+        <v>3200</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1170532368843809</v>
+        <v>0.1479727623444305</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0005958638382637105</v>
+        <v>-0.0004686322786753294</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.05577388432583774</v>
+        <v>-0.07202805398048184</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1615469165798942</v>
+        <v>-0.1775444794788683</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2294601716564699</v>
+        <v>-0.2162718530513885</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1492343886711396</v>
+        <v>-0.1536064749092674</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1887697826358377</v>
+        <v>-0.1931579518391473</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1382693247237938</v>
+        <v>-0.1427455744533077</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.07892266259042913</v>
+        <v>-0.08347212945279381</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.006205128484261024</v>
+        <v>0.001484198892789834</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.01821813231556035</v>
+        <v>0.01350166679026898</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.180492823884336</v>
+        <v>-0.1849873219895741</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3202790602057632</v>
+        <v>-0.3246935457037452</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2425299502208773</v>
+        <v>-0.2470620893865032</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.1965523940292755</v>
+        <v>-0.2011982574860198</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.1757939681582315</v>
+        <v>-0.180420161716917</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.1040296242552756</v>
+        <v>-0.1087591019971725</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.003026421387971823</v>
+        <v>-0.007893363209284132</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.2368329240178042</v>
+        <v>-0.2413933827694237</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.28125</v>
+        <v>-0.2857425883922815</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2745617719238709</v>
+        <v>-0.2791098693676091</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.3005969905942791</v>
+        <v>-0.3051216165611663</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.382501974730225</v>
+        <v>-0.3869046397453317</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.3772991092667084</v>
+        <v>-0.3817172897196315</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.02273</t>
+          <t>X &gt; -0.0227</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3143</v>
+        <v>3147</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.133145576871641</v>
+        <v>0.1664198691904701</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.01245647805705374</v>
+        <v>0.02121653055628769</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.07605174604888987</v>
+        <v>-0.05819272384594143</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2981052724452056</v>
+        <v>-0.2972130939995878</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1713242398142114</v>
+        <v>-0.1590699172577601</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1877797671924668</v>
+        <v>-0.1932727674952943</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2150278245305088</v>
+        <v>-0.2205684335287543</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1590149695181466</v>
+        <v>-0.1646582211471284</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.06771001859375758</v>
+        <v>-0.07346802747587589</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.03150960720174822</v>
+        <v>-0.0373958432827024</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1345141486289947</v>
+        <v>0.1284421577545913</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1578967783405147</v>
+        <v>-0.1636306415765745</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2177172695445151</v>
+        <v>-0.2234937632112874</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1349078437953963</v>
+        <v>-0.140815475275744</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.077043298944659</v>
+        <v>-0.08309529848406783</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1293786455152883</v>
+        <v>-0.1353071123277161</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.0541359234093548</v>
+        <v>-0.06017720115764291</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.01859391791647624</v>
+        <v>0.01244591896837477</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.2227807714781278</v>
+        <v>-0.2286040387083546</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.3028678106132858</v>
+        <v>-0.3085738557187838</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.3187089913247192</v>
+        <v>-0.324454263759776</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.3439169908726853</v>
+        <v>-0.3496416638720206</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.4318484915426524</v>
+        <v>-0.4374368154035864</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.4571097379677909</v>
+        <v>-0.4626773310288073</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.02029</t>
+          <t>X &gt; -0.02026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3075</v>
+        <v>3079</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2341473280993327</v>
+        <v>0.2674216204181619</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3188684542818834</v>
+        <v>0.3525414628952248</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2034573958804984</v>
+        <v>0.2388118195489852</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.007701844685726655</v>
+        <v>0.01035392413725589</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.09766673126404157</v>
+        <v>0.1267598340189195</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.08483379403698166</v>
+        <v>-0.07387087910851164</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.225016852974683</v>
+        <v>-0.2321244725595761</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.06459099213647335</v>
+        <v>-0.07194650035690842</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.02784019445739716</v>
+        <v>0.02036603220258115</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1466492125570866</v>
+        <v>0.1389163956894208</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2131947766949409</v>
+        <v>0.2054068031440792</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.0470900981105018</v>
+        <v>-0.0545822130342728</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1158190740405374</v>
+        <v>-0.1233730444736523</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.05868705435403143</v>
+        <v>-0.06634849305584112</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.01500704111077766</v>
+        <v>0.007159631676103118</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.1430379492916956</v>
+        <v>0.1350973289748794</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.09320192152745932</v>
+        <v>0.08530358613177924</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1049878613114359</v>
+        <v>0.09705572435040466</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1139918475684851</v>
+        <v>-0.1216166072626095</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.2648993179603778</v>
+        <v>-0.2723086024122168</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.3015662309602689</v>
+        <v>-0.309003566933356</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.4231447399086861</v>
+        <v>-0.4304388629024558</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.5516299730608978</v>
+        <v>-0.5587259455872555</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.5758094423049513</v>
+        <v>-0.5828885303821778</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01784</t>
+          <t>X &gt; -0.01781</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3019</v>
+        <v>3022</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3745948549470342</v>
+        <v>0.3927386620043194</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5002488333902591</v>
+        <v>0.5189430951329399</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3113712791132102</v>
+        <v>0.3321588172576995</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.07691954269436962</v>
+        <v>0.0801860292933867</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2571832590670127</v>
+        <v>0.2712312498643215</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.001772993570270387</v>
+        <v>-0.00278379551674135</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.02740735441544473</v>
+        <v>-0.05033340136954934</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1414782752546913</v>
+        <v>0.1184238747433923</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2679329269931969</v>
+        <v>0.2447360995806918</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3709100314033194</v>
+        <v>0.3477363201536363</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3345417559524648</v>
+        <v>0.3113458291832245</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.07465710255409874</v>
+        <v>0.0517568136232498</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.05921609137604378</v>
+        <v>0.03651736519814364</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.05567000975670311</v>
+        <v>0.03300330033003718</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.1764912124473099</v>
+        <v>0.1538098026485883</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.3286787467332815</v>
+        <v>0.3057323565910082</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.3466577273842972</v>
+        <v>0.3237066729753764</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.3078118774265874</v>
+        <v>0.3047639601587093</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.06097207739544075</v>
+        <v>0.1107423555526736</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.09613794244128826</v>
+        <v>-0.04645836034401896</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2226345585677763</v>
+        <v>-0.1724450644465705</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.3781342796024916</v>
+        <v>-0.3475301922466798</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.4809697021319437</v>
+        <v>-0.4700121453286314</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.6035362780363798</v>
+        <v>-0.5924428026249799</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.0154</t>
+          <t>X &gt; -0.01537</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2942</v>
+        <v>2946</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2785812969519057</v>
+        <v>0.3118555892707349</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4839463228481193</v>
+        <v>0.5176193314614608</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.5307323452484738</v>
+        <v>0.5660867689169606</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.308990309422569</v>
+        <v>0.3261057224471955</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.5037177458343294</v>
+        <v>0.5308557904404552</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.2705346341974035</v>
+        <v>0.2786327873486485</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.294898350081084</v>
+        <v>0.2837111304853224</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4757036573042583</v>
+        <v>0.4642124539245742</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4691046310285074</v>
+        <v>0.4576231631716894</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4259904885331238</v>
+        <v>0.4144138508066888</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.5846826236977734</v>
+        <v>0.5729360855735806</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1898431964511289</v>
+        <v>0.1785710768236726</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1698669657015444</v>
+        <v>0.1584016540865818</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.07039002201665312</v>
+        <v>0.05901030333307489</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.0761621780542896</v>
+        <v>0.0646423956229043</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.3523251499953162</v>
+        <v>0.3405368493474228</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.4082828526550486</v>
+        <v>0.396385893325558</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.4390767617464633</v>
+        <v>0.4475302691924128</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1120906239315076</v>
+        <v>0.1410865025860986</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.04030889341479593</v>
+        <v>0.008839557186675506</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1219355533103439</v>
+        <v>-0.07229637412734746</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.1436119863796961</v>
+        <v>-0.1141980042397748</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3242053066531696</v>
+        <v>-0.3149439299111449</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.5839008352515052</v>
+        <v>-0.5944421709144692</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.01295</t>
+          <t>X &gt; -0.01293</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.239225903822927</v>
+        <v>0.3102018376169866</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.7076842116803448</v>
+        <v>0.779620843462979</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.6306671857493455</v>
+        <v>0.6702731231033141</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.46076749876039</v>
+        <v>0.4468295931710671</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6747367200987426</v>
+        <v>0.6704796800643535</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.35725033527509</v>
+        <v>0.3329703416861989</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5489391878974033</v>
+        <v>0.505077601851788</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6405849978179887</v>
+        <v>0.5967690768442395</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.6323926950692993</v>
+        <v>0.5885439951033078</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.6144182977069761</v>
+        <v>0.5709215070992144</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6290505340902541</v>
+        <v>0.5853970916268807</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3003524691221884</v>
+        <v>0.2570394035340229</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.2131788253540066</v>
+        <v>0.1704291022890843</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.223132796737481</v>
+        <v>0.1804596863471915</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.1816395757547866</v>
+        <v>0.1392821672660673</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.4468701376519491</v>
+        <v>0.4040315466130977</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.4040636485542706</v>
+        <v>0.3612981740273113</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.4044173111106701</v>
+        <v>0.3828052807644653</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1991921594357464</v>
+        <v>0.1984478063837614</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1053370786516936</v>
+        <v>0.1252623593219084</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.03964995981132091</v>
+        <v>0.06037992290153227</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.01989934913315494</v>
+        <v>0.01967099592672383</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.09183286316194739</v>
+        <v>-0.09236167036845444</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.3225624107133669</v>
+        <v>-0.3438790957631994</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.01051</t>
+          <t>X &gt; -0.01049</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2736</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.06861115238874049</v>
+        <v>0.08778147878339126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8598891261165065</v>
+        <v>0.880687474176753</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7646654062164089</v>
+        <v>0.7886124047747103</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3621093386760066</v>
+        <v>0.3666732998463473</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.8173940627560796</v>
+        <v>0.8311738422135875</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5161430535531366</v>
+        <v>0.5088639279108165</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.710109905095635</v>
+        <v>0.6827137161921684</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7438318784001012</v>
+        <v>0.6802410209539289</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7336859436141623</v>
+        <v>0.6700375666896434</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7096080871346544</v>
+        <v>0.6829755438869896</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7503063644832864</v>
+        <v>0.6869951078825594</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5654890133563129</v>
+        <v>0.5388834396223174</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1553285241334805</v>
+        <v>0.09330087808532284</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1380611659892992</v>
+        <v>0.07618923817983614</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1213245546253248</v>
+        <v>0.1329244994581771</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.4097966066025123</v>
+        <v>0.4208139792081411</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.275702912453589</v>
+        <v>0.3452723482361151</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.09770014623051537</v>
+        <v>0.1162347439236626</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.1242927916043755</v>
+        <v>-0.04791600538423069</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.2293263964950683</v>
+        <v>-0.1682907190184721</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.1665568735706344</v>
+        <v>-0.1260415653470801</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.03507361829695554</v>
+        <v>0.05396042646018628</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1285874592837501</v>
+        <v>-0.1101613522858145</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2558479532163673</v>
+        <v>-0.2590930207137703</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.008065</t>
+          <t>X &gt; -0.008043</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.371680120966758</v>
+        <v>0.3904864746459893</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6853595681544959</v>
+        <v>0.667096760744009</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4670331498698843</v>
+        <v>0.4518518806087002</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1945976184767844</v>
+        <v>0.1592264817238558</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.500205369096804</v>
+        <v>0.4730347864024154</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.05956267062165921</v>
+        <v>0.01040219527396147</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2639138392328846</v>
+        <v>0.2701692163893412</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3132282858141267</v>
+        <v>0.3196785434890899</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3768199227315847</v>
+        <v>0.3832098018622432</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5052912936326379</v>
+        <v>0.5122326506976975</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5341030597091745</v>
+        <v>0.540815539143658</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4305680914260108</v>
+        <v>0.4375346524592345</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.01816880348322769</v>
+        <v>0.02616853899385774</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.02715426640457963</v>
+        <v>-0.05728159022798707</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.04979406970856814</v>
+        <v>-0.07941543629308256</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1463723687997458</v>
+        <v>0.07784904257296432</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.01227867465082255</v>
+        <v>0.005131578020609595</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.1310630076508303</v>
+        <v>-0.1152084559292348</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.298522506782696</v>
+        <v>-0.2987054641202391</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.456703107019564</v>
+        <v>-0.4347498776677838</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.3478129905092757</v>
+        <v>-0.324454263759776</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.1936184489136821</v>
+        <v>-0.1698854786250976</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.3407842107015853</v>
+        <v>-0.2794353437160169</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.3016507513509552</v>
+        <v>-0.2016577659100989</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.005621</t>
+          <t>X &gt; -0.0056</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2769415705829346</v>
+        <v>0.2917371562309512</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.7841246600300735</v>
+        <v>0.7996569870946217</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7082428882824843</v>
+        <v>0.7260039091711761</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2577550487140243</v>
+        <v>0.2939487661329281</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6778809063019366</v>
+        <v>0.7205981009692835</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5667346523966685</v>
+        <v>0.5865369997472456</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6604445068922971</v>
+        <v>0.6572849450703728</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8472331919640368</v>
+        <v>0.8438284802031575</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7681704788516157</v>
+        <v>0.78819494319238</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8620950081952117</v>
+        <v>0.8823231760175361</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.8383797503713737</v>
+        <v>0.8585288523697656</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8243517046333935</v>
+        <v>0.8446131759421434</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.2872009540745921</v>
+        <v>0.2843783306380914</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1703713531900348</v>
+        <v>0.1676716344200884</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.1398227048102996</v>
+        <v>0.1371233518208044</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.251401690773335</v>
+        <v>0.2726540770019028</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.07701790798621744</v>
+        <v>0.1225236299344985</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1085456853854438</v>
+        <v>-0.03883353732882</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.2953234088355785</v>
+        <v>-0.2019548040170918</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.3903102336825128</v>
+        <v>-0.2972532907036367</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.3291593131075388</v>
+        <v>-0.235204537267002</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.2842441028355651</v>
+        <v>-0.1901315143955742</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.1303392022680185</v>
+        <v>-0.07688211428756375</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1257003642600978</v>
+        <v>-0.07210171132381049</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003177</t>
+          <t>X &gt; -0.003157</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.563911093151269</v>
+        <v>0.5569550843702373</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.5361576250594169</v>
+        <v>0.5738266376687733</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.721402264179261</v>
+        <v>0.7621812150114025</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.6224530440910598</v>
+        <v>0.664611810953275</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.003779657837327</v>
+        <v>1.076074085658753</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9526014941044494</v>
+        <v>0.9993040080198696</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.084040196056492</v>
+        <v>1.106476203250395</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9190289991737259</v>
+        <v>0.8722208024533629</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.092471185568392</v>
+        <v>1.045576116236191</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8722843765445916</v>
+        <v>0.8260156162461811</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6884556684704748</v>
+        <v>0.6420387540111392</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5232053283572426</v>
+        <v>0.4770327436095059</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.1349191165802353</v>
+        <v>-0.205988478176188</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.02171491274845039</v>
+        <v>-0.09286265482558775</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.1958510878809392</v>
+        <v>-0.1962424819483388</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.1347752905196273</v>
+        <v>0.1160236120571057</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.04339068216609121</v>
+        <v>-0.03571287210654361</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.1043018197245758</v>
+        <v>-0.02605516338490332</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.3289014421607561</v>
+        <v>-0.2953865438191983</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4503635962979331</v>
+        <v>-0.4173188547157523</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.5087689413910752</v>
+        <v>-0.4746422613231545</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.4525071614232843</v>
+        <v>-0.4181547423617289</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.2658765520147597</v>
+        <v>-0.2319023501266955</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.4740347268936276</v>
+        <v>-0.4400680837205044</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0007324</t>
+          <t>X &gt; -0.0007145</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7126939117479978</v>
+        <v>0.7502251815704639</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3290452996727353</v>
+        <v>0.3184081115078783</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6343763430999303</v>
+        <v>0.6756340891629691</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.74462568623251</v>
+        <v>0.7875223792786983</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.397290947257908</v>
+        <v>1.470654759715408</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.176077942141497</v>
+        <v>1.172419587248982</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.547082248618189</v>
+        <v>1.516434028055386</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.511128282381534</v>
+        <v>1.480823262584209</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.795245026686068</v>
+        <v>1.764911123780813</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.991812333044258</v>
+        <v>1.991533799849769</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.712830070220782</v>
+        <v>1.711950189796696</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.462664339060645</v>
+        <v>1.433200786348699</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.707265460208319</v>
+        <v>0.650009579133183</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.5344995140913582</v>
+        <v>0.4774979683495388</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.4586586540628019</v>
+        <v>0.4315429305174732</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.5678100545102254</v>
+        <v>0.5691946199967646</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.5794889551134901</v>
+        <v>0.610393675426721</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.8146415934399798</v>
+        <v>0.8460198976755748</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.3019017826108623</v>
+        <v>0.3323392941641075</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.4403547133138943</v>
+        <v>0.4705469718364128</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.5288355482420783</v>
+        <v>0.5602965237147401</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.5500622224342706</v>
+        <v>0.5817268268970821</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.679064794164205</v>
+        <v>0.7102871424919712</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.6031234548957372</v>
+        <v>0.6344548892686959</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001712</t>
+          <t>X &gt; 0.001728</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1824</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.085178375430814</v>
+        <v>1.118452667749644</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6952982656004991</v>
+        <v>0.7289712742138406</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7326218715362387</v>
+        <v>0.7679762952047255</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6205791053890408</v>
+        <v>0.6567728228079446</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.130582843340918</v>
+        <v>1.196255873236595</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9114303481517823</v>
+        <v>0.9455852978460157</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.374737450609167</v>
+        <v>1.377137708047563</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.753356956240665</v>
+        <v>1.755381405526435</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.7948730212633</v>
+        <v>1.796868587441139</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.280621400198136</v>
+        <v>2.315184965482857</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.87575067136455</v>
+        <v>1.91036848215461</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.089807452821155</v>
+        <v>2.124499692069158</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.491752187229942</v>
+        <v>1.494218238575577</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.708991867423663</v>
+        <v>1.711255462895693</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.32418343540391</v>
+        <v>1.360573642606617</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.480646993797222</v>
+        <v>1.516604400166045</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.565851545262326</v>
+        <v>1.635420981044852</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.789815497588101</v>
+        <v>1.859527645644725</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.2932193622743</v>
+        <v>1.362699728323435</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.535087719298247</v>
+        <v>1.604370099694975</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.704606608545902</v>
+        <v>1.774543229974554</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.683476114306806</v>
+        <v>1.753521829968967</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.903426719385422</v>
+        <v>1.973171981047507</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.772660818713447</v>
+        <v>1.842515166420725</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.004156</t>
+          <t>X &gt; 0.004171</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.6189709118734754</v>
+        <v>0.6577954205046836</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2192376180167557</v>
+        <v>0.193736139931211</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.039059426364453</v>
+        <v>1.018160529814246</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.293632801357212</v>
+        <v>1.274825127048942</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.832171925306696</v>
+        <v>1.84401203006729</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.863238497233382</v>
+        <v>1.837054492829182</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.188563579649646</v>
+        <v>2.164006907839926</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.879001182193093</v>
+        <v>2.855414079764287</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.8559177640116</v>
+        <v>2.832260020567162</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.051074601304187</v>
+        <v>3.068475233427186</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.977131160335688</v>
+        <v>2.95443655734848</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.021243462419939</v>
+        <v>2.999102419101007</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.737088378386574</v>
+        <v>2.716820041766233</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.774296531799536</v>
+        <v>2.754473377480053</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.567853980545038</v>
+        <v>2.589637791207934</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>2.581142860159957</v>
+        <v>2.601500441306264</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.447049166011034</v>
+        <v>2.467583304328791</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.794554437698558</v>
+        <v>2.815817034164574</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.170341466176595</v>
+        <v>2.190284466868832</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.551308985132515</v>
+        <v>2.57130503411841</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>2.913085951700168</v>
+        <v>2.934907733466297</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3.095695860504875</v>
+        <v>3.117961448432595</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>3.176547303651517</v>
+        <v>3.198261403633097</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>3.035964723271221</v>
+        <v>3.057704231315974</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0066</t>
+          <t>X &gt; 0.006614</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.212508774077193</v>
+        <v>1.288730351356769</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4864028450466265</v>
+        <v>0.5627172462776855</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.766796204259947</v>
+        <v>0.8461379468554568</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.6784915540847649</v>
+        <v>0.7591620181795378</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.720571260851187</v>
+        <v>1.831822249857616</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.875066571622874</v>
+        <v>1.940541174609145</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.258694962260556</v>
+        <v>1.325087013410503</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.545085543659049</v>
+        <v>2.53357353422863</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.351859824644123</v>
+        <v>2.340318932105774</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.829980595408344</v>
+        <v>2.867030830967913</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.308689601433954</v>
+        <v>3.297707544390605</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.186212769219821</v>
+        <v>3.17557521220337</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.392966656449204</v>
+        <v>3.383658251063771</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.249918381045227</v>
+        <v>3.240887910247572</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3.060838355790224</v>
+        <v>3.102060308986999</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.951121584738161</v>
+        <v>2.991118077324977</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.738719354958846</v>
+        <v>2.778831034391395</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>3.181895688276256</v>
+        <v>3.222579672262995</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.00647617305615</v>
+        <v>3.046621523406756</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.645360219263907</v>
+        <v>2.684877991682001</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.433404915982464</v>
+        <v>3.552990130925991</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.827301074122161</v>
+        <v>3.947363605253578</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>4.258693311865052</v>
+        <v>4.30020822369174</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>3.947826365705446</v>
+        <v>4.06763615855624</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.009044</t>
+          <t>X &gt; 0.009057</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.599712265648805</v>
+        <v>1.587579282507122</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.8588572378198904</v>
+        <v>0.8467111135989285</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6361953132875016</v>
+        <v>0.6269661762430658</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.545120052832679</v>
+        <v>1.538377639033833</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.701148442250833</v>
+        <v>2.725429806080456</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.091152811849902</v>
+        <v>3.115441677457028</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.115446923203592</v>
+        <v>2.140447308287484</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.256770573831069</v>
+        <v>3.283555660488723</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.689767369076826</v>
+        <v>2.817428629205466</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.538650011045732</v>
+        <v>3.668878435402483</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.914429156457217</v>
+        <v>3.942938077564406</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.533915374686167</v>
+        <v>3.66418867411641</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.423622939160488</v>
+        <v>3.556255033656221</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.100846249829985</v>
+        <v>3.233653314570041</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.050434280569554</v>
+        <v>3.18464707282704</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.442654573598652</v>
+        <v>3.575988309490846</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.308560879449729</v>
+        <v>3.442071172513373</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.406417219946732</v>
+        <v>3.540276153971377</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.622540382878547</v>
+        <v>3.756167534895702</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.99822515212982</v>
+        <v>3.130830603746979</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.962124134612587</v>
+        <v>3.095898648978924</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.596108227043004</v>
+        <v>3.730712586046984</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>4.276562906709721</v>
+        <v>4.411278669087409</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.896361932552814</v>
+        <v>4.030877887945351</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.01149</t>
+          <t>X &gt; 0.0115</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>761</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.385011314354323</v>
+        <v>1.418285606673152</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.5242116209977823</v>
+        <v>0.5578846296111237</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.1270525750200306</v>
+        <v>-0.0916981513515438</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3152217095009604</v>
+        <v>-0.2790279920820566</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.159193130967772</v>
+        <v>1.224866160863449</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.346357743974558</v>
+        <v>1.411832346960828</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.04786743320830311</v>
+        <v>0.1142594843582501</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.740403457860573</v>
+        <v>1.807138709776005</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.176137656917369</v>
+        <v>2.242844025724871</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.767611050352926</v>
+        <v>3.835237153893367</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.38494009407799</v>
+        <v>3.452266572665017</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.105846190603089</v>
+        <v>3.173517169217021</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.901197284862334</v>
+        <v>2.970197415107293</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.285622339793818</v>
+        <v>2.354900404626541</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.5465334135029</v>
+        <v>2.616599419792365</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.272999507802332</v>
+        <v>3.342392386413408</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.533123947687571</v>
+        <v>3.602693383470097</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.690952620948408</v>
+        <v>3.760664769005032</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.038481828558282</v>
+        <v>4.107962194607417</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>4.094119579500656</v>
+        <v>4.163401959897385</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.550919170502702</v>
+        <v>3.620855791931355</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.131994338250372</v>
+        <v>4.202040053912533</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.19520577280084</v>
+        <v>5.264951034462925</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.068016076107916</v>
+        <v>4.137870423815194</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.01393</t>
+          <t>X &gt; 0.01394</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.792116536371388</v>
+        <v>1.843023854309969</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.8138542050068054</v>
+        <v>0.863085765637571</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3387839660010528</v>
+        <v>0.3928086520904586</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.1073057653480944</v>
+        <v>0.1637256003896468</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.153611543025008</v>
+        <v>2.247289966552046</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.98386297275205</v>
+        <v>3.079417442972009</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.40713831979771</v>
+        <v>1.501017146178434</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.736300716079782</v>
+        <v>2.835708927231806</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.260131893642615</v>
+        <v>3.361067076888446</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.933241820493762</v>
+        <v>4.039764304077764</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.011459608509426</v>
+        <v>5.120275559142918</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.250050592494325</v>
+        <v>4.357655187952979</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.090189599087566</v>
+        <v>4.20223505658074</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.064974267152891</v>
+        <v>3.174704567230926</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.692216661556103</v>
+        <v>3.80688385029552</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.965733302817355</v>
+        <v>4.078690127077223</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.474726425388695</v>
+        <v>4.589934280422341</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>4.369743009293416</v>
+        <v>4.485093576601159</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.585866172225231</v>
+        <v>4.700984957525485</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.969051446945336</v>
+        <v>4.08137915459028</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.586622742127446</v>
+        <v>3.700123309204891</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>4.636069615745292</v>
+        <v>4.753309605860302</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.393159894767614</v>
+        <v>5.511655286084292</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>4.67413173877889</v>
+        <v>4.79066174253844</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01638</t>
+          <t>X &gt; 0.01639</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.316093858437071</v>
+        <v>1.457192102254311</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.7852236275500815</v>
+        <v>0.9263368725319481</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1283020284345895</v>
+        <v>0.2726315489911499</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.001592863969420932</v>
+        <v>-0.04816560770649403</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.57174382258529</v>
+        <v>2.557220390334471</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.150297868077402</v>
+        <v>3.136343439176947</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.790347587295393</v>
+        <v>1.776159461168952</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.881655955475459</v>
+        <v>3.066575467396262</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.923172020498093</v>
+        <v>3.108062649310966</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.910589055912617</v>
+        <v>4.099852855627418</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.55481133672658</v>
+        <v>5.746461517397179</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.471412149494348</v>
+        <v>5.663790545321731</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.912478660948487</v>
+        <v>6.109255929446014</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.104037701186151</v>
+        <v>5.299941758881772</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.423580043362158</v>
+        <v>5.426112186791407</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>5.431555944255557</v>
+        <v>5.432263814616761</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>5.493156966349289</v>
+        <v>5.494425109011829</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>5.38817355025401</v>
+        <v>5.389584405190647</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>6.191380861913807</v>
+        <v>6.193711080232625</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.595645792563602</v>
+        <v>5.596243164710458</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>4.661055951080321</v>
+        <v>4.661540133999331</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.150658625379002</v>
+        <v>6.154321623570617</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>7.012517940589127</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.545187168835334</v>
+        <v>6.549042514201936</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01882</t>
+          <t>X &gt; 0.01883</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.466229471442183</v>
+        <v>2.389303640336884</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.381680523213902</v>
+        <v>2.557039404801131</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.195112891207962</v>
+        <v>2.375301762805314</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.481319578014805</v>
+        <v>1.662347743362574</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.872942023567205</v>
+        <v>3.83912008488565</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.060106636573991</v>
+        <v>4.026086270983029</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.287240504519964</v>
+        <v>3.254137587092679</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.509938991833479</v>
+        <v>3.478438705153678</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.799575357607992</v>
+        <v>2.766157042847276</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.281379044582927</v>
+        <v>4.254547899474105</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.05699144453034</v>
+        <v>5.031120104450103</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.279150673887521</v>
+        <v>5.254883263816168</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.658418853896613</v>
+        <v>5.639258885402263</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.437062042862259</v>
+        <v>5.418180008955673</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.031263635905155</v>
+        <v>6.01631811841029</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>5.874443986278429</v>
+        <v>5.856936196132182</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.98847059288137</v>
+        <v>4.969250214933595</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>5.134113743202136</v>
+        <v>5.115665792519451</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.102116605382072</v>
+        <v>6.08532601766489</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.286654135338338</v>
+        <v>5.267146702004766</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>4.492827159924353</v>
+        <v>4.473344252631698</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>5.41937836994591</v>
+        <v>5.402523416850748</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>6.933279536367976</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.620718462823724</v>
+        <v>6.606191001737663</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.02126</t>
+          <t>X &gt; 0.02127</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>317</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.10821297910725</v>
+        <v>3.14148727142608</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.034867117459775</v>
+        <v>4.068540126073117</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.74974078586574</v>
+        <v>5.785095209534227</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.089575232924958</v>
+        <v>4.125768950343861</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.301592514146968</v>
+        <v>5.367265544042645</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.911470060907696</v>
+        <v>3.976944663893967</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.084976168601294</v>
+        <v>4.151368219751241</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.806421523082733</v>
+        <v>3.873156774998165</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.955193108610104</v>
+        <v>2.021899477417605</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.758644764086732</v>
+        <v>2.826270867627173</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.717546617952856</v>
+        <v>2.784873096539883</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.384824954225586</v>
+        <v>3.452495932839518</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.15307821523372</v>
+        <v>4.222078345478678</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.931721404199365</v>
+        <v>4.000999469032088</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5.165534644657335</v>
+        <v>5.2356006509468</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.81422245453107</v>
+        <v>4.883615333142146</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.311043586880572</v>
+        <v>5.380613022663098</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.206060170785292</v>
+        <v>5.275772318841916</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>5.737640746966328</v>
+        <v>5.807121113015462</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.662854889589909</v>
+        <v>4.732137269986637</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>3.173282240844316</v>
+        <v>3.243218862272968</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.359156838198551</v>
+        <v>4.429202553860712</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>6.526676484175944</v>
+        <v>6.596421745838029</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>7.397107384655122</v>
+        <v>7.4669617323624</v>
       </c>
     </row>
     <row r="30">
@@ -5155,158 +5155,158 @@
         <v>248</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.777491497475019</v>
+        <v>2.810765789793848</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.651993402185525</v>
+        <v>3.685666410798866</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.841325196163901</v>
+        <v>5.876679619832387</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.514628657164295</v>
+        <v>3.550822374583198</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.77839113020476</v>
+        <v>6.844064160100437</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.949426710953482</v>
+        <v>5.014901313939752</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.386237998254295</v>
+        <v>5.452630049404242</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.317360772090574</v>
+        <v>6.384096024006006</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.342747804855144</v>
+        <v>4.409454173662645</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.181815619892163</v>
+        <v>5.249441723432604</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.456174887007499</v>
+        <v>5.523501365594527</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.773855177080989</v>
+        <v>4.841526155694922</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.052589765045454</v>
+        <v>4.121589895290413</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.831232954011099</v>
+        <v>3.900511018843822</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.785204940780254</v>
+        <v>4.85527094706972</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>5.380264990401635</v>
+        <v>5.449657869012711</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>5.246171296252712</v>
+        <v>5.315740732035238</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.931510460802592</v>
+        <v>4.001222608859216</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.744407817282791</v>
+        <v>3.813888183331926</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.125</v>
+        <v>3.194282380396729</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.372122171647206</v>
+        <v>1.442058793075859</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>2.909070341811052</v>
+        <v>2.979116057473213</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>3.990297121196406</v>
+        <v>4.060042382858491</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>6.333710620637611</v>
+        <v>6.403564968344888</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.02615</t>
+          <t>X &gt; 0.02616</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>179</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6014957074267713</v>
+        <v>-0.5682214151079421</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.091261738822759</v>
+        <v>4.1249347474361</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.444857364122086</v>
+        <v>5.480211787790573</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.848382486683121</v>
+        <v>5.884576204102025</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.276408791044545</v>
+        <v>8.342081820940223</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.022232621928438</v>
+        <v>9.087707224914709</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.132048054120226</v>
+        <v>7.198440105270173</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.412152626478743</v>
+        <v>7.478887878394175</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.777691037870092</v>
+        <v>5.844397406677594</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.238492498609055</v>
+        <v>7.306118602149496</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.395533329970206</v>
+        <v>6.462859808557234</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.557780208618198</v>
+        <v>5.62545118723213</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.991948208008161</v>
+        <v>5.06094833825312</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.887909832727992</v>
+        <v>5.957187897560715</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>5.787637811567784</v>
+        <v>5.857703817857249</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>5.824038643312072</v>
+        <v>5.893431521923148</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.689944949163149</v>
+        <v>5.759514384945675</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>4.467643097313683</v>
+        <v>4.537355245370307</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.566447824491291</v>
+        <v>3.635928190540426</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.194832402234638</v>
+        <v>3.264114782631367</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.534313557482491</v>
+        <v>1.604250178911144</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.017017719716975</v>
+        <v>2.087063435379136</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.291792886199104</v>
+        <v>2.361538147861189</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.567806854193215</v>
+        <v>5.637661201900492</v>
       </c>
     </row>
     <row r="32">
@@ -5319,76 +5319,76 @@
         <v>141</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4826320440486711</v>
+        <v>-0.4493577517298419</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.72829173208715</v>
+        <v>2.761964740700492</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.253130275093206</v>
+        <v>6.288484698761692</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.539336961900048</v>
+        <v>5.575530679318952</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.010946609500124</v>
+        <v>8.076619639395801</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.779671506194852</v>
+        <v>6.845146109181123</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.006805374140825</v>
+        <v>6.073197425290772</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.437470586778289</v>
+        <v>6.504205838693721</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.932887361020775</v>
+        <v>2.999593729828277</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.705151241031494</v>
+        <v>5.772777344571935</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.979510508146831</v>
+        <v>6.046836986733858</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.700416604671929</v>
+        <v>5.768087583285862</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.99436510249685</v>
+        <v>6.063365232741809</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.773008291462496</v>
+        <v>5.842286356295219</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.823296910581213</v>
+        <v>5.893362916870679</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>5.709137102046576</v>
+        <v>5.778529980657652</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>5.575043407897653</v>
+        <v>5.644612843680179</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>4.051620275490308</v>
+        <v>4.121332423546932</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.558523580266097</v>
+        <v>3.628003946315232</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.036347517730498</v>
+        <v>3.105629898127226</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.783927250576511</v>
+        <v>1.853863872005164</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>2.417192053089934</v>
+        <v>2.487237768752095</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.401187077728096</v>
+        <v>3.470932339390181</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>103</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.6948106330841526</v>
+        <v>0.7280849254029818</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.3596351184398259</v>
+        <v>0.3933081270531673</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.716051159208057</v>
+        <v>5.751405582876544</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.973131632422664</v>
+        <v>6.009325349841568</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.549609420214168</v>
+        <v>7.615282450109845</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.765900246813182</v>
+        <v>6.831374849799452</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.051286541943611</v>
+        <v>4.117678593093558</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.714479469240594</v>
+        <v>5.781214721156026</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.872500388632147</v>
+        <v>1.939206757439649</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.06953876427049</v>
+        <v>2.137164867810931</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.343898031385827</v>
+        <v>2.411224509972854</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.03567791431869</v>
+        <v>3.103348892932623</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.85293426864709</v>
+        <v>3.921934398892049</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.602451244020507</v>
+        <v>4.67172930885323</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4.914393791390971</v>
+        <v>4.984459797680437</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.509453841012352</v>
+        <v>5.578846719623428</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>5.375360146863429</v>
+        <v>5.444929582645955</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>3.328629157952612</v>
+        <v>3.398341306009236</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.544752320884427</v>
+        <v>3.614232686933562</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>2.760922330097081</v>
+        <v>2.83020471049381</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.2759743482835972</v>
+        <v>0.34591096971225</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>1.170893079048753</v>
+        <v>1.240938794710914</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>3.387415818346426</v>
+        <v>3.457161080008511</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>6.22409583830126</v>
+        <v>6.293950186008537</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>82</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.01558482038493736</v>
+        <v>0.01768947193389181</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.8687518600926865</v>
+        <v>0.9024248687060279</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.746124566738253</v>
+        <v>6.78147899040674</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.251843448667046</v>
+        <v>7.28803716608595</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.54511024900886</v>
+        <v>10.61078327890453</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8.293250471771742</v>
+        <v>8.358725074758013</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.300872144595758</v>
+        <v>6.367264195745705</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.461341889321105</v>
+        <v>8.528077141236537</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.84432136897788</v>
+        <v>4.911027737785382</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.070485958208451</v>
+        <v>4.138112061748892</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.344845225323787</v>
+        <v>4.412171703910815</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.285263516970836</v>
+        <v>5.352934495584769</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.599796688727601</v>
+        <v>6.668796818972559</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.378439877693246</v>
+        <v>6.447717942525969</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.158533028899846</v>
+        <v>8.228599035189312</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>9.973105273643164</v>
+        <v>10.04249815225424</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>9.83901157949424</v>
+        <v>9.908581015276766</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>6.075491578033123</v>
+        <v>6.145203726089747</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.291614740964938</v>
+        <v>6.361095107014073</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.039634146341463</v>
+        <v>4.108916526738192</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.276921542221558</v>
+        <v>2.346858163650211</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>3.420478681700899</v>
+        <v>3.49052439736306</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>6.134278238426937</v>
+        <v>6.204023500089022</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>7.27784909428042</v>
+        <v>7.347703441987697</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.05093299995368739</v>
+        <v>-0.01765870763485822</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.512442210039659</v>
+        <v>2.546115218653</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.869843195228881</v>
+        <v>6.905197618897368</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.60532524435456</v>
+        <v>7.641518961773464</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.427220072337299</v>
+        <v>7.49269467532357</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5.205078577964436</v>
+        <v>5.271470629114383</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>9.274350019402391</v>
+        <v>9.341085271317823</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.968039997468509</v>
+        <v>5.034746366276011</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.643479949017916</v>
+        <v>5.711106052558357</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>5.917839216133252</v>
+        <v>5.98516569472028</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>7.088020674977201</v>
+        <v>7.155691653591134</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8.862080181127745</v>
+        <v>8.931080311372703</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>8.64072337009339</v>
+        <v>8.710001434926113</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>10.88034285569376</v>
+        <v>10.95040886198323</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>12.92467826763399</v>
+        <v>12.99407114624506</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>11.34130921116622</v>
+        <v>11.41087864694875</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>6.888499708114409</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>7.104622871046224</v>
+        <v>7.174103237095359</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>4.393115942028977</v>
+        <v>4.462398322425706</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>2.400640170712187</v>
+        <v>2.470576792140839</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>3.773960477388414</v>
+        <v>3.844006193050575</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>8.320620391558613</v>
+        <v>8.39047473926589</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1969 +5824,1969 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.03495</t>
+          <t>X &lt; -0.03491</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.500208362272538</v>
+        <v>-1.466934069953709</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.063166847720822</v>
+        <v>1.096839856334164</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.072741745953522</v>
+        <v>1.108096169622009</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.808223795079208</v>
+        <v>1.844417512498111</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.904872076901356</v>
+        <v>-2.839199047005678</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.16698282621342</v>
+        <v>-4.10150822322715</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-6.389124320586284</v>
+        <v>-6.322732269436337</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.218403603786008</v>
+        <v>-5.151668351870576</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.176887538763374</v>
+        <v>-5.110181169955872</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.052172224895116</v>
+        <v>-2.984546121354676</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.227088320098616</v>
+        <v>-4.159761841511589</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.607631498935845</v>
+        <v>-1.539960520321912</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1664280072146909</v>
+        <v>0.2354281374596496</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.843621920818016</v>
+        <v>2.912899985650739</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-2.163135405175801</v>
+        <v>-2.093069398886335</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.330475369083267</v>
+        <v>1.399868247694343</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-3.151444412022187</v>
+        <v>-3.081874976239661</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-3.256427828117467</v>
+        <v>-3.186715680060843</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-3.040304665185651</v>
+        <v>-2.970824299136517</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.494565217391312</v>
+        <v>1.56384759778804</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.4979105539254931</v>
+        <v>-0.4279739324968403</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-2.023140971886939</v>
+        <v>-1.953095256224778</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-1.748365805404809</v>
+        <v>-1.678620543742724</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.3750317823544407</v>
+        <v>-0.3051774346471632</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.03251</t>
+          <t>X &lt; -0.03247</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>97</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.096801818121925</v>
+        <v>-1.063527525803096</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.6298783373368337</v>
+        <v>0.6635513459501752</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.344817048508432</v>
+        <v>4.380171472176919</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.5382402301606319</v>
+        <v>0.5744339475795357</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.203898280188128</v>
+        <v>1.269571310083805</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.6707927769081721</v>
+        <v>-0.6053181739219013</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.443658908962199</v>
+        <v>-1.377266857812252</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.6912857194292172</v>
+        <v>-0.6245504675137852</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3811581806449595</v>
+        <v>0.4478645494524613</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.6382506049270873</v>
+        <v>0.7058767084675281</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.9126098720424238</v>
+        <v>0.9799363506294512</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.726299473722158</v>
+        <v>3.79397045233609</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.694591760389649</v>
+        <v>5.763591890634608</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.504162784406837</v>
+        <v>6.57344084923956</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>3.783375875266444</v>
+        <v>3.853441881555909</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>4.378435924887825</v>
+        <v>4.447828803498901</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.151558725584266</v>
+        <v>1.221128161366792</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.01564747443744352</v>
+        <v>0.08535962249406737</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2317706373692587</v>
+        <v>0.3012510034183933</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>3.511597938144327</v>
+        <v>3.580880318541055</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.968397529146372</v>
+        <v>3.038334150575025</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.861514638452221</v>
+        <v>1.931560354114382</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3.167217639985893</v>
+        <v>3.236962901647978</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>5.153131970820517</v>
+        <v>5.222986318527795</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.03006</t>
+          <t>X &lt; -0.03003</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>122</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.641601080547538</v>
+        <v>-2.027943887625518</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.730608395804957</v>
+        <v>-0.7498174601688845</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2887075335515235</v>
+        <v>0.683918014796987</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.06443004193671</v>
+        <v>-1.655052264808361</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8489886976294017</v>
+        <v>0.4481816528882661</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.42286308280643</v>
+        <v>-1.357388479820159</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.376057083712922</v>
+        <v>-1.309665032562975</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.474283860379018</v>
+        <v>-2.407548608463586</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.613095664208849</v>
+        <v>-1.546389295401347</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.567258943830737</v>
+        <v>-1.499632840290296</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.166116716727224</v>
+        <v>1.233443195314251</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.165711337842488</v>
+        <v>4.233382316456421</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.778925037388127</v>
+        <v>8.847925167633086</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.737896095206231</v>
+        <v>7.807174160038954</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.439620593873848</v>
+        <v>5.509686600163313</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>5.215008512347701</v>
+        <v>5.284401390958777</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>4.261242687051237</v>
+        <v>4.330812122833763</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.697242877513325</v>
+        <v>1.766955025569949</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.372382433887772</v>
+        <v>4.441862799936906</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>6.198770491803273</v>
+        <v>6.268052872200002</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>5.655570082805319</v>
+        <v>5.725506704233972</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>3.940270764867641</v>
+        <v>4.010316480529802</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.034718062497312</v>
+        <v>5.104463324159397</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.598120985523913</v>
+        <v>6.66797533323119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02762</t>
+          <t>X &lt; -0.02759</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>162</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.980869872008462</v>
+        <v>-4.250603210992942</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.9228771673086982</v>
+        <v>-0.9268434239768979</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.5107257795429874</v>
+        <v>-0.1989190344324001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.6273327591157027</v>
+        <v>0.9286177436708698</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.113914825943517</v>
+        <v>1.819821136154268</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.4492275870984415</v>
+        <v>0.5147021900847122</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2936454056616995</v>
+        <v>0.3600374568116465</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.6021931904741464</v>
+        <v>-0.5354579385587144</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.5606771254515124</v>
+        <v>-0.4939707566440106</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.569080437455504</v>
+        <v>-2.501454333915063</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.060153269105605</v>
+        <v>-0.9928267905185777</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.129888629888626</v>
+        <v>1.197559608502559</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.560952966957039</v>
+        <v>5.629953097201998</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.487744304070837</v>
+        <v>3.55702236890356</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>3.446097015650828</v>
+        <v>3.516163021940294</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.189305213420347</v>
+        <v>2.258698092031423</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>2.055211519271424</v>
+        <v>2.12478095505395</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.5189076992929955</v>
+        <v>-0.4491955512363717</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.9317833648733966</v>
+        <v>1.001263730922531</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.353395061728392</v>
+        <v>2.422677442125121</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.044762553965008</v>
+        <v>3.11469917539366</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2.968807498322398</v>
+        <v>3.038853213984559</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>3.86086661542182</v>
+        <v>3.930611877083905</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.40220922677063</v>
+        <v>4.472063574477907</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.02517</t>
+          <t>X &lt; -0.02514</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>212</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.500412485563011</v>
+        <v>-2.943172694827311</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.650806354357378</v>
+        <v>-1.639175313650945</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.20371436561333</v>
+        <v>-0.9535490640991569</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.0307152259763015</v>
+        <v>0.2114311887585743</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.019109328622292</v>
+        <v>0.8146078523615401</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2088203979935628</v>
+        <v>-0.1433457950072921</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4334078095750513</v>
+        <v>0.4997998607249983</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.3168449491510543</v>
+        <v>-0.2501096972356223</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.218725110543517</v>
+        <v>-1.152018741736015</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.464258634520498</v>
+        <v>-2.396632530980057</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.661597480612699</v>
+        <v>-2.594271002025671</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3611954083652194</v>
+        <v>0.428866386979152</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.538590982330909</v>
+        <v>2.607591112575868</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.373837944881465</v>
+        <v>1.443116009714188</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.7149067058441645</v>
+        <v>0.7849727121336301</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.3665705290504491</v>
+        <v>0.4359634076615251</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.7109193915135705</v>
+        <v>-0.6413499557310445</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.230997147231491</v>
+        <v>-2.161284999174867</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.287012808153158</v>
+        <v>1.356493174202292</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.945754716981128</v>
+        <v>2.015037097377856</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>1.874252421190725</v>
+        <v>1.944189042619378</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.269995478755661</v>
+        <v>2.340041194417822</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>3.488166871652886</v>
+        <v>3.557912133314971</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.412225532384419</v>
+        <v>3.482079880091696</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.02273</t>
+          <t>X &lt; -0.0227</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>265</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.170362007254553</v>
+        <v>-2.52973600232086</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.179108241149841</v>
+        <v>-1.559267034458358</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.732016252405792</v>
+        <v>-0.9360310205142639</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.573058358929352</v>
+        <v>1.55130564146733</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.07571310220719596</v>
+        <v>-0.07141000919376239</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2628777152139818</v>
+        <v>0.3283523182002526</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6220870548580635</v>
+        <v>0.6884791060080104</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.03382608122652897</v>
+        <v>0.03290917068890309</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.124385487902011</v>
+        <v>-1.057679119094509</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.520862408105401</v>
+        <v>-1.45323630456496</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.510654084386289</v>
+        <v>-3.443327605799261</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.01616308220081919</v>
+        <v>0.05150789641311349</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.7461381521422297</v>
+        <v>0.8151382823871884</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2299356400242019</v>
+        <v>-0.1606575751914789</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.8888668790615029</v>
+        <v>-0.8188008727720373</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.2938068294401219</v>
+        <v>-0.2244139508290459</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.182617504721122</v>
+        <v>-1.113048068938596</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.042317901948479</v>
+        <v>-1.972605753891855</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.8153146949456058</v>
+        <v>0.8847950609947404</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.757075471698109</v>
+        <v>1.826357852094837</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>1.968592043832231</v>
+        <v>2.038528665260884</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.269995478755661</v>
+        <v>2.340041194417822</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.299487626369867</v>
+        <v>3.369232888031952</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.600904777667438</v>
+        <v>3.670759125374715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.02029</t>
+          <t>X &lt; -0.02026</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>333</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.629345286347807</v>
+        <v>-2.903383986588302</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-4.27148189994746</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.196745132229012</v>
+        <v>-3.484859578023453</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.508136043019761</v>
+        <v>-1.662311265969805</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.474006428644408</v>
+        <v>-2.731044169220695</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.7853403141361213</v>
+        <v>-0.8861997098191807</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5438956559119532</v>
+        <v>0.6102877070619002</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.9358601908078086</v>
+        <v>-0.8691249388923765</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.795245026686075</v>
+        <v>-1.728538657878573</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.869380737755812</v>
+        <v>-2.801754634215371</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.495922371541376</v>
+        <v>-3.428595892954348</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.072313572313568</v>
+        <v>-1.004642593699636</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3950029889989182</v>
+        <v>-0.3260028587539594</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.9166601003335657</v>
+        <v>-0.8473820355008428</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.575591339370867</v>
+        <v>-1.505525333081401</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.782333091551287</v>
+        <v>-2.712940212940211</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.315826185099617</v>
+        <v>-2.246256749317091</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.420809601194897</v>
+        <v>-2.351097453138273</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4028846364612733</v>
+        <v>-0.3334042704121387</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.9853603603603673</v>
+        <v>1.054642740757096</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>1.343060852263299</v>
+        <v>1.412997473691952</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>2.468306997821898</v>
+        <v>2.538352713484059</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>3.643983065204935</v>
+        <v>3.71372832686702</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.86834202623676</v>
+        <v>3.938196373944038</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01784</t>
+          <t>X &lt; -0.01781</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.292442016437825</v>
+        <v>-3.389590832024936</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.774603042844099</v>
+        <v>-4.857236002461882</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.530838816706321</v>
+        <v>-3.645966193136012</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.942841848569557</v>
+        <v>-1.949381790382098</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.331129536406898</v>
+        <v>-3.416702173614972</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.353683593476845</v>
+        <v>-1.313589205636703</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.103531822717578</v>
+        <v>-0.9249209710039281</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.405104371049433</v>
+        <v>-2.223540579022313</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.386606208840099</v>
+        <v>-3.202461560372903</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.160441619609529</v>
+        <v>-3.975377236409393</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.886082352494192</v>
+        <v>-3.70131759424747</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.863385974639165</v>
+        <v>-1.684148630348524</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.709104814609688</v>
+        <v>-1.531800493123015</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.674707149940723</v>
+        <v>-1.49777732875328</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.589392864681344</v>
+        <v>-2.411022667150164</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-3.78461414498323</v>
+        <v>-3.602350030921457</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-3.918707839132153</v>
+        <v>-3.73626716789893</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.624320804706095</v>
+        <v>-3.586005830903794</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.721426829039451</v>
+        <v>-2.09460424589782</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.5061053984575778</v>
+        <v>-0.8873502726644986</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.493110644986622</v>
+        <v>0.1007158042674376</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.70250263304581</v>
+        <v>1.456964419819556</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.491416617008667</v>
+        <v>2.401647014785702</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>3.443752912701633</v>
+        <v>3.351455787203449</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.0154</t>
+          <t>X &lt; -0.01537</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>466</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.081764717852707</v>
+        <v>-2.272426060800392</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.796530962948317</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.276289495355456</v>
+        <v>-4.462268753624613</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.071106262706408</v>
+        <v>-3.160495285340254</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.289254512549213</v>
+        <v>-4.445402314798542</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.822772202314276</v>
+        <v>-2.871165947556463</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.955979485754234</v>
+        <v>-2.889587434604287</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.087412596091561</v>
+        <v>-4.020677344176129</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.045896531068927</v>
+        <v>-3.979190162261425</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.753633860814894</v>
+        <v>-3.686007757274453</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.758592290927716</v>
+        <v>-4.691265812340689</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.265831183741632</v>
+        <v>-2.198160205127699</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.111004705000632</v>
+        <v>-2.042004574755673</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.479483051216221</v>
+        <v>-1.410204986383498</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.498755441639446</v>
+        <v>-1.42868943534998</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-3.249111170269664</v>
+        <v>-3.179718291658588</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-3.596424480623277</v>
+        <v>-3.526855044840751</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.795260975646265</v>
+        <v>-3.84491536486663</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.746197971209291</v>
+        <v>-1.92326705430478</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.7913090128755442</v>
+        <v>-1.096762395722671</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2615480484829362</v>
+        <v>-0.5732104826652531</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.1229108294474273</v>
+        <v>-0.3087251335937893</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.010233435747139</v>
+        <v>0.9499366979790267</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.651030293903567</v>
+        <v>2.720884641610844</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.01295</t>
+          <t>X &lt; -0.01293</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.477284850390511</v>
+        <v>-1.814760156910225</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.185353258423291</v>
+        <v>-4.498271995405474</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.949879218696431</v>
+        <v>-4.104742437252561</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.252737787621513</v>
+        <v>-3.154569008227547</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.323474944779598</v>
+        <v>-4.27324559641049</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.725375587504729</v>
+        <v>-2.59121074038962</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.674608562592262</v>
+        <v>-3.444557999804893</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.129530051144343</v>
+        <v>-3.89851636898679</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.088013986121709</v>
+        <v>-3.857029187072087</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.98001518172358</v>
+        <v>-3.751210240964475</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.058389600675262</v>
+        <v>-3.828644447660189</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.397448230781563</v>
+        <v>-2.174177682391147</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.934637861967119</v>
+        <v>-1.715617429387862</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.979627829967967</v>
+        <v>-1.760949381405631</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.75672485383771</v>
+        <v>-1.540358056842067</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-3.101700077584944</v>
+        <v>-2.879187303616121</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.883060085666848</v>
+        <v>-2.66161059173595</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.887707594594644</v>
+        <v>-2.766451295557133</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.86292875137265</v>
+        <v>-1.847572216917527</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.396276595744681</v>
+        <v>-1.484979482520664</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.052952182047605</v>
+        <v>-1.148791028342593</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.9516022731511953</v>
+        <v>-0.945236509541779</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.3943358931850725</v>
+        <v>-0.3903757772370966</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.7730620215429056</v>
+        <v>0.8752394240612915</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.01051</t>
+          <t>X &lt; -0.01049</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.507700198092472</v>
+        <v>-0.5796226236360482</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-4.048616612511708</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.750326778868263</v>
+        <v>-3.805455826309846</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.248462780392295</v>
+        <v>-2.246655545409247</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.090837439862419</v>
+        <v>-4.116346397084314</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.86969941474338</v>
+        <v>-2.824613630875739</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.642565546797407</v>
+        <v>-3.517958185889874</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.773409704871355</v>
+        <v>-3.502051983584131</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.731893639848721</v>
+        <v>-3.460564801669427</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.619466125950495</v>
+        <v>-3.49818636005886</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.788238321168997</v>
+        <v>-3.518244364955763</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.033358812531631</v>
+        <v>-2.914640827227281</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.351350769571212</v>
+        <v>-1.096626423495159</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.277286605716355</v>
+        <v>-1.023587652882931</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.197665407530607</v>
+        <v>-1.24055447987525</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.375131207244529</v>
+        <v>-2.410873440285208</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.832946856066435</v>
+        <v>-2.103614106674449</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.111500291885584</v>
+        <v>-1.17904304578974</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.2148627867183635</v>
+        <v>-0.5219751942771822</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.2089524517087682</v>
+        <v>-0.04101173725032936</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.03707113708116339</v>
+        <v>-0.2017247595869733</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.8559682432438294</v>
+        <v>-0.9270596014857801</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1955707743489086</v>
+        <v>-0.2700190837637066</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.3237259816207114</v>
+        <v>0.3337043079135071</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.008065</t>
+          <t>X &lt; -0.008043</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.392987003777925</v>
+        <v>-1.440358115876947</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.651272229037097</v>
+        <v>-2.56803517249169</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.049739040847143</v>
+        <v>-1.982270411793166</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.280219622272689</v>
+        <v>-1.157271826881278</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.263536378866576</v>
+        <v>-2.162633153048489</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.840277822720104</v>
+        <v>-0.6788653011457484</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.489534560460172</v>
+        <v>-1.505498029413495</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.644479811664759</v>
+        <v>-1.660556764806962</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.850182535270058</v>
+        <v>-1.865375001611469</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.253189763097595</v>
+        <v>-2.26883254956914</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.34965867892415</v>
+        <v>-2.364231035486036</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.010705610829213</v>
+        <v>-2.027216892136011</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6630089430370063</v>
+        <v>-0.6873247718000002</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5135375711294543</v>
+        <v>-0.4157928108081705</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.4308124442829495</v>
+        <v>-0.335019852231099</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.071846337801247</v>
+        <v>-0.8490073145245631</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.6385300771104383</v>
+        <v>-0.6134663234232107</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.1746973179078921</v>
+        <v>-0.2256961898059657</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.363514517034659</v>
+        <v>0.3596533191971716</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.8734472049689472</v>
+        <v>0.7928045478844155</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.5295607850318902</v>
+        <v>0.4476671618758274</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.03075113560849729</v>
+        <v>-0.04756653910185804</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.5050586045847041</v>
+        <v>0.3009212057780601</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.3794598856692275</v>
+        <v>0.05176043305264955</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.005621</t>
+          <t>X &lt; -0.0056</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.9022663950898107</v>
+        <v>-0.93671137642243</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.461804924664072</v>
+        <v>-2.489424336410231</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.350706786190663</v>
+        <v>-2.384950080897788</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.248260783144495</v>
+        <v>-1.339362937702326</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.3613938160318</v>
+        <v>-2.468777229160615</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.067391596187406</v>
+        <v>-2.117638750713937</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.306069694053392</v>
+        <v>-2.298170377490102</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.798299553247176</v>
+        <v>-2.789828994068152</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.59144229347158</v>
+        <v>-2.641618226240958</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.830518345952235</v>
+        <v>-2.880915972715023</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.770062822152411</v>
+        <v>-2.820303502378067</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.728301110654051</v>
+        <v>-2.778882148088606</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.285947409355096</v>
+        <v>-1.278878811629902</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.9725448621006763</v>
+        <v>-0.9657696538884579</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.8828129995337051</v>
+        <v>-0.8760497036057728</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.187912118115328</v>
+        <v>-1.243201243201241</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.7235586764333917</v>
+        <v>-0.8429303459906805</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.2288107353762854</v>
+        <v>-0.4135830156238285</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.2660979874085641</v>
+        <v>0.01598357897570679</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.5174731182795682</v>
+        <v>0.2664748937657109</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.3616704198502703</v>
+        <v>0.1089096599681696</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.242913500876675</v>
+        <v>-0.009854657874441841</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.1724547318153853</v>
+        <v>-0.3148710879984904</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1840905359150256</v>
+        <v>-0.3269710491181215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003177</t>
+          <t>X &lt; -0.003157</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.247778251504691</v>
+        <v>-1.227054009983689</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.364023720048202</v>
+        <v>-1.430326241376257</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.803164051147924</v>
+        <v>-1.873055741469081</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.688420584729151</v>
+        <v>-1.76186059304721</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.441103960959339</v>
+        <v>-2.569653888788949</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.340895869691678</v>
+        <v>-2.422607413891555</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.592022871310917</v>
+        <v>-2.62795920536179</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.261881864655571</v>
+        <v>-2.16513039795074</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.607545577890022</v>
+        <v>-2.509788657878573</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.162930161853538</v>
+        <v>-2.067426556137285</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.801538692823492</v>
+        <v>-1.706561358419812</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.471407182895426</v>
+        <v>-1.377671872978915</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.1589967477707361</v>
+        <v>-0.01891905905502966</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3803535588050906</v>
+        <v>-0.23999793550162</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.02962028120469284</v>
+        <v>-0.02933150241319282</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.6899180959104925</v>
+        <v>-0.6512782034067897</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.3363598077274759</v>
+        <v>-0.3507904750497701</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.2148481812596756</v>
+        <v>-0.368750205804055</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.2281659945893608</v>
+        <v>0.1596104834721856</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.4675196850393775</v>
+        <v>0.398372893886723</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.5896805016850521</v>
+        <v>0.517589870967285</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.4791135975855596</v>
+        <v>0.4071892919980584</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.1051811053503329</v>
+        <v>0.03622883784919395</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.520745087770635</v>
+        <v>0.4492051993633481</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0007324</t>
+          <t>X &lt; -0.0007145</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.188741288791725</v>
+        <v>-1.239100388541139</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.7539933359035373</v>
+        <v>-0.7345459802449952</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.276230180967353</v>
+        <v>-1.332010307751545</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.510776045659767</v>
+        <v>-1.567880714755873</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.495802418182336</v>
+        <v>-2.593774314116658</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.162010239193151</v>
+        <v>-2.148321193659385</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.714935022273572</v>
+        <v>-2.661405038315053</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.660108283361112</v>
+        <v>-2.607220020074507</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.09235711674971</v>
+        <v>-3.03812056775331</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.38547361240856</v>
+        <v>-3.371797590788333</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.96416357380167</v>
+        <v>-2.95132506429259</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.581979005564605</v>
+        <v>-2.530564119621161</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.428733265932713</v>
+        <v>-1.340286937554154</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.166395129480357</v>
+        <v>-1.078721225020516</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.046585512351797</v>
+        <v>-1.00318880726725</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.218029465391986</v>
+        <v>-1.215845172191464</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.235453255058296</v>
+        <v>-1.276394737635556</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.592326250587647</v>
+        <v>-1.632096513873016</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.8166563417458903</v>
+        <v>-0.8592056044427139</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.029357459379618</v>
+        <v>-1.070423501956206</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.15988555312213</v>
+        <v>-1.202200505744436</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.192380316711571</v>
+        <v>-1.234860853543935</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.392215235242084</v>
+        <v>-1.432980651824273</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.27680311890839</v>
+        <v>-1.318387643701925</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001712</t>
+          <t>X &lt; 0.001728</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.334757712675312</v>
+        <v>-1.36953410783147</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.01304223874719</v>
+        <v>-1.049098382516526</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.107960532513744</v>
+        <v>-1.145730188227105</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.037790697674417</v>
+        <v>-1.076721668534816</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.618742158745995</v>
+        <v>-1.690085518928797</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.369038458809882</v>
+        <v>-1.406507409027505</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.891748243146587</v>
+        <v>-1.89434059394366</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.323480602207944</v>
+        <v>-2.325581395348827</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.372716674915395</v>
+        <v>-2.374775889481661</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.924134739878234</v>
+        <v>-2.960074304730163</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.46180554795086</v>
+        <v>-2.498397401780238</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.706173137207614</v>
+        <v>-2.742550714586478</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.012482537512938</v>
+        <v>-2.015168542910246</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.260664079218344</v>
+        <v>-2.263083451202263</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.81651022435755</v>
+        <v>-1.856063841514654</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.001401406096988</v>
+        <v>-2.040229885057471</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.099330619766839</v>
+        <v>-2.174147022034944</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.356783310753507</v>
+        <v>-2.431164973607288</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.789860032247248</v>
+        <v>-1.865444785503499</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.070214105793454</v>
+        <v>-2.144913599502772</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.262245777617998</v>
+        <v>-2.337264416104816</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.23879606993691</v>
+        <v>-2.314046855896642</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.495405534751498</v>
+        <v>-2.569710555690818</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.345826687931954</v>
+        <v>-2.420681395513078</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.004156</t>
+          <t>X &lt; 0.004171</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5922935630302888</v>
+        <v>-0.6217793168218009</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3676169629256876</v>
+        <v>-0.3455232228575582</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.08729525682169</v>
+        <v>-1.065816873856257</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.346398999962865</v>
+        <v>-1.325535972297949</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.788976350643082</v>
+        <v>-1.791474501635058</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.814804282897214</v>
+        <v>-1.787901351676204</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.079132273455883</v>
+        <v>-2.052683446876308</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.648180186709894</v>
+        <v>-2.620637216720446</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.630800582241633</v>
+        <v>-2.603243149604346</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.788456697386728</v>
+        <v>-2.791052442662107</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.727544602096366</v>
+        <v>-2.700459560773304</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.763647191036405</v>
+        <v>-2.7368860192338</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.523092617088544</v>
+        <v>-2.498660332423682</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.553786269795388</v>
+        <v>-2.529607971458127</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.380139202742264</v>
+        <v>-2.388177708271087</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.396232705450906</v>
+        <v>-2.403030303030306</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.285603242671101</v>
+        <v>-2.293048471669103</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.574096256891835</v>
+        <v>-2.580852034200909</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-2.059364267217433</v>
+        <v>-2.067349754357629</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-2.377680965147455</v>
+        <v>-2.384285230506535</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.675711138611689</v>
+        <v>-2.682488386499784</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.828293950952961</v>
+        <v>-2.834757154007825</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.898757312121916</v>
+        <v>-2.904453023648387</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.782962690624103</v>
+        <v>-2.789205907823536</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0066</t>
+          <t>X &lt; 0.006614</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2131</v>
+        <v>2136</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7930805135574843</v>
+        <v>-0.8360256020735974</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4528115647465896</v>
+        <v>-0.4969597188318744</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.65829971006265</v>
+        <v>-0.7036661626689167</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6485980499312873</v>
+        <v>-0.6948421056037049</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.267352847689153</v>
+        <v>-1.330014020382905</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.359517843620921</v>
+        <v>-1.396239110571578</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.9889366640652213</v>
+        <v>-1.0269143485502</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.753919629556904</v>
+        <v>-1.744186046511622</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.639844871285923</v>
+        <v>-1.630301751824078</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.921277784055839</v>
+        <v>-1.937884714970856</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.206620009477817</v>
+        <v>-2.196358068537741</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.133103713831666</v>
+        <v>-2.12318078722619</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.251060727409595</v>
+        <v>-2.241711671014485</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.165550279630104</v>
+        <v>-2.15652334464216</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.050037748396718</v>
+        <v>-2.068745896301969</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.988832718808276</v>
+        <v>-2.007010402532792</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.862145188855472</v>
+        <v>-1.880795627906366</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.127254464401574</v>
+        <v>-2.145429600411596</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.024590612099828</v>
+        <v>-2.042773611729167</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.81059718969555</v>
+        <v>-1.829082105584575</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.279962358388772</v>
+        <v>-2.344757476208848</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.516424569188146</v>
+        <v>-2.580798242897949</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.777541649002714</v>
+        <v>-2.794230263450025</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.592130647281429</v>
+        <v>-2.65617890020652</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.009044</t>
+          <t>X &lt; 0.009057</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2422</v>
+        <v>2427</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7088862319266624</v>
+        <v>-0.7020716032278855</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4904753164671334</v>
+        <v>-0.4844030052893373</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4346707369167859</v>
+        <v>-0.4299828300938131</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8392853741690871</v>
+        <v>-0.8344024563486911</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.304791330711581</v>
+        <v>-1.311120077496163</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.463846689363812</v>
+        <v>-1.469695295335264</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.066201526140951</v>
+        <v>-1.073556529973828</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.526853152596509</v>
+        <v>-1.53352245142743</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.298276987658127</v>
+        <v>-1.346338275678193</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.638593300071818</v>
+        <v>-1.686669864890533</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.792781859365945</v>
+        <v>-1.799343689931646</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.637998402583442</v>
+        <v>-1.686135895119136</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.588428226813789</v>
+        <v>-1.637691906292055</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.457126553628974</v>
+        <v>-1.506884377399572</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.434026491923667</v>
+        <v>-1.484445139587415</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.596703017032326</v>
+        <v>-1.646288345466992</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.542265469175774</v>
+        <v>-1.592110409057348</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.582120830051423</v>
+        <v>-1.632005981888959</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.671644125245486</v>
+        <v>-1.721181850623928</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.41951772464963</v>
+        <v>-1.469436253910139</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.402736491472176</v>
+        <v>-1.453202059174245</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.660822131307228</v>
+        <v>-1.71085326482855</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.939768246982204</v>
+        <v>-1.989009006842309</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.785412471448367</v>
+        <v>-1.835067619344677</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.01149</t>
+          <t>X &lt; 0.0115</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2647</v>
+        <v>2651</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4531476229792659</v>
+        <v>-0.4620886990714652</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2813089099042969</v>
+        <v>-0.2906257823392053</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.1266585538965543</v>
+        <v>-0.1366968530283401</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1072976343073364</v>
+        <v>-0.1176115815284362</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5265601076046948</v>
+        <v>-0.5447844565481077</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5810459635003085</v>
+        <v>-0.5991380145510377</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.2068550948388008</v>
+        <v>-0.2257807451984561</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6893500682180758</v>
+        <v>-0.7076586356937895</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8143618143979126</v>
+        <v>-0.8324813102083155</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.266312054642022</v>
+        <v>-1.284026775024088</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.158547402587452</v>
+        <v>-1.176343640702093</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.077847500374766</v>
+        <v>-1.095871637238098</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.014584195487565</v>
+        <v>-1.033096127830689</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8376574996900104</v>
+        <v>-0.8565230818459497</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.9097523075679845</v>
+        <v>-0.9287455457752998</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.121010752262848</v>
+        <v>-1.139497646643193</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.195414137784773</v>
+        <v>-1.213847364763232</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.240662246905053</v>
+        <v>-1.259075811624719</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.341832634232794</v>
+        <v>-1.360033309089367</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.359156921916259</v>
+        <v>-1.377280708115514</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.20121927692248</v>
+        <v>-1.219778482369605</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.368258899899153</v>
+        <v>-1.386605037331208</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.67557365163276</v>
+        <v>-1.693375609648683</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.351800670294303</v>
+        <v>-1.370129681269979</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.01393</t>
+          <t>X &lt; 0.01394</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2786</v>
+        <v>2792</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4523342928992449</v>
+        <v>-0.4614510210696281</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3055932166914133</v>
+        <v>-0.3153538336012502</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.229902265136765</v>
+        <v>-0.2412291677093279</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2112582671683612</v>
+        <v>-0.2233252875101286</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6635328534649574</v>
+        <v>-0.6815265492097566</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8487418040711319</v>
+        <v>-0.8661685976662667</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.4958526189415622</v>
+        <v>-0.5147960808912444</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.7898898092913953</v>
+        <v>-0.8084873782548172</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.9066734847764408</v>
+        <v>-0.9249919690451023</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.053207421582492</v>
+        <v>-1.07197781534375</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.294363899886434</v>
+        <v>-1.312362012014582</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.124367055389207</v>
+        <v>-1.143012061598348</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.084394561479506</v>
+        <v>-1.104233818932833</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8557622926546458</v>
+        <v>-0.8763188952728171</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.9928261054428376</v>
+        <v>-1.013744727055887</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.05662742883775</v>
+        <v>-1.076839826839823</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.169782181912751</v>
+        <v>-1.189894921251081</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.146361800959127</v>
+        <v>-1.166639227936649</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.195866798128499</v>
+        <v>-1.21583836700426</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.05958781362007</v>
+        <v>-1.079680423608998</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.9723416782700909</v>
+        <v>-0.993165397587191</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.206494058614737</v>
+        <v>-1.22690144547088</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.377076745951761</v>
+        <v>-1.39686024236817</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.216714315100987</v>
+        <v>-1.236928607771205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01638</t>
+          <t>X &lt; 0.01639</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2897</v>
+        <v>2902</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2837104468466833</v>
+        <v>-0.3075137800986312</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2580122338586435</v>
+        <v>-0.282053460345395</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.171409995858923</v>
+        <v>-0.1964004017980585</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1806172317848009</v>
+        <v>-0.1717715182431903</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6295693990221949</v>
+        <v>-0.6253453439359546</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7319764871873957</v>
+        <v>-0.727476061225957</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4905636489660239</v>
+        <v>-0.4869040376118576</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6810224488433931</v>
+        <v>-0.7114621355818755</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.6887126701537198</v>
+        <v>-0.719130209320312</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.8590915065802847</v>
+        <v>-0.8896573517477151</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.149245798060676</v>
+        <v>-1.179176662403037</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.133839519023432</v>
+        <v>-1.163964578690802</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.207094310031088</v>
+        <v>-1.237728178306249</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.064485944753834</v>
+        <v>-1.09550103361984</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.118320579278354</v>
+        <v>-1.115269051378881</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.122566612507704</v>
+        <v>-1.119181505779437</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.133238638875703</v>
+        <v>-1.129911803477469</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.114715356760996</v>
+        <v>-1.111480945296172</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.257426290451576</v>
+        <v>-1.253829339444025</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.153697001034125</v>
+        <v>-1.150177358075396</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.9871659262393422</v>
+        <v>-0.9842362488429615</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.249760845806478</v>
+        <v>-1.246423798565175</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.403300242947942</v>
+        <v>-1.399548918687188</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.321037895625032</v>
+        <v>-1.317472803158637</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01882</t>
+          <t>X &lt; 0.01883</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3009</v>
+        <v>3014</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3759683714500071</v>
+        <v>-0.36458764685311</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4296202460302254</v>
+        <v>-0.451249735233695</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.432495734316241</v>
+        <v>-0.4548291222625238</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.368799281365412</v>
+        <v>-0.3915936842766143</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6826179463708613</v>
+        <v>-0.6760373044348285</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7082562925525906</v>
+        <v>-0.7015426387370667</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6035174544886033</v>
+        <v>-0.5973534543898893</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6319860687518712</v>
+        <v>-0.6259114283521328</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5386312700723153</v>
+        <v>-0.5326911100996981</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7313180968813882</v>
+        <v>-0.7254378947546414</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.8350550184172363</v>
+        <v>-0.828870300166308</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8635646048754211</v>
+        <v>-0.8574696441473151</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9094909869306207</v>
+        <v>-0.9038699820756193</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8796572147053112</v>
+        <v>-0.8741945623133702</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.9558861471010616</v>
+        <v>-0.9506204447329125</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.9378303189742709</v>
+        <v>-0.9323045143693705</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.8203983965683719</v>
+        <v>-0.8151334711232963</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.8395268258822668</v>
+        <v>-0.834282625065164</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.9688122096881173</v>
+        <v>-0.9632490870737769</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.8618901427149055</v>
+        <v>-0.8564134446529721</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.754853795452135</v>
+        <v>-0.7498216264821309</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.877582897387164</v>
+        <v>-0.8723856110473633</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.081506544005606</v>
+        <v>-1.075837358221065</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.038259490534244</v>
+        <v>-1.032700202791958</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.02126</t>
+          <t>X &lt; 0.02127</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3091</v>
+        <v>3095</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3664785027321713</v>
+        <v>-0.3695193392177245</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5239130463186683</v>
+        <v>-0.5267949095360365</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7253469988771428</v>
+        <v>-0.7281487374494873</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5858058053568342</v>
+        <v>-0.5888762739954814</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7081247913801434</v>
+        <v>-0.7141536698869189</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5673352392638904</v>
+        <v>-0.5735259888383979</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5822304702141707</v>
+        <v>-0.5885010559942145</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5529217325555464</v>
+        <v>-0.5592683127387374</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3643227973092422</v>
+        <v>-0.3709109336913698</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.4434765727212095</v>
+        <v>-0.450062317904198</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4404829114627375</v>
+        <v>-0.4470429114013683</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5077141678817441</v>
+        <v>-0.5142262037016536</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.5820372185863292</v>
+        <v>-0.5885964246314828</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5587401035873825</v>
+        <v>-0.5653608839144795</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6825369947036251</v>
+        <v>-0.6890838916399602</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.649125343629116</v>
+        <v>-0.655646051230967</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.6996522319340457</v>
+        <v>-0.706128613444271</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6887255636539606</v>
+        <v>-0.6952332690573826</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.7442143382560857</v>
+        <v>-0.7506279457003302</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.6350969305331162</v>
+        <v>-0.6416324308326935</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.4805792066708676</v>
+        <v>-0.4873858017720138</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.6019795836189061</v>
+        <v>-0.6086431684165632</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.825460505144207</v>
+        <v>-0.831805579132002</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.9147004792256723</v>
+        <v>-0.9209438648407868</v>
       </c>
     </row>
     <row r="30">
@@ -7796,161 +7796,161 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3160</v>
+        <v>3164</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2653875069132141</v>
+        <v>-0.2677689835292369</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3952177249205846</v>
+        <v>-0.3974694861697259</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.592034165367771</v>
+        <v>-0.5941767127751021</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4395202574228492</v>
+        <v>-0.4419236134213449</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.6928921907827714</v>
+        <v>-0.6973858819576719</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5510909609440375</v>
+        <v>-0.5557481051717872</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5824431474806744</v>
+        <v>-0.5871373193477254</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6542813827806455</v>
+        <v>-0.6589147286821699</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5004068814542251</v>
+        <v>-0.5052329363029529</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.5631993200432035</v>
+        <v>-0.5680231053296509</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5858581945373871</v>
+        <v>-0.5906304487566061</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5316404906568835</v>
+        <v>-0.5365107338801138</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.4711434624903745</v>
+        <v>-0.4762003002899746</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4531366399646757</v>
+        <v>-0.4582405310474229</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.5254405258877668</v>
+        <v>-0.5305194415926877</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.5744433836615812</v>
+        <v>-0.5794069318659538</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.5636161285005485</v>
+        <v>-0.5686093763054743</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4604158530563538</v>
+        <v>-0.4655526022937266</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4467199409600795</v>
+        <v>-0.4518565819853109</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.399020227560051</v>
+        <v>-0.4042024680881227</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2596484014102245</v>
+        <v>-0.2650620193343727</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.3799872166962217</v>
+        <v>-0.3852594647080281</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.4659794756339153</v>
+        <v>-0.4711200285974613</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6497520171737321</v>
+        <v>-0.6546708295426384</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.02615</t>
+          <t>X &lt; 0.02616</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3229</v>
+        <v>3233</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.01483481288486388</v>
+        <v>-0.01676848935334618</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3335048564148124</v>
+        <v>-0.3350709163900731</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4336127690966478</v>
+        <v>-0.4351549460617008</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4841203375636098</v>
+        <v>-0.4856501619339681</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6167304334373753</v>
+        <v>-0.6198290272185289</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6587277144714747</v>
+        <v>-0.6617639305011593</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5518396357567923</v>
+        <v>-0.5550622582880607</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5664306688359204</v>
+        <v>-0.5696564953796113</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4765712357558129</v>
+        <v>-0.4799070213159027</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.5544848983456276</v>
+        <v>-0.5577798309550701</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5091292860437804</v>
+        <v>-0.5124634943820254</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4619840202993544</v>
+        <v>-0.4653976476750259</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4267013540306124</v>
+        <v>-0.4302377965277273</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4755273961567141</v>
+        <v>-0.4790210750954742</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.4676891196712489</v>
+        <v>-0.4712399681359472</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4720524680176581</v>
+        <v>-0.4755593578487733</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4642836660663576</v>
+        <v>-0.4678116375386381</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.3964049801905816</v>
+        <v>-0.4000262831723802</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.3474488667397821</v>
+        <v>-0.351118092943743</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3276755335601536</v>
+        <v>-0.3313586452442934</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.2337944684039002</v>
+        <v>-0.2376333796582983</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2603269285836234</v>
+        <v>-0.2641406608794838</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.2766558399541026</v>
+        <v>-0.280432810151261</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.4580655209821884</v>
+        <v>-0.4616256565615728</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3267</v>
+        <v>3271</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.02670499237693491</v>
+        <v>-0.02821809096688099</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2239518307022053</v>
+        <v>-0.2252443187055562</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4003355839946394</v>
+        <v>-0.4014922925260223</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3976553158672971</v>
+        <v>-0.3988546526954977</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5024974881762461</v>
+        <v>-0.504940644292148</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4504849107875657</v>
+        <v>-0.4529828355713263</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4146146205033148</v>
+        <v>-0.4171996342940574</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.4322191754397124</v>
+        <v>-0.4347995273841221</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.281940131297084</v>
+        <v>-0.2847028561608553</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3983330365953321</v>
+        <v>-0.4009977129104954</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4112523356518238</v>
+        <v>-0.4138881279420801</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3983550758482153</v>
+        <v>-0.4010234399738692</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4070040077113433</v>
+        <v>-0.4097246060954376</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3967932698167544</v>
+        <v>-0.3995401064031938</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.3966651604446909</v>
+        <v>-0.3994497452984902</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.3940516803691096</v>
+        <v>-0.3968088940641579</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3879055949920911</v>
+        <v>-0.3906793903840224</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.3220105271437603</v>
+        <v>-0.3248722654849416</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.3016525975764281</v>
+        <v>-0.3045292415371108</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2799220421889288</v>
+        <v>-0.2828168562444944</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2240108065514761</v>
+        <v>-0.2270053880580036</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.2511147794157296</v>
+        <v>-0.2540822512698782</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.2946556959552495</v>
+        <v>-0.2975567968875552</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4442350136130031</v>
+        <v>-0.4469591882216051</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3305</v>
+        <v>3309</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.06835217498156965</v>
+        <v>-0.06941854200339748</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1169013688471807</v>
+        <v>-0.1179235215085939</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3076865005365761</v>
+        <v>-0.3085378557076695</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3432418254939691</v>
+        <v>-0.3440797078013205</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3908763671749966</v>
+        <v>-0.3926759143412468</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3673779641846053</v>
+        <v>-0.3691994452446323</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2805290095723194</v>
+        <v>-0.2824872085632819</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3311904804470416</v>
+        <v>-0.3331001923413197</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2122463653741704</v>
+        <v>-0.2142987862379826</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2156272554395073</v>
+        <v>-0.2177080537799867</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2252013793013887</v>
+        <v>-0.2272609035398858</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2457408434194619</v>
+        <v>-0.2477881783086389</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2671308466514972</v>
+        <v>-0.2691990670104047</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2896982969011717</v>
+        <v>-0.2917495726674204</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.2970949794019688</v>
+        <v>-0.2991652659618396</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.3178402256095865</v>
+        <v>-0.3198627821781201</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3132801608144575</v>
+        <v>-0.3153149510652753</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.2493237087787676</v>
+        <v>-0.2514412358349887</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2569078439587997</v>
+        <v>-0.2590088127939936</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2332653369598106</v>
+        <v>-0.2353886126609268</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.153992428344992</v>
+        <v>-0.1562348020620519</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1816365653360634</v>
+        <v>-0.1838500087186645</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.2517456944076812</v>
+        <v>-0.2538646437471002</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3399509868973993</v>
+        <v>-0.341967743028782</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3326</v>
+        <v>3330</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.04617276436530204</v>
+        <v>-0.04705051337231936</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1263817471573674</v>
+        <v>-0.1271752244309425</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2951282479410722</v>
+        <v>-0.2957676996966825</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3349365434604294</v>
+        <v>-0.335552204136107</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4144580910691644</v>
+        <v>-0.4158063838269754</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3600346256725331</v>
+        <v>-0.3614427720817588</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3084972694693136</v>
+        <v>-0.309993195292499</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.360599112853734</v>
+        <v>-0.3620428418521158</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2720816358184095</v>
+        <v>-0.2736308352577481</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2503844960050685</v>
+        <v>-0.2519859660256429</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2581832847456766</v>
+        <v>-0.2597674773416045</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2803592453083183</v>
+        <v>-0.2819270594939809</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3087015242137738</v>
+        <v>-0.3102732710399252</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3025567883885287</v>
+        <v>-0.3041441868737778</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.3440449504031946</v>
+        <v>-0.3456053052368517</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.3909194823812356</v>
+        <v>-0.3924051782050526</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3872549495976827</v>
+        <v>-0.3887504566894222</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2943734411452894</v>
+        <v>-0.2959847865148149</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3005607574937486</v>
+        <v>-0.3021586319700944</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.245870870870867</v>
+        <v>-0.2475292572757368</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2005674861983167</v>
+        <v>-0.2022991911096597</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.2285304646405635</v>
+        <v>-0.2302321979579887</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.2964767814767413</v>
+        <v>-0.2980889542387715</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.324485798581442</v>
+        <v>-0.3260678903202248</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3339</v>
+        <v>3343</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.0453290202659602</v>
+        <v>-0.04607587160190008</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1562769858518323</v>
+        <v>-0.1569017721086752</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.270425955909829</v>
+        <v>-0.2709556837616418</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3128353538220736</v>
+        <v>-0.3133350117749956</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3338972903220494</v>
+        <v>-0.3350822773120044</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.3087242879222387</v>
+        <v>-0.3099348043430155</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.260365100672999</v>
+        <v>-0.2616556648814736</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3431363193954127</v>
+        <v>-0.3443369773672842</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2547958118182621</v>
+        <v>-0.2561013605455074</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2660019339594655</v>
+        <v>-0.2673167110375019</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2727110934374863</v>
+        <v>-0.2740110339594679</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2958880868460128</v>
+        <v>-0.2971690993408984</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3284887135294099</v>
+        <v>-0.329763327630701</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3232329915287337</v>
+        <v>-0.3245209698422755</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3671248083236947</v>
+        <v>-0.3683798343607307</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4115129137397773</v>
+        <v>-0.4126990586256483</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3785033272746645</v>
+        <v>-0.3797335096595233</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2863881842622646</v>
+        <v>-0.2877322067333026</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2917088673907742</v>
+        <v>-0.2930413268233849</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2365016452288344</v>
+        <v>-0.2378956895166198</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1934846699195631</v>
+        <v>-0.1949463936661289</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.2216322679928524</v>
+        <v>-0.2230634111607586</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2882425736075334</v>
+        <v>-0.2895871896063937</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3164357434466609</v>
+        <v>-0.3177496708144503</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/roc/roc_12.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/roc/roc_12.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.03369</t>
+          <t>X ≈ -0.03352</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.06905299825097444</v>
+        <v>-1.679432363462737</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.4023690749936719</v>
+        <v>-1.924181105963754</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12.36421136520652</v>
+        <v>11.55047026133342</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.541010838701382</v>
+        <v>-3.761673576622016</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.32926476319861</v>
+        <v>10.69461535441347</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.966644755682282</v>
+        <v>7.169864547735578</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.75450079770193</v>
+        <v>10.06585178135578</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.48075057839222</v>
+        <v>9.765293020663208</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>14.08054874144024</v>
+        <v>13.58284450951187</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.758546286577655</v>
+        <v>9.105644822206003</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.59206238997285</v>
+        <v>13.06912147862947</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.87677958497677</v>
+        <v>16.48780935220256</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>19.32195114956088</v>
+        <v>19.07305972371287</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.54654276166028</v>
+        <v>15.13856751003531</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>18.45696409830662</v>
+        <v>18.15691279243732</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>11.92966509670474</v>
+        <v>11.33248040508717</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>11.79986903665164</v>
+        <v>11.23239975293354</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>8.133823723908563</v>
+        <v>7.406032540563928</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>8.351855721689184</v>
+        <v>7.622401931268769</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>8.540904519344195</v>
+        <v>7.838868244552884</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>11.56971498171492</v>
+        <v>10.9747214356331</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>11.49746261801759</v>
+        <v>10.90284717697258</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>15.3457025611178</v>
+        <v>14.85225872755145</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>18.84596128170895</v>
+        <v>18.3982474791405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.03125</t>
+          <t>X ≈ -0.03108</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.893325778607625</v>
+        <v>-8.323613106144641</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-6.24647159866015</v>
+        <v>-5.365835118821607</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-13.53914014614687</v>
+        <v>-13.02602104733385</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-10.30616721327193</v>
+        <v>-3.998801526846009</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.69942783191108</v>
+        <v>2.140514933475735</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.252917928098569</v>
+        <v>-0.9111114290671694</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.042574927052748</v>
+        <v>1.506771239999772</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.281104526513971</v>
+        <v>-5.21685314466658</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-9.242715467061956</v>
+        <v>-8.302294422162539</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-10.01512323342756</v>
+        <v>-9.097586605319286</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.207612309459357</v>
+        <v>0.810531549777437</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.91576789494075</v>
+        <v>3.749210461624344</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>20.74472466294271</v>
+        <v>15.49960345019888</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.55487052464595</v>
+        <v>8.824709562669973</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>11.90265364943819</v>
+        <v>8.147438435249605</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>8.508940992339404</v>
+        <v>5.491883047128837</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>16.36118851523482</v>
+        <v>11.82810121447762</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>8.276181791531798</v>
+        <v>5.259156914580274</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>20.47608201716151</v>
+        <v>15.13773040456395</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>16.67370427706483</v>
+        <v>12.13458633826991</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>16.1368083886557</v>
+        <v>11.57138053595808</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>12.06843134515301</v>
+        <v>8.27588617158225</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>12.34653905235662</v>
+        <v>8.521955649174735</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>12.27453271028038</v>
+        <v>8.362405185233676</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.02881</t>
+          <t>X ≈ -0.02864</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-11.06913775519786</v>
+        <v>-9.034283342212781</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.467077850823785</v>
+        <v>-1.003745820892711</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.896781813514693</v>
+        <v>-2.25118699115253</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.821262066527296</v>
+        <v>8.203112854498372</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.003395952731339</v>
+        <v>5.169265508371303</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.189696122391631</v>
+        <v>5.327073597686081</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.423697395118133</v>
+        <v>4.537452701491006</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.14874574797436</v>
+        <v>4.235647901550806</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.702978137382544</v>
+        <v>1.599319635072817</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.533590564113339</v>
+        <v>-7.490784690470683</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.752735049969495</v>
+        <v>-9.988946614347704</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.033178950410345</v>
+        <v>-10.26779298362854</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.172348898930451</v>
+        <v>-5.845501018668806</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-9.378426186176377</v>
+        <v>-11.63305940494129</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-2.557966804637346</v>
+        <v>-4.005982753849956</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-6.95342503972492</v>
+        <v>-8.989128140872815</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-4.594380360902882</v>
+        <v>-6.323554740749337</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-7.195562256642603</v>
+        <v>-9.230604334607925</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.478461161319153</v>
+        <v>-11.7929221254239</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-9.294746115287509</v>
+        <v>-11.58225021625498</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-4.844123154087136</v>
+        <v>-6.602140850795834</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.07566233258212662</v>
+        <v>-1.127073039021454</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.3501537296182988</v>
+        <v>-0.8838257406373344</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-2.225467289719631</v>
+        <v>-3.823974743081727</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.02636</t>
+          <t>X ≈ -0.0262</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.276087134646666</v>
+        <v>1.999775131382854</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.951311035454523</v>
+        <v>-3.762473303089223</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.393204949150309</v>
+        <v>-1.330866245390489</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.115268746081497</v>
+        <v>-0.08015764729090336</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.450015947051163</v>
+        <v>-2.195528694309239</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.263734404327245</v>
+        <v>-2.039971482566749</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.9466678834958557</v>
+        <v>0.8525295858817756</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.6704153508648432</v>
+        <v>0.5496723855704388</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.269389977213628</v>
+        <v>-3.009050648046689</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.048180564336839</v>
+        <v>-3.80223976326397</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.7518886858984</v>
+        <v>-9.065659684109207</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.054795742741781</v>
+        <v>-3.809361261395715</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.161721009274459</v>
+        <v>-8.613307858796482</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.390115813370912</v>
+        <v>-7.016803857838063</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.042369877921622</v>
+        <v>-9.54575696591359</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-5.456709181341445</v>
+        <v>-7.141265469234305</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-9.583207602212198</v>
+        <v>-10.94276900127196</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-7.694264586698658</v>
+        <v>-7.38172719027812</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.503214097381381</v>
+        <v>2.074925520688709</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.6930776785304289</v>
+        <v>0.4402373393528833</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.846816673596329</v>
+        <v>-1.976655811908202</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.07565592637964613</v>
+        <v>-0.2017047362858762</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2.349522985772261</v>
+        <v>1.893095864145835</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.2745327102808304</v>
+        <v>-0.1202710393784514</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.02392</t>
+          <t>X ≈ -0.02377</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.9473677139666208</v>
+        <v>-0.3136034063178883</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.288076319856614</v>
+        <v>-6.965004909727476</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.8935334112144346</v>
+        <v>-8.214270671195045</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.928061744987303</v>
+        <v>-3.997993049323959</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.612771701024329</v>
+        <v>-12.28965579686233</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.201673199963039</v>
+        <v>-2.514772879801008</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.434404045844133</v>
+        <v>-4.911141650713894</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.158369503762692</v>
+        <v>-3.610969809475087</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6774892789121196</v>
+        <v>-5.08946760011181</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.310078401275398</v>
+        <v>-1.065861360319381</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.811361070279766</v>
+        <v>-8.826361306441292</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.453090591040748</v>
+        <v>-4.284948797136444</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-6.333669309926002</v>
+        <v>-10.21957409927158</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.555705383849244</v>
+        <v>-8.862031979665744</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-7.213839992941551</v>
+        <v>-9.544795185418828</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.859113867902252</v>
+        <v>-10.59661834459207</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.993424044299545</v>
+        <v>-7.484811650607959</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.215586212513763</v>
+        <v>-4.400025891102032</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.000790849942625</v>
+        <v>-7.408379734807113</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.069917756447722</v>
+        <v>-3.974740514391669</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>2.413320491993673</v>
+        <v>-1.320104849953083</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.338361192632497</v>
+        <v>0.2161928863335305</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.613562469623531</v>
+        <v>2.072227666545082</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.425476106506359</v>
+        <v>3.523695507814331</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.02148</t>
+          <t>X ≈ -0.02133</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.406880013604372</v>
+        <v>-3.515451827175895</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-14.98098150873174</v>
+        <v>-6.768854582454225</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-13.50638374021335</v>
+        <v>-6.512906876303937</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-14.22366675346061</v>
+        <v>-8.610331409399365</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-13.10127291991757</v>
+        <v>-10.39213230551972</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.599720037243785</v>
+        <v>-4.21496072155049</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.3026822161168141</v>
+        <v>1.020138951633044</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.362590402221919</v>
+        <v>-5.31209529794652</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.322219053210851</v>
+        <v>-6.693594245244583</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-8.020710310858604</v>
+        <v>-8.996502569544191</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.356471712160491</v>
+        <v>-4.20108862933489</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.101279339837475</v>
+        <v>-5.988329430022766</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.756901013110692</v>
+        <v>-2.57183377040986</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.512636626086042</v>
+        <v>-2.819821606421449</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.169785445001473</v>
+        <v>-6.522166226933109</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-12.37906115307301</v>
+        <v>-10.49800428315501</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-6.64746167268909</v>
+        <v>-7.581645535420158</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.818636298255683</v>
+        <v>-4.692351991698139</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-5.072932000788555</v>
+        <v>-2.967375241765389</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.950643192938237</v>
+        <v>-1.241024510742101</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.024052727414571</v>
+        <v>-1.808338099863008</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>3.308807980461893</v>
+        <v>1.144225353398646</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5.05446365276579</v>
+        <v>2.902819357308694</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.98041506322155</v>
+        <v>5.771984852878212</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01903</t>
+          <t>X ≈ -0.0189</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.376580128237833</v>
+        <v>-6.944195267851008</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-8.469664372585157</v>
+        <v>-10.56328932555741</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.710216725639107</v>
+        <v>-6.782228664642687</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.691972773789658</v>
+        <v>-6.43951311053543</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.532759792030532</v>
+        <v>-6.714521542831463</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.842733451289995</v>
+        <v>-4.877724688199024</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-9.870240562670098</v>
+        <v>-9.041834424106867</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-10.16491621181515</v>
+        <v>-9.347212658531632</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-11.87518385580895</v>
+        <v>-9.222108476899983</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-10.93220310836072</v>
+        <v>-11.70444402883672</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.411220156334899</v>
+        <v>-6.373845005940382</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.692416222841736</v>
+        <v>-6.652436588105971</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-8.60036985198542</v>
+        <v>-11.14333716139512</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.333736556425926</v>
+        <v>-8.015445517958121</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-7.767872239882863</v>
+        <v>-5.317950163257912</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-8.911552731655618</v>
+        <v>-6.450012428084577</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-12.55424252687396</v>
+        <v>-9.93808108461981</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-10.91512477762708</v>
+        <v>-8.382647924459327</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-12.44071810950417</v>
+        <v>-11.55598379079619</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-12.24633371697542</v>
+        <v>-9.653074547022378</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-7.548999961935003</v>
+        <v>-5.143434769902868</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-4.826052945740329</v>
+        <v>-1.832786252284123</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-5.262113741755023</v>
+        <v>-6.672902949874626</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.07634448270248129</v>
+        <v>-0.05749640033220516</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01659</t>
+          <t>X ≈ -0.01646</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.528021981387994</v>
+        <v>2.534765420533006</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5702563553460607</v>
+        <v>-0.4599287097074054</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-8.73562730890275</v>
+        <v>-6.680089162983037</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-9.452437865852794</v>
+        <v>-10.61765022617489</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-9.792635809836774</v>
+        <v>-12.01042987838793</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-10.91137923132523</v>
+        <v>-12.97755087968824</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-12.99895433353306</v>
+        <v>-14.890137440134</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-13.2854334182534</v>
+        <v>-11.84495512605945</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8.00743876014387</v>
+        <v>-6.131347880550777</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.23689532858193</v>
+        <v>-0.2156607036219214</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-9.82871858300097</v>
+        <v>-7.775458672344897</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.863964494119479</v>
+        <v>-3.578494500341066</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.6881025698721</v>
+        <v>-2.451631384265013</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.975110263445913</v>
+        <v>1.779327817768902</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3.610220080249363</v>
+        <v>4.460644836344578</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.04339969157224</v>
+        <v>0.540096344384402</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.49356942112513</v>
+        <v>-1.805391564974855</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-5.229309018963576</v>
+        <v>-4.181617459451587</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.065492607085368</v>
+        <v>-0.6042756685895654</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.189980268836464</v>
+        <v>-2.634736874283526</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-4.05452456024166</v>
+        <v>-4.325118792577335</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-9.392222637882782</v>
+        <v>-8.893252632851699</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-6.480945864011566</v>
+        <v>-6.406271281132781</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.5149409739298534</v>
+        <v>-2.076159512120689</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01415</t>
+          <t>X ≈ -0.01402</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3589213613364493</v>
+        <v>1.099555027852219</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-6.938943700101731</v>
+        <v>-4.322415517187096</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.399056871226627</v>
+        <v>-2.477595128427666</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.109695638354211</v>
+        <v>0.03227786359723694</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.442840108255616</v>
+        <v>-1.727380714033885</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.267814009097847</v>
+        <v>-0.539283732839948</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-6.016378644604131</v>
+        <v>-5.472142116344351</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.308349034369108</v>
+        <v>-3.705264976436965</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.268383713602319</v>
+        <v>-4.615641896857824</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.039794047278676</v>
+        <v>-5.409937969797802</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2182958532966879</v>
+        <v>0.04466812863265091</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.05463750135295</v>
+        <v>-2.30708757762158</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1838995217564658</v>
+        <v>-0.3057010259054564</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.397439137248838</v>
+        <v>-3.667687083946817</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-2.059605505341338</v>
+        <v>-1.233763106309048</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.466522234833718</v>
+        <v>-0.6737059346273995</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>1.394982384553558</v>
+        <v>4.417980983177706</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.289603439852016</v>
+        <v>5.3261270787429</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.491416203495298</v>
+        <v>2.421891290617587</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-3.304553391582246</v>
+        <v>0.5562583899522835</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-3.848263787569294</v>
+        <v>-0.01054838933429636</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-3.924109748978395</v>
+        <v>-1.126784662516002</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-6.649635036496349</v>
+        <v>-2.966329823369684</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-7.725467289719397</v>
+        <v>-5.212863631970379</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.01171</t>
+          <t>X ≈ -0.01159</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5.842402762787103</v>
+        <v>5.952020781605192</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.734181898654292</v>
+        <v>-1.206554079661942</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.273147555559824</v>
+        <v>-1.599931007874872</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.440535216229613</v>
+        <v>2.989958400796084</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.326422389393166</v>
+        <v>-1.606135942685611</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.041982857500763</v>
+        <v>-1.825586062626392</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.913217023923721</v>
+        <v>-1.751607393658865</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.479405823920295</v>
+        <v>0.5380413425150365</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.438423385443976</v>
+        <v>-0.1993710339472585</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.216167989731183</v>
+        <v>-0.9919239659677714</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.9416226581505</v>
+        <v>-0.7213713055385895</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-6.753190439534819</v>
+        <v>-4.46160601933947</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.088818387938751</v>
+        <v>3.952714981444984</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.773950106218948</v>
+        <v>4.573144648654456</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.2974147047421383</v>
+        <v>1.29451913481212</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.01339332229621704</v>
+        <v>2.722429361752241</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.7599041682517793</v>
+        <v>2.619350248825363</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>7.013141542550031</v>
+        <v>8.561024086907793</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>6.326187706358432</v>
+        <v>7.909770557413182</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>7.426728016951969</v>
+        <v>8.99496505851323</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>4.697190757885245</v>
+        <v>5.825458734178042</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.83320065806911</v>
+        <v>1.40766195479717</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.350364963503452</v>
+        <v>2.520874099174456</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-2.452740016992763</v>
+        <v>-0.2490955160285893</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.009267</t>
+          <t>X ≈ -0.00915</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.883762530506132</v>
+        <v>-5.741507636330191</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.094249730077159</v>
+        <v>4.396214920619109</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.431979108776794</v>
+        <v>5.373429249882861</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.45903325735361</v>
+        <v>3.300510949348009</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7.896280670488721</v>
+        <v>5.994742310449965</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>10.34215447174694</v>
+        <v>8.371324130756086</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8.821091575938858</v>
+        <v>7.585241937734665</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.793155349124049</v>
+        <v>7.28438878152491</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>6.328367109193813</v>
+        <v>5.930564847773098</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.051267164075767</v>
+        <v>3.65615477096668</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.570719327549988</v>
+        <v>3.185774150048069</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.53821860456658</v>
+        <v>2.167861403252274</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.417638840162581</v>
+        <v>1.799520691107972</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.709204671315966</v>
+        <v>3.039622076310351</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4.321812322915072</v>
+        <v>5.336035138573486</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>7.186576820102133</v>
+        <v>7.386273158380703</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>7.055322087942031</v>
+        <v>7.285060981038633</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.681977868294595</v>
+        <v>4.920762281010539</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.899476044226184</v>
+        <v>5.136373403342418</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>5.08822177433612</v>
+        <v>5.352373375191263</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.788099848794332</v>
+        <v>4.042380532589917</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>4.469829644960818</v>
+        <v>4.714571380675686</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.229152842291874</v>
+        <v>3.467863414367947</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.392133956386118</v>
+        <v>-1.170575074756684</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.006821</t>
+          <t>X ≈ -0.006711</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.382332482675999</v>
+        <v>-0.1044283805209929</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.00674000003535</v>
+        <v>-4.134775170609025</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.077995134541538</v>
+        <v>-3.107397402947221</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.558220572088331</v>
+        <v>-2.93947816617387</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.520498412300235</v>
+        <v>-4.725988002866337</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-11.610658373004</v>
+        <v>-9.121014945086607</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.538238286518279</v>
+        <v>-6.122506499071349</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-10.25280920437763</v>
+        <v>-9.462205545257042</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7.785636829358047</v>
+        <v>-8.579362698456073</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.9527640429489</v>
+        <v>-7.855889178981649</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.867694461782946</v>
+        <v>-5.310092742079668</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-7.773537028525205</v>
+        <v>-7.867239404696612</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.18211189246437</v>
+        <v>-6.702644938446468</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.594752731300019</v>
+        <v>-6.192660269311411</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-4.447161235566021</v>
+        <v>-5.353728457655784</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-3.85151104212806</v>
+        <v>-4.795908293861707</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.362752005705786</v>
+        <v>-4.14055983760273</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.655746448186456</v>
+        <v>-2.752299040772385</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.250237071566765</v>
+        <v>-3.301483513492975</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-3.208156643993512</v>
+        <v>-5.375115914338799</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.124686551796941</v>
+        <v>-4.418827224884339</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.2384918770378661</v>
+        <v>-1.44464938099668</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.365082190968081</v>
+        <v>-5.77998160636195</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.814898184028571</v>
+        <v>-4.41769823756858</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004379</t>
+          <t>X ≈ -0.004274</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.517837811487389</v>
+        <v>-3.081804758323244</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.191981296199337</v>
+        <v>2.962216496137479</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3427611412281877</v>
+        <v>-0.5345209926583649</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.632654610538673</v>
+        <v>-3.371398173357413</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.045121792913932</v>
+        <v>-2.297377726288161</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.786092943028684</v>
+        <v>-3.938261173190448</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.101203757238466</v>
+        <v>-4.47339282565936</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5430556085151537</v>
+        <v>-0.7340300646752524</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.938361689005319</v>
+        <v>-2.404883191587501</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.478814942380559</v>
+        <v>1.299798734320795</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.151907604608063</v>
+        <v>2.02006200642036</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4.738561026867906</v>
+        <v>3.995970109921267</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>5.479058496908998</v>
+        <v>5.136670969687906</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.927630670494608</v>
+        <v>3.08919457107325</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>3.668620291795747</v>
+        <v>3.312104727184753</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.931912320132113</v>
+        <v>2.069694698065923</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.79879535950014</v>
+        <v>2.417541001822734</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1742007042954228</v>
+        <v>0.02877734430075662</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.787810402204407</v>
+        <v>0.6939301162107299</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.9746562121724338</v>
+        <v>1.360053401250561</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.30126892271096</v>
+        <v>2.601729111509307</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.225422961301973</v>
+        <v>2.075584155073209</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.565318234531688</v>
+        <v>1.415544055693687</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.825934579439249</v>
+        <v>3.063908615389863</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001936</t>
+          <t>X ≈ -0.001836</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.3262833983012</v>
+        <v>1.128843805011229</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.062644124809921</v>
+        <v>5.076408376232564</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.605502972093731</v>
+        <v>2.894673445423749</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5330380870423923</v>
+        <v>1.372446050056517</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.768749923158772</v>
+        <v>0.1674803685445099</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.6875473232363518</v>
+        <v>2.186570298538356</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.888183928498783</v>
+        <v>-0.003179899341965609</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.058047719011107</v>
+        <v>-2.367197552994043</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-5.963678744009037</v>
+        <v>-2.705827190759358</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.53088194531298</v>
+        <v>-7.696806921862532</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-9.783259407008245</v>
+        <v>-7.431500607076089</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-8.839941170474781</v>
+        <v>-6.311308180623755</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-8.546898458404002</v>
+        <v>-5.559544460971075</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.650499817138687</v>
+        <v>-4.407328611438714</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-6.313431145596176</v>
+        <v>-3.686816798874347</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-4.299709052985186</v>
+        <v>-1.725538521084957</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-6.331424065132019</v>
+        <v>-4.170013737398477</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-8.523620687272768</v>
+        <v>-6.645335406762676</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-6.41199470919215</v>
+        <v>-4.561891974154193</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-9.068750794958611</v>
+        <v>-7.161521752285516</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-10.55916426150274</v>
+        <v>-9.137872592141036</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-10.16107657362296</v>
+        <v>-7.810354700330478</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-9.412668211851688</v>
+        <v>-7.570444712726996</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-10.91030141294226</v>
+        <v>-9.614272082674844</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005068</t>
+          <t>X ≈ 0.0006007</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.144804709769346</v>
+        <v>-2.883673303883917</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.909467788387204</v>
+        <v>-2.715300169230716</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.05036670316523839</v>
+        <v>0.192219295564648</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.81548440946262</v>
+        <v>1.679845332149</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.627997729273048</v>
+        <v>3.485609684983153</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.955806414279245</v>
+        <v>2.393232092204833</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.611591302599642</v>
+        <v>2.437495500195098</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.6777717922720115</v>
+        <v>0.4763180137188954</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.51365934052027</v>
+        <v>2.265344321927778</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5530339851277049</v>
+        <v>0.6470134978149531</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1519718912585901</v>
+        <v>1.746003973214037</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-4.001838886212219</v>
+        <v>-2.687035553578482</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-5.987217122689799</v>
+        <v>-5.466018717493412</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.22238854049607</v>
+        <v>-7.796852464138873</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-6.872560599011024</v>
+        <v>-7.232126475458607</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.879406410299644</v>
+        <v>-7.510244677379497</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-7.448441692881438</v>
+        <v>-8.034709179317566</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-7.122247913944001</v>
+        <v>-7.754318843079197</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-7.768425498536715</v>
+        <v>-7.963703353337124</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-8.443648654086125</v>
+        <v>-9.006353056979663</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-8.986194822052155</v>
+        <v>-8.742322697324454</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-8.631006300702538</v>
+        <v>-9.658807263698002</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-9.218600553737829</v>
+        <v>-10.25721881126895</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-8.863398324202478</v>
+        <v>-8.751915235875686</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.002949</t>
+          <t>X ≈ 0.003038</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.669404090665303</v>
+        <v>2.967493323202511</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.692907770510054</v>
+        <v>3.080984482517934</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6174525308587988</v>
+        <v>-0.6857412715870126</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.765774883472893</v>
+        <v>-2.354972250754301</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.390780909212999</v>
+        <v>-2.986174072951094</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.991045190501666</v>
+        <v>-3.912553969631681</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.980256247791864</v>
+        <v>-3.260146267720437</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.336197381919668</v>
+        <v>-5.0019760888569</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.936750639009411</v>
+        <v>-4.303371807475507</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.85626114195076</v>
+        <v>-1.849094891068091</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.871298815962014</v>
+        <v>-4.469235043981577</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.718730462999645</v>
+        <v>-2.220245064580247</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.276103574791996</v>
+        <v>-4.778195609277645</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.065703956576868</v>
+        <v>-3.943260507450844</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-5.445534277067331</v>
+        <v>-4.626658041520066</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-4.491153247008334</v>
+        <v>-4.071509919211159</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.972789733914581</v>
+        <v>-2.368121007473263</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.436053376803869</v>
+        <v>-3.589126653596672</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.220161995879621</v>
+        <v>-3.743017759745292</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.750162064047714</v>
+        <v>-3.53163978751801</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.65113117108185</v>
+        <v>-4.826827372022805</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-5.802245949695205</v>
+        <v>-5.996013920297024</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-4.810925359076997</v>
+        <v>-4.667321999660381</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-4.886757612300272</v>
+        <v>-5.19771211681919</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.005392</t>
+          <t>X ≈ 0.005475</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.33504090576772</v>
+        <v>-2.02766824066768</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.556523680507752</v>
+        <v>-2.27589588900662</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.834148692845545</v>
+        <v>1.251842324654632</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.720870208526151</v>
+        <v>2.865347894803961</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.90183418451911</v>
+        <v>1.136719604198333</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.346165994869203</v>
+        <v>-0.1748890245441004</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>6.143418749073895</v>
+        <v>4.166832367968055</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.38206291286275</v>
+        <v>2.774816926420719</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.165779830517828</v>
+        <v>2.535997079525565</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.024025633196828</v>
+        <v>1.749573778950122</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.32613254446467</v>
+        <v>0.1858522712972359</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.162004709068952</v>
+        <v>-0.09129070986404031</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.44632328560796</v>
+        <v>-1.935009927756113</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4471687536460252</v>
+        <v>0.02116030204736319</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.1589644354975945</v>
+        <v>-0.6596244316487727</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.7533513574405859</v>
+        <v>0.2640238200188776</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.991181432358978</v>
+        <v>0.5263870357384732</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.8863407285378315</v>
+        <v>1.13179124020855</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.871745585705128</v>
+        <v>-1.609347675452319</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.032572343222007</v>
+        <v>1.555841783711365</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.003037327672338108</v>
+        <v>-0.1184057079671703</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.8163030575286285</v>
+        <v>-1.67513353038958</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.028817192630179</v>
+        <v>-2.545794813119763</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.732902233957546</v>
+        <v>-2.71286363197062</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.007836</t>
+          <t>X ≈ 0.007912</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2771626634423896</v>
+        <v>0.6353882473338146</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.3985678372667678</v>
+        <v>0.3858337409513695</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.588008029512523</v>
+        <v>2.914985519659766</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.878389138320443</v>
+        <v>0.2797796617244401</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.192931849384607</v>
+        <v>0.7098791759332741</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.036355716473913</v>
+        <v>0.5224951863605725</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.434809517358623</v>
+        <v>1.440489920398434</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.005025759125942386</v>
+        <v>2.523782871308519</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.7253599917511906</v>
+        <v>4.361140856584711</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1528731321086099</v>
+        <v>3.239863320966123</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.113679794644206</v>
+        <v>4.199089066081861</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.521677411569875</v>
+        <v>4.954568747375191</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.799438901051509</v>
+        <v>5.571701690361586</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.265376146475667</v>
+        <v>6.01331976947889</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.822514046504416</v>
+        <v>5.683500993218239</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.011402686660418</v>
+        <v>3.48691619051754</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.5338429379991396</v>
+        <v>3.382537922654429</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.147215292597195</v>
+        <v>4.63360713715393</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.6448936151022835</v>
+        <v>3.466272462413613</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.175382036754115</v>
+        <v>3.678893384030935</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>5.100189820678118</v>
+        <v>7.270695090960842</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>4.680701247585127</v>
+        <v>6.853495283027634</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.924248125015673</v>
+        <v>6.059224542268034</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>4.192058483476245</v>
+        <v>6.245469701362715</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.01028</t>
+          <t>X ≈ 0.01035</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.162724315139485</v>
+        <v>1.705974717409298</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.827947516789649</v>
+        <v>2.349123251637437</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.06849989633011</v>
+        <v>3.348536162834229</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.712688734030252</v>
+        <v>8.600976392351498</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7.82332683291142</v>
+        <v>9.253048020694251</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8.903150161865995</v>
+        <v>9.407951395191809</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9.024058620832768</v>
+        <v>9.503954984391626</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>8.299418604651109</v>
+        <v>8.330281486056364</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.7694772151373</v>
+        <v>4.867474980503125</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.103704396243735</v>
+        <v>2.309750547589019</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.609906895548498</v>
+        <v>4.824045171413928</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.331157492100502</v>
+        <v>4.548806734366799</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.54728113953005</v>
+        <v>5.25170236978807</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.219059405940598</v>
+        <v>5.905686799442186</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.114487536931414</v>
+        <v>4.784966795668502</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.369588744588739</v>
+        <v>4.445276268914334</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.896385893325579</v>
+        <v>2.532426446263358</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.791545189504319</v>
+        <v>2.401265713396064</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.561007999000076</v>
+        <v>1.70821923245208</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.3771461910318408</v>
+        <v>-0.8078881112706355</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.31245049814499</v>
+        <v>0.8968643424942968</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.129461679593071</v>
+        <v>1.276313198814407</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.511079249217907</v>
+        <v>0.6053546575231366</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.667389853137514</v>
+        <v>2.720926322367276</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.01272</t>
+          <t>X ≈ 0.01279</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4493577517298846</v>
+        <v>0.4218221541099751</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7841345500796564</v>
+        <v>-1.972256871510069</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.22215359911069</v>
+        <v>-3.224278259692888</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.225887760397356</v>
+        <v>-3.102107902811703</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.270898091100584</v>
+        <v>-4.07976593462633</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.920811337627356</v>
+        <v>-6.067440900266085</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.983540163361717</v>
+        <v>-6.866086530777103</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.715652317334651</v>
+        <v>-3.584780627195016</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.674165135419948</v>
+        <v>-3.454179003802103</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.935897911947777</v>
+        <v>4.061438805495968</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.88224102745054</v>
+        <v>-3.821425765516395</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.033330856430453</v>
+        <v>-1.246978337198286</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.447273065130538</v>
+        <v>-1.635492843312157</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.249912225265078</v>
+        <v>-1.179422468529957</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-2.617275381001654</v>
+        <v>-2.570513033684982</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.1047711154094131</v>
+        <v>-0.5729642267447872</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.7383658797241708</v>
+        <v>-0.6782326919329975</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.5752331327667548</v>
+        <v>1.354633383132075</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.500344371847099</v>
+        <v>2.29291752150327</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>4.524069614439284</v>
+        <v>5.405312278725773</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.272303588317229</v>
+        <v>4.115731755624395</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.778017910596063</v>
+        <v>3.316666432825755</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.180152197546242</v>
+        <v>5.017461167744976</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.267440511698815</v>
+        <v>1.204411307202136</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.01516</t>
+          <t>X ≈ 0.01522</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.631880159295306</v>
+        <v>1.814641235800494</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5698306336727157</v>
+        <v>-1.126830697829163</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.949993402823587</v>
+        <v>-0.5864275063875652</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.14613029247176</v>
+        <v>-1.177662042025368</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.8103398199244296</v>
+        <v>-0.5714349882579839</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.815487824203686</v>
+        <v>2.28106371566605</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.2253573221314582</v>
+        <v>-1.207248068151891</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.765327695560259</v>
+        <v>2.073355422424605</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.534087604747683</v>
+        <v>5.794981908286431</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.761171928711192</v>
+        <v>4.091456629452296</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.217049752691359</v>
+        <v>3.457385523612309</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.698063287120277</v>
+        <v>-0.7625365987426207</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.639407172158272</v>
+        <v>-3.688041553570088</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-6.678667866786682</v>
+        <v>-7.559879232597382</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-3.7004475280036</v>
+        <v>-4.648735999180722</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.196969696969695</v>
+        <v>-1.382831063485114</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.3963858933256148</v>
+        <v>-0.5916310368111013</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.2915451895044328</v>
+        <v>-1.642758659083796</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.219836156843975</v>
+        <v>-3.265898731884043</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.942081255966912</v>
+        <v>-3.055837551568196</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.757354696660208</v>
+        <v>0.01599391599119571</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.742291567160223</v>
+        <v>-1.322560306644725</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.467816854678112</v>
+        <v>0.7350718318740164</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-3.361830926083208</v>
+        <v>-3.416227546343713</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.01761</t>
+          <t>X ≈ 0.01766</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.855132827717711</v>
+        <v>-1.283355449485931</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.86848105463887</v>
+        <v>-2.427662759259455</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-7.199357246527057</v>
+        <v>-5.47960764296645</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.126596980255513</v>
+        <v>-4.274759059959258</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.998101738517043</v>
+        <v>-0.9486182976068491</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.02542126670538636</v>
+        <v>0.1067157824608529</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.475941379167111</v>
+        <v>-2.486516678939942</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.602990033222596</v>
+        <v>1.705513418438763</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.323048643708731</v>
+        <v>3.630693109938413</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.550132967672241</v>
+        <v>2.838240284129363</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.288478324119801</v>
+        <v>7.607875673197213</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.11687177781468</v>
+        <v>6.432443410980028</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.779423996672897</v>
+        <v>7.688254299715773</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.87977369165489</v>
+        <v>6.545773872286723</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>3.328773251217179</v>
+        <v>4.971386108380507</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.923160173160127</v>
+        <v>4.625325889565268</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>7.360671607611266</v>
+        <v>8.154234342326895</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>6.362973760932945</v>
+        <v>7.119505038569315</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>6.578865141857229</v>
+        <v>7.337144583299235</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>6.765710951825298</v>
+        <v>5.731571604727591</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.330307641002157</v>
+        <v>4.249157868319308</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>8.825890251021541</v>
+        <v>7.82710667488562</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>7.314650677789317</v>
+        <v>5.92022337455132</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.345961281708902</v>
+        <v>7.592946765582958</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.02005</t>
+          <t>X ≈ 0.0201</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.5544273603455139</v>
+        <v>-0.2688448887498325</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.358339961164525</v>
+        <v>-3.083772796359618</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-10.96919851636833</v>
+        <v>-10.76564961501451</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.978448832107368</v>
+        <v>-10.07817131486805</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.141399798481871</v>
+        <v>-2.609625943262458</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.218405893788386</v>
+        <v>1.403154289093735</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.257246493805674</v>
+        <v>-3.250089367996338</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.933677863910418</v>
+        <v>-0.9790436840013825</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.678868749528831</v>
+        <v>4.289242387993788</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.844224678430621</v>
+        <v>7.372187704124556</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>13.82198802429628</v>
+        <v>11.50952941908385</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>12.30867071961367</v>
+        <v>9.948436928659561</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.18550865275753</v>
+        <v>8.845119903704763</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.96442977631094</v>
+        <v>9.405052648157415</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>9.071718577495808</v>
+        <v>7.47679326945444</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>9.666105499438913</v>
+        <v>8.037837847130874</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.35934885628852</v>
+        <v>1.442072586090084</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.489076053701908</v>
+        <v>2.608885226607271</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>7.174103237095402</v>
+        <v>5.439360583679218</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>6.964229020901868</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>9.287538681566467</v>
+        <v>10.35097883759224</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>9.21169272015748</v>
+        <v>11.59160578932117</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>8.251599531404921</v>
+        <v>11.83524027459946</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>3.237495673243338</v>
+        <v>7.72573285925737</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.02249</t>
+          <t>X ≈ 0.02253</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.330167379321615</v>
+        <v>3.17563079259746</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.444665943290723</v>
+        <v>4.420122188628419</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.455922256578539</v>
+        <v>3.188359042540029</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.192243599454628</v>
+        <v>4.063424119663317</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.05935167763203708</v>
+        <v>-2.116399557866963</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2463178637293737</v>
+        <v>-1.973797799245894</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.525630820160977</v>
+        <v>-2.757414333576996</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-5.151668351870576</v>
+        <v>-7.50199940796049</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-6.559456532274709</v>
+        <v>-8.873067838437336</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-5.883096845992362</v>
+        <v>-8.175854732446574</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.058312566149276</v>
+        <v>-9.385418841150766</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.539960520321912</v>
+        <v>-3.740537041338662</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.583254224416216</v>
+        <v>2.553566457753355</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.362175347969625</v>
+        <v>2.305332396320246</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6.602582775026754</v>
+        <v>5.537805220925669</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.849143610013172</v>
+        <v>1.636401029293111</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.613777197673386</v>
+        <v>4.519462228423109</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>9.85676258080872</v>
+        <v>8.880065856235802</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>12.97120468637078</v>
+        <v>12.12247738687765</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>10.25949977170107</v>
+        <v>9.342908388939392</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>9.716953603735043</v>
+        <v>8.795954914147259</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>9.641107642325942</v>
+        <v>8.720792392191946</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>15.71268380408331</v>
+        <v>15.02503293807643</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>11.28902546390356</v>
+        <v>10.31743939833245</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.02493</t>
+          <t>X ≈ 0.02497</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>11.5765441909159</v>
+        <v>11.34361046888358</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.546115218653</v>
+        <v>2.34039870057596</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.905197618897397</v>
+        <v>5.587109299292273</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.503408574458405</v>
+        <v>-3.865968134693148</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.957902402269696</v>
+        <v>1.825889891826854</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-5.550783585545986</v>
+        <v>-6.877851737352323</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.9236445421578452</v>
+        <v>-0.2911912682409081</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.543983822042499</v>
+        <v>2.361753796016771</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.6869202793195157</v>
+        <v>-0.5198679532522092</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.08599539671699574</v>
+        <v>-1.264234297184757</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.086614970082586</v>
+        <v>1.940023649442487</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.807865566634618</v>
+        <v>1.637599119327838</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.684703499778472</v>
+        <v>0.5227070018770661</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.434926101305777</v>
+        <v>-2.657549991578982</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>2.254756688070181</v>
+        <v>1.110015175857072</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>4.298418972332009</v>
+        <v>3.139824087614336</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.164501835354535</v>
+        <v>3.035756725361409</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>2.610385769214496</v>
+        <v>1.38981194878447</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.275552512457701</v>
+        <v>3.090714821646806</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.01312296010687</v>
+        <v>1.794211602437734</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.02130142982201</v>
+        <v>-0.29495417676182</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>5.293281555369425</v>
+        <v>4.175337846737484</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>8.466306992489166</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>8.39047473926589</v>
+        <v>7.28713636802933</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.02738</t>
+          <t>X ≈ 0.02741</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.009268166063549</v>
+        <v>1.257735764559619</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.182270825060286</v>
+        <v>10.78876024424858</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.481093881292445</v>
+        <v>6.87691733136208</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.031297756586589</v>
+        <v>6.255147410878322</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.327086231407662</v>
+        <v>10.88273878931319</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>17.40878925961037</v>
+        <v>16.03092507887167</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.37368268098323</v>
+        <v>12.75490058569642</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.09547123623007</v>
+        <v>12.4499801422878</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>16.40011631288162</v>
+        <v>17.71600034390935</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.99562168947675</v>
+        <v>14.29216775937043</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.006523436901865</v>
+        <v>9.602517812089815</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.096195086085409</v>
+        <v>4.364050895733541</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.341454071860873</v>
+        <v>-1.771461626952949</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.38353309015109</v>
+        <v>2.942189273498919</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>5.725389792570574</v>
+        <v>2.230667169938471</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>6.319776714513523</v>
+        <v>4.398894727119796</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>6.18585957753605</v>
+        <v>4.281091260678849</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.081018873714939</v>
+        <v>4.177151223439544</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.665331307270769</v>
+        <v>1.867972264213925</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.852177117238831</v>
+        <v>3.688703740832338</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.6780520019043834</v>
+        <v>2.152598270790627</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.6022060404952825</v>
+        <v>2.077435748835342</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.754898194391082</v>
+        <v>-0.2430323299888428</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.800848499754089</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.02982</t>
+          <t>X ≈ 0.02985</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-4.746878875758966</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.182270825060364</v>
+        <v>8.237227518550391</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.74425177602933</v>
+        <v>7.101282592011763</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.399718809218193</v>
+        <v>6.528671922429098</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.327086231407748</v>
+        <v>8.918907957557806</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.882473470136659</v>
+        <v>9.056050034330447</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11.37368268098319</v>
+        <v>10.88717913887487</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.463892288861658</v>
+        <v>7.956047578689109</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.873800523407994</v>
+        <v>5.339016196243072</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>15.62720063684516</v>
+        <v>15.14676681425988</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>15.90126027900708</v>
+        <v>15.41900182886421</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.99093192819068</v>
+        <v>12.51620875761576</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.86776986133456</v>
+        <v>11.44089969861592</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.015112037519543</v>
+        <v>8.566454520405649</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>8.356968739938942</v>
+        <v>7.904091667746108</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>6.319776714513566</v>
+        <v>5.819393040563085</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>6.185859577536093</v>
+        <v>5.735417573005641</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>6.081018873714868</v>
+        <v>5.600625335129777</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.665331307270769</v>
+        <v>3.129156950812963</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.852177117238853</v>
+        <v>3.343743395872004</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>5.941209896641233</v>
+        <v>5.479001597193957</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>5.865363935232132</v>
+        <v>5.403839075238672</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.508259700345718</v>
+        <v>2.944770857814305</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>8.69558534185925</v>
+        <v>8.188037268930252</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.03227</t>
+          <t>X ≈ 0.03228</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>21</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.502010029425172</v>
+        <v>5.62607219800072</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.594671530829395</v>
+        <v>0.7316392851993143</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.729214182044366</v>
+        <v>3.997118032321559</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.01626016260159</v>
+        <v>3.383323628832684</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.081435071850336</v>
+        <v>-6.210678870142196</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.8674358761517666</v>
+        <v>3.264699094731434</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.666417569643372</v>
+        <v>-2.157516789918169</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-4.944629014396384</v>
+        <v>-2.483829438007405</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.665046594386546</v>
+        <v>-11.54599165911513</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-5.676057508518234</v>
+        <v>-7.71490928191762</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.401997866356311</v>
+        <v>-7.442674267313286</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.680747269804307</v>
+        <v>-7.740648426465206</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.803909336660361</v>
+        <v>-8.898324953277246</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.263083451202192</v>
+        <v>-4.519425142293478</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-7.68313151068751</v>
+        <v>-9.871497805956579</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-11.85064935064925</v>
+        <v>-13.95871986423448</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-11.98456648762672</v>
+        <v>-14.30240946780327</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-7.327502429543173</v>
+        <v>-9.842705533733032</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-7.111611048618848</v>
+        <v>-6.652052830396713</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-2.162860476746168</v>
+        <v>-1.675561623433076</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-7.467311406616915</v>
+        <v>-7.004910886718527</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-7.543157368026016</v>
+        <v>-7.080073408673812</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-7.268682655543898</v>
+        <v>-6.83643892339537</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.179294615042352</v>
+        <v>2.525231606124692</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.03471</t>
+          <t>X ≈ 0.03472</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>13</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.205306732721823</v>
+        <v>3.746750561266708</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.821777757935628</v>
+        <v>-4.154833930114748</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.124818577648767</v>
+        <v>9.389006766528361</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.411864558206084</v>
+        <v>1.140926912042495</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>20.46068947027415</v>
+        <v>23.39284129941559</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.95534796406393</v>
+        <v>8.604719960358899</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.18339928017347</v>
+        <v>15.39205553054373</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.212880143112763</v>
+        <v>-0.1509601509600813</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.25436732502741</v>
+        <v>0.1967489785041607</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-4.210856043316724</v>
+        <v>-8.181720099132718</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-3.936796401154801</v>
+        <v>-7.909485084528384</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.215545804602847</v>
+        <v>-8.25932711225984</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-5.338707871459022</v>
+        <v>-9.520739376230644</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-5.559786747905612</v>
+        <v>-9.768973437663753</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-6.217930045486113</v>
+        <v>-10.59764796606907</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-5.623543123543179</v>
+        <v>-10.10960402050939</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.934847431787041</v>
+        <v>-2.85879093296262</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.830006727965973</v>
+        <v>2.29099409996666</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.045898108890299</v>
+        <v>2.505456327112434</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.232743918858326</v>
+        <v>2.720042772171418</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.690197750892239</v>
+        <v>2.152598270790627</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>1.614351789483194</v>
+        <v>2.077435748835398</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>1.888826501965248</v>
+        <v>2.321070234113776</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1.812994248741859</v>
+        <v>2.158931239824199</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.03491</t>
+          <t>X &gt; -0.03474</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3343</v>
+        <v>3367</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01636701836363841</v>
+        <v>-0.03230224433479378</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1271840900878729</v>
+        <v>-0.02636183174011109</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1520496195523648</v>
+        <v>-0.05503404114879373</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1943935904250083</v>
+        <v>-0.0702327579302704</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.09712867826382166</v>
+        <v>-0.004513462380877797</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0719104068422709</v>
+        <v>-0.03785853450917642</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.02356042678623993</v>
+        <v>-0.0481543777513096</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.04662932628065874</v>
+        <v>-0.07033725626691023</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.04764394541744821</v>
+        <v>-0.04389151642373434</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.08858570120728615</v>
+        <v>-0.1133288630396478</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.0654293891442137</v>
+        <v>-0.06079531276171934</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1183315434541683</v>
+        <v>-0.08369589726780902</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1508724510654105</v>
+        <v>-0.08626029699141213</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2052248171432112</v>
+        <v>-0.1098703257919738</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.09988341431299119</v>
+        <v>0.02514945767627808</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1739643525677508</v>
+        <v>-0.01811032901573384</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.08122604697295088</v>
+        <v>0.073324194823158</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.0787145895341439</v>
+        <v>0.07657643935860392</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.0839612790336588</v>
+        <v>0.1010398657564195</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1781406850350038</v>
+        <v>0.00685563299786196</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.135173530545984</v>
+        <v>0.08001210324896846</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1034819462878147</v>
+        <v>0.05218287763412377</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1101613522858145</v>
+        <v>0.07595786429826035</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1382701613917732</v>
+        <v>-0.009170928277910662</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.03247</t>
+          <t>X &gt; -0.0323</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3315</v>
+        <v>3340</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.01592200857876236</v>
+        <v>-0.01898712061728958</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1248597523571462</v>
+        <v>-0.01102017892452523</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2577676610525828</v>
+        <v>-0.1488509920970031</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1745729922495158</v>
+        <v>-0.0403917692761766</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1936412020529445</v>
+        <v>-0.09100342586993548</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1398077053492699</v>
+        <v>-0.096124559425526</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1145968413520606</v>
+        <v>-0.1299143077800267</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1355483722326483</v>
+        <v>-0.149846842337908</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1669770963170052</v>
+        <v>-0.1540477657352</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1717590633967205</v>
+        <v>-0.1878535006149846</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1807867857702377</v>
+        <v>-0.1669353586801563</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2618799934077316</v>
+        <v>-0.2176571672485537</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.315348789170244</v>
+        <v>-0.241141027697708</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3382714211270681</v>
+        <v>-0.2331361406324888</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.2566230011465791</v>
+        <v>-0.1214246770657965</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2761971201634168</v>
+        <v>-0.109866601417167</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1815791879507742</v>
+        <v>-0.01688390100588322</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1480814289840353</v>
+        <v>0.01732634512730158</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1552140319809325</v>
+        <v>0.04023843588551301</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2517857124023095</v>
+        <v>-0.05645704380213346</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2340383505590538</v>
+        <v>-0.008058900336180841</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2014688083694196</v>
+        <v>-0.03553207328867813</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.2407086191260248</v>
+        <v>-0.04349127441665956</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2986196275778426</v>
+        <v>-0.1579734124097385</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.03003</t>
+          <t>X &gt; -0.02986</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3290</v>
+        <v>3309</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.02873911429379916</v>
+        <v>0.05881384811989676</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.07834294501441263</v>
+        <v>0.03914581174842624</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1568453777312016</v>
+        <v>-0.02821265069103873</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.09758519421743728</v>
+        <v>-0.003307845890056171</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.174600270215123</v>
+        <v>-0.1119091584597598</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1085530683982796</v>
+        <v>-0.088489445204047</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1075453361415626</v>
+        <v>-0.1452474150575043</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.06605326467732198</v>
+        <v>-0.1023771550087389</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.09801251903170538</v>
+        <v>-0.07771181942233341</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.09696146332049693</v>
+        <v>-0.1043836528525759</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1989357150652893</v>
+        <v>-0.1760926491492327</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3088226065410709</v>
+        <v>-0.2548203272651932</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4753797424537751</v>
+        <v>-0.3886064489170522</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.436243624362433</v>
+        <v>-0.317993564870136</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.3490187203759447</v>
+        <v>-0.1988906052863371</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.3429534887994521</v>
+        <v>-0.1623459725579792</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.3072841097075099</v>
+        <v>-0.1278523321270626</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.2120955871946464</v>
+        <v>-0.03178116398512998</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.3119867983118141</v>
+        <v>-0.1012007454469241</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.3803988582189319</v>
+        <v>-0.1706674834649462</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.3584368820120574</v>
+        <v>-0.1165395961733253</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.2947051317244558</v>
+        <v>-0.1133966745552186</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.3363563977847051</v>
+        <v>-0.1237357152239511</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.3941602988381661</v>
+        <v>-0.2377956355970952</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02759</t>
+          <t>X &gt; -0.02742</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.16532836807216</v>
+        <v>0.1588295825690125</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.06125082309676344</v>
+        <v>0.05061666380314023</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1231230831369388</v>
+        <v>-0.003761970502644374</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2073556220419874</v>
+        <v>-0.09357095166884477</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2506371468052322</v>
+        <v>-0.169997239121507</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1860699815156934</v>
+        <v>-0.1480556748233681</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1756221697570695</v>
+        <v>-0.1967528242221022</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1302354063714901</v>
+        <v>-0.1500914544392842</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1324862501875756</v>
+        <v>-0.09615762827105101</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.03004910515689119</v>
+        <v>-0.02314001174219271</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1059658770972405</v>
+        <v>-0.06816024989865355</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2137536053857616</v>
+        <v>-0.1446868058386528</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4298785836048324</v>
+        <v>-0.3285856103863196</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3261859928324071</v>
+        <v>-0.1935382119087663</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.3218316670311907</v>
+        <v>-0.1570160811958132</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.2615938389419057</v>
+        <v>-0.06525945924929033</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.2545198481543309</v>
+        <v>-0.05970528455284807</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.1261452281860471</v>
+        <v>0.06939745933977548</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1991686523055591</v>
+        <v>0.02739747321459873</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2706838150550155</v>
+        <v>-0.04515053315011386</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.3032284355865116</v>
+        <v>-0.0452039270115705</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2992635005159201</v>
+        <v>-0.102247163671997</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.3448057531989051</v>
+        <v>-0.1153754216355409</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.3716211358734682</v>
+        <v>-0.1983509524716851</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.02514</t>
+          <t>X &gt; -0.02499</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3200</v>
+        <v>3219</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1479727623444305</v>
+        <v>0.1279469918153779</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0004686322786753294</v>
+        <v>0.1145827583083303</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.07202805398048184</v>
+        <v>0.01850072935567937</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1775444794788683</v>
+        <v>-0.09379596516261302</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2162718530513885</v>
+        <v>-0.1360181466766051</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1536064749092674</v>
+        <v>-0.1163180377876003</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1931579518391473</v>
+        <v>-0.2143549522573949</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1427455744533077</v>
+        <v>-0.1618302700219232</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.08347212945279381</v>
+        <v>-0.04729269410892556</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.001484198892789834</v>
+        <v>0.04025588343710496</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.01350166679026898</v>
+        <v>0.08277636689145851</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1849873219895741</v>
+        <v>-0.08321044032138758</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3246935457037452</v>
+        <v>-0.189606113208896</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2470620893865032</v>
+        <v>-0.0790752281000664</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.2011982574860198</v>
+        <v>0.0004837658917153931</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.180420161716917</v>
+        <v>0.05344334427329755</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.1087591019971725</v>
+        <v>0.1228624199214678</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.007893363209284132</v>
+        <v>0.1943930266213414</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.2413933827694237</v>
+        <v>-0.006950620778439998</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.2857425883922815</v>
+        <v>-0.05329310696656364</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2791098693676091</v>
+        <v>-0.01280305662187686</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.3051216165611663</v>
+        <v>-0.1005787234976694</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.3869046397453317</v>
+        <v>-0.149068322981357</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.3817172897196315</v>
+        <v>-0.1996607739401668</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.0227</t>
+          <t>X &gt; -0.02255</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3147</v>
+        <v>3157</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1664198691904701</v>
+        <v>0.1366185549082743</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02121653055628769</v>
+        <v>0.2536180561918258</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.05819272384594143</v>
+        <v>0.1801832845771401</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2972130939995878</v>
+        <v>-0.01712183807423173</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1590699172577601</v>
+        <v>0.1026658996685086</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1932727674952943</v>
+        <v>-0.06921502853678163</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2205684335287543</v>
+        <v>-0.1221152388255646</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1646582211471284</v>
+        <v>-0.09409297149606743</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.07346802747587589</v>
+        <v>0.05173006299344962</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.0373958432827024</v>
+        <v>0.06197880681781243</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1284421577545913</v>
+        <v>0.2577420101434811</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1636306415765745</v>
+        <v>-0.0006929306215042175</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2234937632112874</v>
+        <v>0.007371401880078565</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.140815475275744</v>
+        <v>0.09341236093922589</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.08309529848406783</v>
+        <v>0.1879425226168578</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1353071123277161</v>
+        <v>0.2625988161483832</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.06017720115764291</v>
+        <v>0.2722687526337992</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.01244591896837477</v>
+        <v>0.2846223496808449</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.2286040387083546</v>
+        <v>0.1384052883345745</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.3085738557187838</v>
+        <v>0.02371979745547037</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.324454263759776</v>
+        <v>0.01287090954426873</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.3496416638720206</v>
+        <v>-0.1067997687335094</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.4374368154035864</v>
+        <v>-0.1926921276537144</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.4626773310288073</v>
+        <v>-0.2727833870123177</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.02026</t>
+          <t>X &gt; -0.02011</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3079</v>
+        <v>3091</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2674216204181619</v>
+        <v>0.2145987054154119</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3525414628952248</v>
+        <v>0.4035640911807192</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2388118195489852</v>
+        <v>0.3230962417489707</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.01035392413725589</v>
+        <v>0.1663630638045959</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1267598340189195</v>
+        <v>0.3267541175728823</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.07387087910851164</v>
+        <v>0.01930623181226565</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2321244725595761</v>
+        <v>-0.1465050080168453</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.07194650035690842</v>
+        <v>0.01732344828578647</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.02036603220258115</v>
+        <v>0.1957583400376777</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1389163956894208</v>
+        <v>0.2553983379856817</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2054068031440792</v>
+        <v>0.3529483583173914</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.0545822130342728</v>
+        <v>0.1271569590454291</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1233730444736523</v>
+        <v>0.06244339844143809</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.06634849305584112</v>
+        <v>0.155616644939812</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.007159631676103118</v>
+        <v>0.3312188660236188</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.1350973289748794</v>
+        <v>0.4923625833932874</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.08530358613177924</v>
+        <v>0.4399679901011453</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.09705572435040466</v>
+        <v>0.3908922644433872</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1216166072626095</v>
+        <v>0.2047208868420469</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.2723086024122168</v>
+        <v>0.05072501400061213</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.309003566933356</v>
+        <v>0.05175793465617318</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.4304388629024558</v>
+        <v>-0.1335120489213821</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.5587259455872555</v>
+        <v>-0.2587884582934876</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.5828885303821778</v>
+        <v>-0.4018531714939613</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01781</t>
+          <t>X &gt; -0.01768</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3022</v>
+        <v>3032</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3927386620043194</v>
+        <v>0.3539024139981066</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5189430951329399</v>
+        <v>0.6169692203322725</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3321588172576995</v>
+        <v>0.4613594902572515</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.0801860292933867</v>
+        <v>0.2949074880414244</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2712312498643215</v>
+        <v>0.4637710252126794</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.00278379551674135</v>
+        <v>0.1145980604008727</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.05033340136954934</v>
+        <v>0.0265901224413625</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1184238747433923</v>
+        <v>0.1995489200213498</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2447360995806918</v>
+        <v>0.379021579549331</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3477363201536363</v>
+        <v>0.4881261412978688</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3113458291832245</v>
+        <v>0.4838457225954969</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.0517568136232498</v>
+        <v>0.2590817675157169</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.03651736519814364</v>
+        <v>0.2804978354567211</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.03300330033003718</v>
+        <v>0.3146181843893459</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.1538098026485883</v>
+        <v>0.441146627477309</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.3057323565910082</v>
+        <v>0.6274549731285148</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.3237066729753764</v>
+        <v>0.6419155149720268</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.3047639601587093</v>
+        <v>0.5616174857973633</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.1107423555526736</v>
+        <v>0.4335736493686468</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.04645836034401896</v>
+        <v>0.2395522482025711</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.1724450644465705</v>
+        <v>0.1528517240918532</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.3475301922466798</v>
+        <v>-0.1004456973387917</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.4700121453286314</v>
+        <v>-0.133975544374195</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.5924428026249799</v>
+        <v>-0.4085540453391303</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01537</t>
+          <t>X &gt; -0.01524</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2946</v>
+        <v>2943</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3118555892707349</v>
+        <v>0.2879503896754301</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5176193314614608</v>
+        <v>0.6495359603164843</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.5660867689169606</v>
+        <v>0.6773258273752916</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3261057224471955</v>
+        <v>0.6249168786514332</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.5308557904404552</v>
+        <v>0.8410064585869392</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.2786327873486485</v>
+        <v>0.5105210150960673</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2837111304853224</v>
+        <v>0.4776906161787835</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4642124539245742</v>
+        <v>0.5637897831206331</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4576231631716894</v>
+        <v>0.5759032927497714</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4144138508066888</v>
+        <v>0.5094095355207244</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.5729360855735806</v>
+        <v>0.7336174151370116</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1785710768236726</v>
+        <v>0.3751348724560088</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1584016540865818</v>
+        <v>0.3631208393830718</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.05901030333307489</v>
+        <v>0.2703235335667813</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.0646423956229043</v>
+        <v>0.319591975561174</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.3405368493474228</v>
+        <v>0.6300968072971287</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.396385893325558</v>
+        <v>0.7159251412429342</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.4475302691924128</v>
+        <v>0.7050588416000068</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1410865025860986</v>
+        <v>0.4649595104961577</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.008839557186675506</v>
+        <v>0.3264743453487711</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.07229637412734746</v>
+        <v>0.2882711518810268</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.1141980042397748</v>
+        <v>0.1654597791344159</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3149439299111449</v>
+        <v>0.0557065217391326</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.5944421709144692</v>
+        <v>-0.3581235708085302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.01293</t>
+          <t>X &gt; -0.0128</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3102018376169866</v>
+        <v>0.2605833207379717</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.779620843462979</v>
+        <v>0.8171886971764621</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.6702731231033141</v>
+        <v>0.7837088311536888</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4468295931710671</v>
+        <v>0.6449004913824439</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6704796800643535</v>
+        <v>0.927611716251711</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3329703416861989</v>
+        <v>0.5459201214542873</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.505077601851788</v>
+        <v>0.678317220436675</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5967690768442395</v>
+        <v>0.7077410500393313</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5885439951033078</v>
+        <v>0.7509606647913358</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5709215070992144</v>
+        <v>0.7090081869118592</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5853970916268807</v>
+        <v>0.7568485818052437</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.2570394035340229</v>
+        <v>0.465578622089815</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.1704291022890843</v>
+        <v>0.3856733153464376</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1804596863471915</v>
+        <v>0.4031120896894791</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.1392821672660673</v>
+        <v>0.371970650608425</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.4040315466130977</v>
+        <v>0.6740606510711871</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.3612981740273113</v>
+        <v>0.5910929105349183</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.3828052807644653</v>
+        <v>0.5492377840777962</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1984478063837614</v>
+        <v>0.398972348258134</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1252623593219084</v>
+        <v>0.3187260951619351</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.06037992290153227</v>
+        <v>0.298347258644867</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.01967099592672383</v>
+        <v>0.2090338804334735</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.09236167036845444</v>
+        <v>0.1576086956521792</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.3438790957631994</v>
+        <v>-0.1944231683246755</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.01049</t>
+          <t>X &gt; -0.01037</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2736</v>
+        <v>2732</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.08778147878339126</v>
+        <v>0.02100963552577184</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.880687474176753</v>
+        <v>0.9023755270946197</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7886124047747103</v>
+        <v>0.884045061566674</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3666732998463473</v>
+        <v>0.5461883173039084</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.8311738422135875</v>
+        <v>1.034266540840939</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5088639279108165</v>
+        <v>0.6457456013844691</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.6827137161921684</v>
+        <v>0.7806017484824181</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6802410209539289</v>
+        <v>0.7148843393384823</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.6700375666896434</v>
+        <v>0.7909636462536085</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6829755438869896</v>
+        <v>0.7806067218976409</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6869951078825594</v>
+        <v>0.8190723325535956</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5388834396223174</v>
+        <v>0.6729820751514453</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.09330087808532284</v>
+        <v>0.2355233184206185</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.07618923817983614</v>
+        <v>0.2275799724563328</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1329244994581771</v>
+        <v>0.3331371675617945</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.4208139792081411</v>
+        <v>0.5878372243770755</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.3452723482361151</v>
+        <v>0.5057160460021919</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.1162347439236626</v>
+        <v>0.211992020964523</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.04791600538423069</v>
+        <v>0.0828150297907726</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.1682907190184721</v>
+        <v>-0.04648894172876794</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.1260415653470801</v>
+        <v>0.06569066285925373</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.05396042646018628</v>
+        <v>0.1585791847702893</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1101613522858145</v>
+        <v>0.05813010070156821</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2590930207137703</v>
+        <v>-0.1921218066899968</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.008043</t>
+          <t>X &gt; -0.007929</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2604</v>
+        <v>2598</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3904864746459893</v>
+        <v>0.3182295410025588</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.667096760744009</v>
+        <v>0.7221698000999055</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4518518806087002</v>
+        <v>0.6524909887281964</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1592264817238558</v>
+        <v>0.4041254871676827</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.4730347864024154</v>
+        <v>0.7784144418695718</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.01040219527396147</v>
+        <v>0.2472746533722443</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2701692163893412</v>
+        <v>0.4296310843716498</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3196785434890899</v>
+        <v>0.3760415390101599</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3832098018622432</v>
+        <v>0.5258725912098754</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5122326506976975</v>
+        <v>0.6322913105907659</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.540815539143658</v>
+        <v>0.6970022619053111</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4375346524592345</v>
+        <v>0.5958789843256156</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.02616853899385774</v>
+        <v>0.1548552476199561</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.05728159022798707</v>
+        <v>0.08254007949387443</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.07941543629308256</v>
+        <v>0.07509701047342787</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.07784904257296432</v>
+        <v>0.2371865641936708</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.005131578020609595</v>
+        <v>0.1560500639795208</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.1152084559292348</v>
+        <v>-0.03087757674377656</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.2987054641202391</v>
+        <v>-0.1778380964817075</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.4347498776677838</v>
+        <v>-0.3249522021087827</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.324454263759776</v>
+        <v>-0.1394195921614951</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.1698854786250976</v>
+        <v>-0.07641040501081875</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.2794353437160169</v>
+        <v>-0.1177375913812924</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.2016577659100989</v>
+        <v>-0.1416550099536806</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.0056</t>
+          <t>X &gt; -0.005492</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2481</v>
+        <v>2467</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2917371562309512</v>
+        <v>0.3406730706821648</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.7996569870946217</v>
+        <v>0.9800781062056529</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7260039091711761</v>
+        <v>0.8521445676943458</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2939487661329281</v>
+        <v>0.5816739584233517</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7205981009692835</v>
+        <v>1.070703343474925</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5865369997472456</v>
+        <v>0.7447395651671727</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6572849450703728</v>
+        <v>0.7775556986525629</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8438284802031575</v>
+        <v>0.8984616314459188</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.78819494319238</v>
+        <v>1.009369073960684</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8823231760175361</v>
+        <v>1.083021608172444</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.8585288523697656</v>
+        <v>1.015984607070308</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8446131759421434</v>
+        <v>1.045278461002511</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.2843783306380914</v>
+        <v>0.5189949007917036</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1676716344200884</v>
+        <v>0.4157590684251673</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.1371233518208044</v>
+        <v>0.3633727041600565</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2726540770019028</v>
+        <v>0.5044485935431808</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.1225236299344985</v>
+        <v>0.3842040555106436</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.03883353732882</v>
+        <v>0.1136324401949125</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.2019548040170918</v>
+        <v>-0.0119696126436537</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2972532907036367</v>
+        <v>-0.05678380068920319</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.235204537267002</v>
+        <v>0.08782094285540154</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.1901315143955742</v>
+        <v>-0.003755639767952346</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.07688211428756375</v>
+        <v>0.1829328447607637</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.07210171132381049</v>
+        <v>0.08540687201532648</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003157</t>
+          <t>X &gt; -0.003055</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2267</v>
+        <v>2246</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.5569550843702373</v>
+        <v>0.6774351366706668</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.5738266376687733</v>
+        <v>0.7850413367599955</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7621812150114025</v>
+        <v>0.9885885075153311</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.664611810953275</v>
+        <v>0.9706449918710618</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.076074085658753</v>
+        <v>1.402112923358118</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9993040080198696</v>
+        <v>1.205533493563003</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.106476203250395</v>
+        <v>1.294234070813268</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8722208024533629</v>
+        <v>1.059094162542436</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.045576116236191</v>
+        <v>1.34532176794383</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8260156162461811</v>
+        <v>1.061691356668085</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6420387540111392</v>
+        <v>0.917186252103086</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4770327436095059</v>
+        <v>0.7549388107749664</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.205988478176188</v>
+        <v>0.06462873372756661</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.09286265482558775</v>
+        <v>0.1527006329464342</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.1962424819483388</v>
+        <v>0.07322587553652937</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.1160236120571057</v>
+        <v>0.350432837042959</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.03571287210654361</v>
+        <v>0.1841294940079905</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.02605516338490332</v>
+        <v>0.121981939835436</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.2953865438191983</v>
+        <v>-0.08142813449443054</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4173188547157523</v>
+        <v>-0.1961965440679592</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.4746422613231545</v>
+        <v>-0.159540457533069</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.4181547423617289</v>
+        <v>-0.2083567504802843</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.2319023501266955</v>
+        <v>0.06164741394323414</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.4400680837205044</v>
+        <v>-0.2076692122615071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0007145</t>
+          <t>X &gt; -0.0006176</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2056</v>
+        <v>2033</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7502251815704639</v>
+        <v>0.6301404754033086</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3184081115078783</v>
+        <v>0.3354293449215007</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6756340891629691</v>
+        <v>0.7888855602578388</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7875223792786983</v>
+        <v>0.9285477831187237</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.470654759715408</v>
+        <v>1.53146694902231</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.172419587248982</v>
+        <v>1.102749017685113</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.516434028055386</v>
+        <v>1.430165785345025</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.480823262584209</v>
+        <v>1.418071110604046</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.764911123780813</v>
+        <v>1.769765805427248</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.991533799849769</v>
+        <v>1.979330379455597</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.711950189796696</v>
+        <v>1.791888810393871</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.433200786348699</v>
+        <v>1.495278510316503</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.650009579133183</v>
+        <v>0.6538805244165999</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4774979683495388</v>
+        <v>0.630460706263726</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.4315429305174732</v>
+        <v>0.467170336751245</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.5691946199967646</v>
+        <v>0.5679350009786361</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.610393675426721</v>
+        <v>0.6403186274509736</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.8460198976755748</v>
+        <v>0.831002399661017</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.3323392941641075</v>
+        <v>0.3879957700051051</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.4705469718364128</v>
+        <v>0.5335694516774225</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.5602965237147401</v>
+        <v>0.7811308384194646</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.5817268268970821</v>
+        <v>0.5881142595138513</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.7102871424919712</v>
+        <v>0.8612714291821675</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.6344548892686959</v>
+        <v>0.7778725542894236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001728</t>
+          <t>X &gt; 0.001819</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1824</v>
+        <v>1794</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.118452667749644</v>
+        <v>1.09825724978996</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7289712742138406</v>
+        <v>0.7418531765170258</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7679762952047255</v>
+        <v>0.868374544238705</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6567728228079446</v>
+        <v>0.8284585332757857</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.196255873236595</v>
+        <v>1.27113243737535</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9455852978460157</v>
+        <v>0.9308284743126478</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.377137708047563</v>
+        <v>1.295967456555076</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.755381405526435</v>
+        <v>1.54353320099176</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.796868587441139</v>
+        <v>1.703743918334929</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.315184965482857</v>
+        <v>2.156824100030924</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.91036848215461</v>
+        <v>1.798001673318062</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.124499692069158</v>
+        <v>2.052454129754011</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.494218238575577</v>
+        <v>1.469184826989903</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.711255462895693</v>
+        <v>1.753162962521365</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.360573642606617</v>
+        <v>1.492884906493806</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.516604400166045</v>
+        <v>1.644125047315093</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.635420981044852</v>
+        <v>1.796021885989262</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.859527645644725</v>
+        <v>1.974754783727285</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.362699728323435</v>
+        <v>1.500624582981018</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.604370099694975</v>
+        <v>1.804495582986803</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.774543229974554</v>
+        <v>2.049862942679667</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.753521829968967</v>
+        <v>1.953228107923913</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.973171981047507</v>
+        <v>2.342497275039371</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.842515166420725</v>
+        <v>2.047448519645876</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.004171</t>
+          <t>X &gt; 0.004256</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1545</v>
+        <v>1519</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.6577954205046836</v>
+        <v>0.7598504557225212</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.193736139931211</v>
+        <v>0.3183764752989617</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.018160529814246</v>
+        <v>1.149731917084047</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.274825127048942</v>
+        <v>1.40478734539446</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.84401203006729</v>
+        <v>2.04187588065367</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.837054492829182</v>
+        <v>1.807675197212376</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.164006907839926</v>
+        <v>2.120807005057884</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.855414079764287</v>
+        <v>2.728533237007809</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.832260020567162</v>
+        <v>2.791273098452017</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.068475233427186</v>
+        <v>2.882056307109409</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.95443655734848</v>
+        <v>2.932623198833127</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.999102419101007</v>
+        <v>2.825984266977137</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.716820041766233</v>
+        <v>2.600211568249655</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.754473377480053</v>
+        <v>2.784444367552553</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.589637791207934</v>
+        <v>2.600767928681961</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>2.601500441306264</v>
+        <v>2.6788845047178</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.467583304328791</v>
+        <v>2.549898973350807</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.815817034164574</v>
+        <v>2.982040758226368</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.190284466868832</v>
+        <v>2.449934421196765</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.57130503411841</v>
+        <v>2.770550373565364</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>2.934907733466297</v>
+        <v>3.294820043761412</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3.117961448432595</v>
+        <v>3.392360140682804</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>3.198261403633097</v>
+        <v>3.611556064073227</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>3.057704231315974</v>
+        <v>3.359113545997339</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.006614</t>
+          <t>X &gt; 0.006694</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1276</v>
+        <v>1249</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.288730351356769</v>
+        <v>1.362436563028645</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5627172462776855</v>
+        <v>0.8791879551728741</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.8461379468554568</v>
+        <v>1.12765841024332</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.7591620181795378</v>
+        <v>1.089053679789529</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.831822249857616</v>
+        <v>2.237546172601583</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.940541174609145</v>
+        <v>2.236251930498398</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.325087013410503</v>
+        <v>1.678511690417579</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.53357353422863</v>
+        <v>2.718527955869718</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.340318932105774</v>
+        <v>2.846456865553826</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.867030830967913</v>
+        <v>3.1268683828524</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.297707544390605</v>
+        <v>3.526400741214786</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.17557521220337</v>
+        <v>3.456620170697811</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.383658251063771</v>
+        <v>3.580603725112397</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.240887910247572</v>
+        <v>3.38179160349042</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3.102060308986999</v>
+        <v>3.305576525390777</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.991118077324977</v>
+        <v>3.200912034636701</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.778831034391395</v>
+        <v>2.987327494692138</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>3.222579672262995</v>
+        <v>3.382014633218212</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.046621523406756</v>
+        <v>3.32744135962372</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.684877991682001</v>
+        <v>3.033137498673909</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.552990130925991</v>
+        <v>4.032667083766782</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.947363605253578</v>
+        <v>4.487815137631991</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>4.30020822369174</v>
+        <v>4.942608695652176</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>4.06763615855624</v>
+        <v>4.67171069415695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.009057</t>
+          <t>X &gt; 0.009131</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>985</v>
+        <v>961</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.587579282507122</v>
+        <v>1.580324091561536</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.8467111135989285</v>
+        <v>1.027040206677327</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6269661762430658</v>
+        <v>0.5920182359332955</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.538377639033833</v>
+        <v>1.331583250239831</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.725429806080456</v>
+        <v>2.695369372435579</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.115441677457028</v>
+        <v>2.749843962040224</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.140447308287484</v>
+        <v>1.749843917020605</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.283555660488723</v>
+        <v>2.776890686726752</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.817428629205466</v>
+        <v>2.392524514443636</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.668878435402483</v>
+        <v>3.093005175592523</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.942938077564406</v>
+        <v>3.324804240109991</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.66418867411641</v>
+        <v>3.007703219518746</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.556255033656221</v>
+        <v>2.983895906182354</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.233653314570041</v>
+        <v>2.593154650519892</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.18464707282704</v>
+        <v>2.592941513180257</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.575988309490846</v>
+        <v>3.115200071167735</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.442071172513373</v>
+        <v>2.868887741046834</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.540276153971377</v>
+        <v>3.006927597699487</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.756167534895702</v>
+        <v>3.285835368360978</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.130830603746979</v>
+        <v>2.839612321792721</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.095898648978924</v>
+        <v>3.062269512412072</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.730712586046984</v>
+        <v>3.7788495997819</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>4.411278669087409</v>
+        <v>4.607972521016002</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>4.030877887945351</v>
+        <v>4.20007427992671</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.0115</t>
+          <t>X &gt; 0.01157</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.418285606673152</v>
+        <v>1.543238529485173</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.5578846296111237</v>
+        <v>0.6368297122753646</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.0916981513515438</v>
+        <v>-0.2215632007126587</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2790279920820566</v>
+        <v>-0.8139653995208818</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.224866160863449</v>
+        <v>0.7598820085964277</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.411832346960828</v>
+        <v>0.7847152182933286</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.1142594843582501</v>
+        <v>-0.5387683791441447</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.807138709776005</v>
+        <v>1.137817121965064</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.242844025724871</v>
+        <v>1.662047220552743</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.835237153893367</v>
+        <v>3.324181406768759</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.452266572665017</v>
+        <v>2.882305905938075</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.173517169217021</v>
+        <v>2.552849217157927</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.970197415107293</v>
+        <v>2.314556801694955</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.354900404626541</v>
+        <v>1.615466590393233</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.616599419792365</v>
+        <v>1.945969091529399</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.342392386413408</v>
+        <v>2.722630411725</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.602693383470097</v>
+        <v>2.968193702714728</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.760664769005032</v>
+        <v>3.185687641718971</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.107962194607417</v>
+        <v>3.751466006857001</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>4.163401959897385</v>
+        <v>3.916165684111959</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.620855791931355</v>
+        <v>3.701385054476738</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.202040053912533</v>
+        <v>4.517468834029714</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.264951034462925</v>
+        <v>5.789338170753119</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.137870423815194</v>
+        <v>4.636642208101257</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.01394</t>
+          <t>X &gt; 0.014</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.843023854309969</v>
+        <v>1.797179097132116</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.863085765637571</v>
+        <v>1.227647665958997</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3928086520904586</v>
+        <v>0.4583904572712996</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.1637256003896468</v>
+        <v>-0.2958240392715581</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.247289966552046</v>
+        <v>1.855802286648526</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.079417442972009</v>
+        <v>2.336360488115872</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.501017146178434</v>
+        <v>0.8940292849446365</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.835708927231806</v>
+        <v>2.207231818882299</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.361067076888446</v>
+        <v>2.820597621770297</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.039764304077764</v>
+        <v>3.157232210693344</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.120275559142918</v>
+        <v>4.400341011705443</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.357655187952979</v>
+        <v>3.413306035251807</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.20223505658074</v>
+        <v>3.209030853539531</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.174704567230926</v>
+        <v>2.248358823570882</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.80688385029552</v>
+        <v>2.968709671949853</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>4.078690127077223</v>
+        <v>3.468905561262801</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.589934280422341</v>
+        <v>3.793913398692808</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>4.485093576601159</v>
+        <v>3.60032306887004</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.700984957525485</v>
+        <v>4.081748887011493</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>4.08137915459028</v>
+        <v>3.578953975910153</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.700123309204891</v>
+        <v>3.607557784960669</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>4.753309605860302</v>
+        <v>4.789386071988297</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.511655286084292</v>
+        <v>5.964126847467362</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>4.79066174253844</v>
+        <v>5.413858131114786</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01639</t>
+          <t>X &gt; 0.01644</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.457192102254311</v>
+        <v>1.793341651336043</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.9263368725319481</v>
+        <v>1.745063274130196</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2726315489911499</v>
+        <v>0.6879976307366391</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.04816560770649403</v>
+        <v>-0.1020330265696074</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.557220390334471</v>
+        <v>2.389207252303386</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.136343439176947</v>
+        <v>2.348512399803447</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.776159461168952</v>
+        <v>1.355801929072705</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.066575467396262</v>
+        <v>2.236652236652233</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.108062649310966</v>
+        <v>2.166952687838318</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.099852855627418</v>
+        <v>2.951928860603161</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.746461517397179</v>
+        <v>4.607563084693666</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.663790545321731</v>
+        <v>4.330981130222369</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.109255929446014</v>
+        <v>4.724718136553541</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.299941758881772</v>
+        <v>4.403798235107857</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.426112186791407</v>
+        <v>4.642704789194276</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>5.432263814616761</v>
+        <v>4.535113811459404</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>5.494425109011829</v>
+        <v>4.757672155688617</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>5.389584405190647</v>
+        <v>4.752532561505063</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>6.193711080232625</v>
+        <v>5.696453706486508</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.596243164710458</v>
+        <v>5.0370029204568</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>4.661540133999331</v>
+        <v>4.396832909391456</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.154321623570617</v>
+        <v>6.132535578583052</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>7.113253856942499</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.549042514201936</v>
+        <v>7.354340669104651</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01883</t>
+          <t>X &gt; 0.01888</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.389303640336884</v>
+        <v>2.659904917459023</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.557039404801131</v>
+        <v>2.920327195679207</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.375301762805314</v>
+        <v>2.425126764673692</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.662347743362574</v>
+        <v>1.073230894979403</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.83912008488565</v>
+        <v>3.329318324500321</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.026086270983029</v>
+        <v>2.979922816574351</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.254137587092679</v>
+        <v>2.438005361303659</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.478438705153678</v>
+        <v>2.386249474857067</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.766157042847276</v>
+        <v>1.754684713655095</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.254547899474105</v>
+        <v>2.983949674131964</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.031120104450103</v>
+        <v>3.762513802660351</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.254883263816168</v>
+        <v>3.739096405151081</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.639258885402263</v>
+        <v>3.890027072510428</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.418180008955673</v>
+        <v>3.800502771406308</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.01631811841029</v>
+        <v>4.550130464152154</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>5.856936196132182</v>
+        <v>4.509705241656981</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.969250214933595</v>
+        <v>3.801017689684564</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>5.115665792519451</v>
+        <v>4.085865894838392</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.08532601766489</v>
+        <v>5.234346973740813</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.267146702004766</v>
+        <v>4.841375048142808</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>4.473344252631698</v>
+        <v>4.438426138013838</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>5.402523416850748</v>
+        <v>5.655253280141245</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.933279536367976</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.606191001737663</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.02127</t>
+          <t>X &gt; 0.02132</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.14148727142608</v>
+        <v>3.37561226560009</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.068540126073117</v>
+        <v>4.38756706511635</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.785095209534227</v>
+        <v>5.648596233665018</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.125768950343861</v>
+        <v>3.798332399636671</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.367265544042645</v>
+        <v>4.780635894757459</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.976944663893967</v>
+        <v>3.365242456730385</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.151368219751241</v>
+        <v>3.828022079717798</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.873156774998165</v>
+        <v>3.208636227504144</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.021899477417605</v>
+        <v>1.135307275553032</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.826270867627173</v>
+        <v>1.911582824358852</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.784873096539883</v>
+        <v>1.869352430158152</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.452495932839518</v>
+        <v>2.221701293296917</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.222078345478678</v>
+        <v>2.679136219871303</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.000999469032088</v>
+        <v>2.430902158438194</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5.2356006509468</v>
+        <v>3.8349331226635</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.883615333142146</v>
+        <v>3.647524926492942</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.380613022663098</v>
+        <v>4.377480158730151</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.275772318841916</v>
+        <v>4.446800077428627</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>5.807121113015462</v>
+        <v>5.184247184816968</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.732137269986637</v>
+        <v>4.322606874735456</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>3.243218862272968</v>
+        <v>2.993557954194038</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.429202553860712</v>
+        <v>4.204569065679266</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>6.596421745838029</v>
+        <v>6.377464001118419</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>7.4669617323624</v>
+        <v>7.179955231909339</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.02371</t>
+          <t>X &gt; 0.02375</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.810765789793848</v>
+        <v>3.429484825674265</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.685666410798866</v>
+        <v>4.378797113476374</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.876679619832387</v>
+        <v>6.311354007600727</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.550822374583198</v>
+        <v>3.726919936282542</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.844064160100437</v>
+        <v>6.63861279219914</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.014901313939752</v>
+        <v>4.80351452568727</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.452630049404242</v>
+        <v>5.602058011462518</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.384096024006006</v>
+        <v>6.093950317057882</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.409454173662645</v>
+        <v>3.83144097973004</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.249441723432604</v>
+        <v>4.629014982518669</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.523501365594527</v>
+        <v>4.901249997123003</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.841526155694922</v>
+        <v>3.827855293647723</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.121589895290413</v>
+        <v>2.712963176196951</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.900511018843822</v>
+        <v>2.464729114763841</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.85527094706972</v>
+        <v>3.376200230886752</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>5.449657869012711</v>
+        <v>4.189297078391675</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>5.315740732035238</v>
+        <v>4.339231927710841</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.001222608859216</v>
+        <v>3.252532561505063</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.813888183331926</v>
+        <v>3.315172926302658</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.194282380396729</v>
+        <v>2.970199119888683</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.442058793075859</v>
+        <v>1.430463262941331</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>2.979116057473213</v>
+        <v>2.987953802210541</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>4.060042382858491</v>
+        <v>4.047914818101162</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>6.403564968344888</v>
+        <v>6.334755415648424</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.02616</t>
+          <t>X &gt; 0.02619</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>179</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5682214151079421</v>
+        <v>0.5114273259434583</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.1249347474361</v>
+        <v>5.130385355104451</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.480211787790573</v>
+        <v>6.57839395591558</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.884576204102025</v>
+        <v>6.52653229764789</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.342081820940223</v>
+        <v>8.413136319710716</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.087707224914709</v>
+        <v>9.110610466249348</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.198440105270173</v>
+        <v>7.774987913476082</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.478887878394175</v>
+        <v>7.470067470067463</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.844397406677594</v>
+        <v>5.435834217589409</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.306118602149496</v>
+        <v>6.801944884532233</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.462859808557234</v>
+        <v>5.993098818055486</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.62545118723213</v>
+        <v>4.635435782503109</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.06094833825312</v>
+        <v>3.520543665052337</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.957187897560715</v>
+        <v>4.353390684700308</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>5.857703817857249</v>
+        <v>4.2117768433558</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>5.893431521923148</v>
+        <v>4.576253600130805</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.759514384945675</v>
+        <v>4.819842896174869</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>4.537355245370307</v>
+        <v>3.939345748318246</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.635928190540426</v>
+        <v>3.397934015170172</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.264114782631367</v>
+        <v>3.403803455932042</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.604250178911144</v>
+        <v>2.066650698809532</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.087063435379136</v>
+        <v>2.55014739473134</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.361538147861189</v>
+        <v>2.793781880009718</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.637661201900492</v>
+        <v>5.983598192982832</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.0286</t>
+          <t>X &gt; 0.02863</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4493577517298419</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.761964740700492</v>
+        <v>3.554123778842879</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.288484698761692</v>
+        <v>6.495233872755492</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.575530679318952</v>
+        <v>6.602132373247969</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.076619639395801</v>
+        <v>7.725175631750027</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.845146109181123</v>
+        <v>7.182808538447418</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.073197425290772</v>
+        <v>6.387726526214699</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.504205838693721</v>
+        <v>6.08280608280608</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.999593729828277</v>
+        <v>2.014930796685988</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.772777344571935</v>
+        <v>4.71538279797015</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.046836986733858</v>
+        <v>4.987617812574484</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.768087583285862</v>
+        <v>4.711035858103187</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>6.063365232741809</v>
+        <v>4.994745139253808</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.842286356295219</v>
+        <v>4.746511077820699</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.893362916870679</v>
+        <v>4.763657395236343</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>5.778529980657652</v>
+        <v>4.625660714755305</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>5.644612843680179</v>
+        <v>4.969923708920184</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>4.121332423546932</v>
+        <v>3.873099937391594</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.628003946315232</v>
+        <v>3.824137645793691</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.105629898127226</v>
+        <v>3.324438376566967</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.853863872005164</v>
+        <v>2.042708160900517</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>2.487237768752095</v>
+        <v>2.681831353230947</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.470932339390181</v>
+        <v>3.639751552795033</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>7.049041129934146</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.03104</t>
+          <t>X &gt; 0.03106</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>103</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.7280849254029818</v>
+        <v>2.117750630379966</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.3933081270531673</v>
+        <v>1.871843794676096</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.751405582876544</v>
+        <v>6.277527051275079</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.009325349841568</v>
+        <v>6.628521078881953</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.615282450109845</v>
+        <v>7.296359165197714</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.831374849799452</v>
+        <v>6.509896544780702</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.117678593093558</v>
+        <v>4.771418306132887</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.781214721156026</v>
+        <v>5.409894089139364</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.939206757439649</v>
+        <v>0.8208418667480046</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.137164867810931</v>
+        <v>0.9681865979437561</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.411224509972854</v>
+        <v>1.24042161254809</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.103348892932623</v>
+        <v>1.90723588449189</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.921934398892049</v>
+        <v>2.679136219871303</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.67172930885323</v>
+        <v>3.37429838485329</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4.984459797680437</v>
+        <v>3.635540229383331</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.578846719623428</v>
+        <v>4.196844248202993</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>5.444929582645955</v>
+        <v>4.694940476190467</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>3.398341306009236</v>
+        <v>3.252532561505063</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.614232686933562</v>
+        <v>4.073790905155697</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>2.83020471049381</v>
+        <v>3.317503563806902</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.34591096971225</v>
+        <v>0.808311489610638</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>1.240938794710914</v>
+        <v>1.704022754063118</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>3.457161080008511</v>
+        <v>3.889404812157039</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>6.293950186008537</v>
+        <v>6.639887177090877</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.03349</t>
+          <t>X &gt; 0.0335</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>82</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.01768947193389181</v>
+        <v>1.219278033794168</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.9024248687060279</v>
+        <v>2.163847388566488</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.78147899040674</v>
+        <v>6.861534239055857</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.28803716608595</v>
+        <v>7.459608230723823</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.61078327890453</v>
+        <v>10.75547866205305</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8.358725074758013</v>
+        <v>7.340983696622573</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.367264195745705</v>
+        <v>6.545901684389854</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.528077141236537</v>
+        <v>7.431457431457432</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.911027737785382</v>
+        <v>3.987957769712956</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.138112061748892</v>
+        <v>3.191906274493618</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.412171703910815</v>
+        <v>3.464141289097952</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.352934495584769</v>
+        <v>4.378035525102852</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.668796818972559</v>
+        <v>5.644095788604467</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.447717942525969</v>
+        <v>5.395861727171358</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.228599035189312</v>
+        <v>7.094659726238667</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>10.04249815225424</v>
+        <v>8.846439935534534</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>9.908581015276766</v>
+        <v>9.560115461847381</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>6.145203726089747</v>
+        <v>6.606191098090434</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.361095107014073</v>
+        <v>6.820653325236208</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.108916526738192</v>
+        <v>4.596215380051284</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.346858163650211</v>
+        <v>2.809258683548599</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>3.49052439736306</v>
+        <v>3.953608356715264</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>6.204023500089022</v>
+        <v>6.63626723223755</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>7.347703441987697</v>
+        <v>7.693640433070037</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.03593</t>
+          <t>X &gt; 0.03594</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01765870763485822</v>
+        <v>0.7430875576036868</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.546115218653</v>
+        <v>3.354323579042671</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.905197618897368</v>
+        <v>6.385343762865382</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.641518961773464</v>
+        <v>8.65008442120002</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>8.374526281100685</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.49269467532357</v>
+        <v>7.102888458527332</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5.271470629114383</v>
+        <v>4.87923501772319</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>9.341085271317823</v>
+        <v>8.860028860028848</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5.034746366276011</v>
+        <v>4.702243483998679</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.711106052558357</v>
+        <v>5.334763417350764</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>5.98516569472028</v>
+        <v>5.606998431955098</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>7.155691653591134</v>
+        <v>6.758987906055239</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8.931080311372703</v>
+        <v>8.501238645747314</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>8.710001434926113</v>
+        <v>8.253004584314205</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>10.95040886198323</v>
+        <v>10.42799305957201</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>12.99407114624506</v>
+        <v>12.4178685069631</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>11.41087864694875</v>
+        <v>11.89990942028985</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>7.419199228171721</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>4.462398322425706</v>
+        <v>4.949697175738798</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>2.470576792140839</v>
+        <v>2.932977312039228</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>3.844006193050575</v>
+        <v>4.307090152402779</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>8.39047473926589</v>
+        <v>8.73641173034823</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.03491</t>
+          <t>X &lt; -0.03474</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.466934069953709</v>
+        <v>-0.6854838709677367</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.096839856334164</v>
+        <v>1.925752150471247</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.108096169622009</v>
+        <v>2.09962947715109</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.844417512498111</v>
+        <v>2.935798706914305</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.839199047005678</v>
+        <v>-1.625473718899322</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.10150822322715</v>
+        <v>-2.897111541472661</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-6.322732269436337</v>
+        <v>-5.120764982276818</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.151668351870576</v>
+        <v>-3.997113997113999</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.110181169955872</v>
+        <v>-3.869185087429891</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.984546121354676</v>
+        <v>-1.808093725506374</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.159761841511589</v>
+        <v>-2.964430139473471</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.539960520321912</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2354281374596496</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.912899985650739</v>
+        <v>3.96729029859992</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-2.093069398886335</v>
+        <v>-1.000578368999413</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.399868247694343</v>
+        <v>2.417868506963103</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-3.081874976239661</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-3.186715680060843</v>
+        <v>-2.104610295637798</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-2.970824299136517</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.56384759778804</v>
+        <v>2.610152662281251</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.4279739324968403</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-1.953095256224778</v>
+        <v>-0.8895972181976219</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-1.678620543742724</v>
+        <v>-0.6459627329192443</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.3051774346471632</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.03247</t>
+          <t>X &lt; -0.0323</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>97</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.063527525803096</v>
+        <v>-0.9653071404817268</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.6635513459501752</v>
+        <v>0.8506416939174883</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.380171472176919</v>
+        <v>4.750586767283643</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.5744339475795357</v>
+        <v>1.065401063320778</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.269571310083805</v>
+        <v>1.820770758272985</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.6053181739219013</v>
+        <v>-0.08415130583201602</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.377266857812252</v>
+        <v>-0.8792333180647347</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.6245504675137852</v>
+        <v>-0.1532259264218112</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.4478645494524613</v>
+        <v>1.00563081831384</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.7058767084675281</v>
+        <v>1.240507158146059</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.9799363506294512</v>
+        <v>1.512742172750393</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.79397045233609</v>
+        <v>4.328943723433731</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.763591890634608</v>
+        <v>6.306835111137595</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.57344084923956</v>
+        <v>7.089528884756028</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>3.853441881555909</v>
+        <v>4.34551883276788</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>4.447828803498901</v>
+        <v>4.906822851587542</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.221128161366792</v>
+        <v>1.710158934707898</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.08535962249406737</v>
+        <v>0.5463469944947548</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.3012510034183933</v>
+        <v>0.7608092216405282</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>3.580880318541055</v>
+        <v>4.068179171854148</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>3.038334150575025</v>
+        <v>3.500734670473413</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.931560354114382</v>
+        <v>2.394644313466586</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3.236962901647978</v>
+        <v>3.669206633796506</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>5.222986318527795</v>
+        <v>5.568923309610135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.03003</t>
+          <t>X &lt; -0.02986</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.027943887625518</v>
+        <v>-2.761376728110598</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.7498174601688845</v>
+        <v>-0.6635335638144682</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.683918014796987</v>
+        <v>0.4255223342939516</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.655052264808361</v>
+        <v>-0.1668798645142715</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.4481816528882661</v>
+        <v>1.901311995386394</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.357388479820159</v>
+        <v>-0.2855043986155223</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.309665032562975</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.407548608463586</v>
+        <v>-1.38550685425686</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.546389295401347</v>
+        <v>-1.257577944572752</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.499632840290296</v>
+        <v>-1.27237943979209</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.233443195314251</v>
+        <v>1.343605574812244</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.233382316456421</v>
+        <v>4.192023620340947</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.847925167633086</v>
+        <v>8.545881502890175</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.807174160038954</v>
+        <v>7.516397441457066</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.509686600163313</v>
+        <v>5.27174305957201</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>5.284401390958777</v>
+        <v>5.051797078391672</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>4.330812122833763</v>
+        <v>4.166666666666664</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.766955025569949</v>
+        <v>1.690032561505063</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.441862799936906</v>
+        <v>4.248244788650837</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>6.268052872200002</v>
+        <v>6.025331233709821</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>5.725506704233972</v>
+        <v>5.457886732329086</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>4.010316480529802</v>
+        <v>3.820224210373802</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.104463324159397</v>
+        <v>4.845108695652179</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.66797533323119</v>
+        <v>6.245469701362715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02759</t>
+          <t>X &lt; -0.02742</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.250603210992942</v>
+        <v>-4.152382825671573</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.9268434239768979</v>
+        <v>-0.7397530760095847</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1989190344324001</v>
+        <v>-0.1651788852182392</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9286177436708698</v>
+        <v>1.681443306217432</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.819821136154268</v>
+        <v>2.625397361240047</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.5147021900847122</v>
+        <v>0.9530626745552055</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3600374568116465</v>
+        <v>0.7677367598834621</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.5354579385587144</v>
+        <v>-0.1469397810861324</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4939707566440106</v>
+        <v>-0.6287669689629922</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.501454333915063</v>
+        <v>-2.644330659304281</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.9928267905185777</v>
+        <v>-1.152583449577996</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.197559608502559</v>
+        <v>1.009858986194601</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.629953097201998</v>
+        <v>5.382771746792621</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.55702236890356</v>
+        <v>3.305269392676578</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>3.516163021940294</v>
+        <v>3.232871108352498</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.258698092031423</v>
+        <v>1.964906834489234</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>2.12478095505395</v>
+        <v>1.861026422764226</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.4491955512363717</v>
+        <v>-0.710882072641283</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.001263730922531</v>
+        <v>0.723092349626441</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.422677442125121</v>
+        <v>2.157190989807383</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.11469917539366</v>
+        <v>2.809258683548599</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.038853213984559</v>
+        <v>2.734096161593314</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>3.930611877083905</v>
+        <v>3.587486744432667</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.472063574477907</v>
+        <v>4.035103847704178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.02514</t>
+          <t>X &lt; -0.02499</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.943172694827311</v>
+        <v>-2.625195535450054</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.639175313650945</v>
+        <v>-1.494955582163094</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.9535490640991569</v>
+        <v>-0.4560717024032996</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2114311887585743</v>
+        <v>1.245104080439859</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8146078523615401</v>
+        <v>1.428261536670796</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1433457950072921</v>
+        <v>0.2090483536780496</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4997998607249983</v>
+        <v>0.7901131304361613</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2501096972356223</v>
+        <v>0.02647709069727</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.152018741736015</v>
+        <v>-1.221740788609452</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.396632530980057</v>
+        <v>-2.935223476489341</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.594271002025671</v>
+        <v>-3.121704058215279</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.428866386979152</v>
+        <v>-0.1872768383746504</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.607591112575868</v>
+        <v>1.90884021848651</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.443116009714188</v>
+        <v>0.7431749643928427</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.7849727121336301</v>
+        <v>0.06102058250778697</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.4359634076615251</v>
+        <v>-0.295106591333095</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.6413499557310445</v>
+        <v>-1.316418195718661</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.161284999174867</v>
+        <v>-2.366733493540806</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.356493174202292</v>
+        <v>1.058737907916885</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.015037097377856</v>
+        <v>1.732039949306156</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>1.944189042619378</v>
+        <v>1.623311044255694</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.340041194417822</v>
+        <v>2.006864118630681</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>3.557912133314971</v>
+        <v>3.167929796569616</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.482079880091696</v>
+        <v>3.005790802280153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.0227</t>
+          <t>X &lt; -0.02255</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.52973600232086</v>
+        <v>-2.114055299539174</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.559267034458358</v>
+        <v>-2.717104992385899</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9360310205142639</v>
+        <v>-2.186084808563187</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.55130564146733</v>
+        <v>0.0786558497714438</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.07141000919376239</v>
+        <v>-1.625473718899322</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3283523182002526</v>
+        <v>-0.3971115414726611</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6884791060080104</v>
+        <v>-0.4779078394196716</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.03290917068890309</v>
+        <v>-0.7828282828282909</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.057679119094509</v>
+        <v>-2.083470801715613</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.45323630456496</v>
+        <v>-2.522379439792083</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.443327605799261</v>
+        <v>-4.393001568044895</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.05150789641311349</v>
+        <v>-1.098154951087622</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.8151382823871884</v>
+        <v>-0.7844756399669635</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1606575751914789</v>
+        <v>-1.389852558542941</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.8188008727720373</v>
+        <v>-2.072006940427997</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.2244139508290459</v>
+        <v>-2.582131493036897</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.113048068938596</v>
+        <v>-2.686011904761905</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.972605753891855</v>
+        <v>-2.818896009923506</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.8847950609947404</v>
+        <v>-0.8187194970634479</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.826357852094837</v>
+        <v>0.4672955194241055</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2.038528665260884</v>
+        <v>0.9712795894719406</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.340041194417822</v>
+        <v>1.610402781802378</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.369232888031952</v>
+        <v>2.925465838509325</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.670759125374715</v>
+        <v>3.120469701362715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.02026</t>
+          <t>X &lt; -0.02011</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.903383986588302</v>
+        <v>-2.386557363948747</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.27148189994746</v>
+        <v>-3.499516222774005</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.484859578023453</v>
+        <v>-3.020106278422816</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.662311265969805</v>
+        <v>-1.589387089947792</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.731044169220695</v>
+        <v>-3.310031935249441</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.8861997098191807</v>
+        <v>-1.129976941968124</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6102877070619002</v>
+        <v>-0.1909549079580657</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.8691249388923765</v>
+        <v>-1.651944715528536</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.728538657878573</v>
+        <v>-2.969102511046742</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.801754634215371</v>
+        <v>-3.76515400626608</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.428595892954348</v>
+        <v>-4.359971014783127</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.004642593699636</v>
+        <v>-2.035396899890273</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3260028587539594</v>
+        <v>-1.127167630057798</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.8473820355008428</v>
+        <v>-1.664419032531377</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.505525333081401</v>
+        <v>-2.924608096497352</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.712940212940211</v>
+        <v>-4.097408123920466</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.246256749317091</v>
+        <v>-3.623253853564556</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.351097453138273</v>
+        <v>-3.178103276645224</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.3334042704121387</v>
+        <v>-1.229537003256674</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.054642740757096</v>
+        <v>0.1411188059641617</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>1.412997473691952</v>
+        <v>0.4407263277048088</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>2.538352713484059</v>
+        <v>1.521633169911375</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>3.71372832686702</v>
+        <v>2.921337019351604</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.938196373944038</v>
+        <v>3.626250048183522</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01781</t>
+          <t>X &lt; -0.01768</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.389590832024936</v>
+        <v>-3.050015890672178</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.857236002461882</v>
+        <v>-4.527449819972105</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.645966193136012</v>
+        <v>-3.565395153390782</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.949381790382098</v>
+        <v>-2.302296531180936</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.416702173614972</v>
+        <v>-3.812422572514834</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.313589205636703</v>
+        <v>-1.680180324541446</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.9249209710039281</v>
+        <v>-1.487608015786513</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.223540579022313</v>
+        <v>-2.780182780182784</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.202461560372903</v>
+        <v>-3.886821771733253</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.975377236409393</v>
+        <v>-4.929786847199502</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.70131759424747</v>
+        <v>-4.657551832595168</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.684148630348524</v>
+        <v>-2.711911564844236</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.531800493123015</v>
+        <v>-2.592235781060445</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.49777732875328</v>
+        <v>-2.593556262246636</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.411022667150164</v>
+        <v>-3.275710644131692</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-3.602350030921457</v>
+        <v>-4.442801687040422</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-3.73626716789893</v>
+        <v>-4.54668209876543</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.586005830903794</v>
+        <v>-3.938825463186298</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-2.09460424589782</v>
+        <v>-2.736708915052866</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.8873502726644986</v>
+        <v>-1.287554568759319</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.1007158042674376</v>
+        <v>-0.3735175886585651</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.456964419819556</v>
+        <v>1.032801370867631</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.401647014785702</v>
+        <v>1.52334943639292</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>3.351455787203449</v>
+        <v>3.089605503831848</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01537</t>
+          <t>X &lt; -0.01524</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.272426060800392</v>
+        <v>-2.03357240215486</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.462268753624613</v>
+        <v>-4.134136756615142</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.160495285340254</v>
+        <v>-3.813767516336135</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.445402314798542</v>
+        <v>-5.303900555220892</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.871165947556463</v>
+        <v>-3.729962900639819</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.889587434604287</v>
+        <v>-3.917757463479823</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.020677344176129</v>
+        <v>-4.425107056686009</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.979190162261425</v>
+        <v>-4.297178147001901</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.686007757274453</v>
+        <v>-4.081083893233384</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.691265812340689</v>
+        <v>-5.225852927212053</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.198160205127699</v>
+        <v>-2.870855934314918</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.042004574755673</v>
+        <v>-2.568744003182694</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.410204986383498</v>
+        <v>-1.804832315627962</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.42868943534998</v>
+        <v>-1.879699248120303</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-3.179718291658588</v>
+        <v>-3.545115877073911</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-3.526855044840751</v>
+        <v>-4.053854588394067</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.84491536486663</v>
+        <v>-3.984309543758087</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.92326705430478</v>
+        <v>-2.352843268029325</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.096762395722671</v>
+        <v>-1.530969373577626</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.5732104826652531</v>
+        <v>-1.086268125970513</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3087251335937893</v>
+        <v>-0.7565723483306499</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.9499366979790267</v>
+        <v>0.09434958634043511</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.720884641610844</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.01293</t>
+          <t>X &lt; -0.0128</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>566</v>
+        <v>590</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.814760156910225</v>
+        <v>-1.522424707908577</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.498271995405474</v>
+        <v>-3.872850595854942</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.104742437252561</v>
+        <v>-3.860795233273613</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.154569008227547</v>
+        <v>-3.182161167390753</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.27324559641049</v>
+        <v>-4.724747326647503</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.59121074038962</v>
+        <v>-3.211881517259584</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.444557999804893</v>
+        <v>-4.17645505491604</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.89851636898679</v>
+        <v>-4.311883972900922</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.857029187072087</v>
+        <v>-4.353446588640551</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.751210240964475</v>
+        <v>-4.302040456741238</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.828644447660189</v>
+        <v>-4.368788492984365</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.174177682391147</v>
+        <v>-2.780963667794644</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.715617429387862</v>
+        <v>-2.200940531008129</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.760949381405631</v>
+        <v>-2.110191541593778</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.540358056842067</v>
+        <v>-1.775396770936467</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.879187303616121</v>
+        <v>-3.078499531777823</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.66161059173595</v>
+        <v>-2.67390536723164</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.766451295557133</v>
+        <v>-2.467806421545781</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.847572216917527</v>
+        <v>-1.575378092705094</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.484979482520664</v>
+        <v>-1.19130012222238</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.148791028342593</v>
+        <v>-0.9112869964844705</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.945236509541779</v>
+        <v>-0.8169579930160324</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.3903757772370966</v>
+        <v>-0.4038319823139176</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.8752394240612915</v>
+        <v>0.9594527522101757</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.01049</t>
+          <t>X &lt; -0.01037</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>676</v>
+        <v>705</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.5796226236360482</v>
+        <v>-0.3031901083922932</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.048616612511708</v>
+        <v>-3.435924254928715</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.805455826309846</v>
+        <v>-3.489555349321869</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.246655545409247</v>
+        <v>-2.170283329860801</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.116346397084314</v>
+        <v>-4.21147129073259</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.824613630875739</v>
+        <v>-2.988296951807015</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.517958185889874</v>
+        <v>-3.783378964039734</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.502051983584131</v>
+        <v>-3.520923520923525</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.460564801669427</v>
+        <v>-3.676682554501831</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.49818636005886</v>
+        <v>-3.763514191565136</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.518244364955763</v>
+        <v>-3.774967120223216</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.914640827227281</v>
+        <v>-3.058641273276073</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.096626423495159</v>
+        <v>-1.194809986471519</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.023587652882931</v>
+        <v>-1.017512133011024</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.24055447987525</v>
+        <v>-1.274134600002462</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.410873440285208</v>
+        <v>-2.131270297494851</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.103614106674449</v>
+        <v>-1.809618794326241</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.17904304578974</v>
+        <v>-0.6659071548069946</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.5219751942771822</v>
+        <v>-0.02591301276760305</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.04101173725032936</v>
+        <v>0.4723613755537883</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2017247595869733</v>
+        <v>0.1886048174354684</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.9270596014857801</v>
+        <v>-0.4539335910446383</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2700190837637066</v>
+        <v>0.07338883749614666</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.3337043079135071</v>
+        <v>0.7623136729939191</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.008043</t>
+          <t>X &lt; -0.007929</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>808</v>
+        <v>839</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.440358115876947</v>
+        <v>-1.172958481665098</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.56803517249169</v>
+        <v>-2.187110076269981</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.982270411793166</v>
+        <v>-2.074106525563529</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.157271826881278</v>
+        <v>-1.295558520875744</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.162633153048489</v>
+        <v>-2.577854671280271</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.6788653011457484</v>
+        <v>-1.16545821267988</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.505498029413495</v>
+        <v>-1.960540224912599</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.660556764806962</v>
+        <v>-1.788702623029209</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.865375001611469</v>
+        <v>-2.13753175863711</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.26883254956914</v>
+        <v>-2.576014719887439</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.364231035486036</v>
+        <v>-2.661348239252114</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.027216892136011</v>
+        <v>-2.222793125785394</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6873247718000002</v>
+        <v>-0.7155159941300866</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4157928108081705</v>
+        <v>-0.3678024989481798</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.335019852231099</v>
+        <v>-0.2156303015722116</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.8490073145245631</v>
+        <v>-0.6078423733365739</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.6134663234232107</v>
+        <v>-0.3541542510925737</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.2256961898059657</v>
+        <v>0.2280987116838489</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.3596533191971716</v>
+        <v>0.8001294727986306</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.7928045478844155</v>
+        <v>1.253094940503622</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.4476671618758274</v>
+        <v>0.8048399504458885</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.04756653910185804</v>
+        <v>0.3721088945215953</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.3009212057780601</v>
+        <v>0.615743379799973</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.05176043305264955</v>
+        <v>0.4536043855105092</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.0056</t>
+          <t>X &lt; -0.005492</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>931</v>
+        <v>970</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.93671137642243</v>
+        <v>-1.029806215290087</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.489424336410231</v>
+        <v>-2.453831305087576</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.384950080897788</v>
+        <v>-2.216917285438832</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.339362937702326</v>
+        <v>-1.52040352706571</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.468777229160615</v>
+        <v>-2.873082958269634</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.117638750713937</v>
+        <v>-2.249099759440263</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.298170377490102</v>
+        <v>-2.52871785414721</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.789828994068152</v>
+        <v>-2.833638297555829</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.641618226240958</v>
+        <v>-3.014987738387184</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.880915972715023</v>
+        <v>-3.29557531608075</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.820303502378067</v>
+        <v>-3.023340301476416</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.778882148088606</v>
+        <v>-2.99064390543225</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.278878811629902</v>
+        <v>-1.528216435254159</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.9657696538884579</v>
+        <v>-1.157893795656342</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.8760497036057728</v>
+        <v>-0.9122131259949953</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.243201243201241</v>
+        <v>-1.175651375216567</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.8429303459906805</v>
+        <v>-0.8671606529209583</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.4135830156238285</v>
+        <v>-0.1753024900413251</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.01598357897570679</v>
+        <v>0.2453453041147569</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.2664748937657109</v>
+        <v>0.3568389656685866</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.1089096599681696</v>
+        <v>0.09867281480331513</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.009854657874441841</v>
+        <v>0.1266030763531845</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.3148710879984904</v>
+        <v>-0.2483191393993636</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.3269710491181215</v>
+        <v>-0.2042725666785188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003157</t>
+          <t>X &lt; -0.003055</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1145</v>
+        <v>1191</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.227054009983689</v>
+        <v>-1.412300913574263</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.430326241376257</v>
+        <v>-1.447396440068651</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.873055741469081</v>
+        <v>-1.905152351898515</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.76186059304721</v>
+        <v>-1.866785643408747</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.569653888788949</v>
+        <v>-2.767851877203718</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.422607413891555</v>
+        <v>-2.566334935528268</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.62795920536179</v>
+        <v>-2.896943463744961</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.16513039795074</v>
+        <v>-2.446196400856351</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.509788657878573</v>
+        <v>-2.906008884958979</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.067426556137285</v>
+        <v>-2.442614536349602</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.706561358419812</v>
+        <v>-2.086416465490025</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.377671872978915</v>
+        <v>-1.691293969919336</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.01891905905502966</v>
+        <v>-0.2872943997126782</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.23999793550162</v>
+        <v>-0.3676023486352875</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.02933150241319282</v>
+        <v>-0.1261631117126285</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.6512782034067897</v>
+        <v>-0.5724157679559383</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.3507904750497701</v>
+        <v>-0.2564808984047104</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.368750205804055</v>
+        <v>-0.1374758348005614</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1596104834721856</v>
+        <v>0.3288755611109551</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.398372893886723</v>
+        <v>0.5434620061699391</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.517589870967285</v>
+        <v>0.5637588985759407</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.4071892919980584</v>
+        <v>0.4885963766206558</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.03622883784919395</v>
+        <v>0.06052641185705454</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.4492051993633481</v>
+        <v>0.4021657550990696</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0007145</t>
+          <t>X &lt; -0.0006176</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1356</v>
+        <v>1404</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.239100388541139</v>
+        <v>-1.026680590619456</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.7345459802449952</v>
+        <v>-0.4552002304811325</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.332010307751545</v>
+        <v>-1.175236182384538</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.567880714755873</v>
+        <v>-1.374266228150638</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.593774314116658</v>
+        <v>-2.321991131834643</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.148321193659385</v>
+        <v>-1.842447855230034</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.661405038315053</v>
+        <v>-2.456809720456775</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.607220020074507</v>
+        <v>-2.438302438302443</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.03812056775331</v>
+        <v>-2.880174098418905</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.371797590788333</v>
+        <v>-3.248875166287817</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.95132506429259</v>
+        <v>-2.905415080458411</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.530564119621161</v>
+        <v>-2.398521251453921</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.340286937554154</v>
+        <v>-1.091760947252276</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.078721225020516</v>
+        <v>-0.9838696525600241</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.00318880726725</v>
+        <v>-0.6688730372940839</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.215845172191464</v>
+        <v>-0.7485946595000712</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.276394737635556</v>
+        <v>-0.8524750712250793</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.632096513873016</v>
+        <v>-1.12780931883681</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.8592056044427139</v>
+        <v>-0.414771593115546</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.070423501956206</v>
+        <v>-0.6275355754069878</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.202200505744436</v>
+        <v>-0.9100797918874406</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.234860853543935</v>
+        <v>-0.7715671001675162</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.432980651824273</v>
+        <v>-1.097733184689694</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.318387643701925</v>
+        <v>-1.117422036529028</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001728</t>
+          <t>X &lt; 0.001819</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1588</v>
+        <v>1643</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.36953410783147</v>
+        <v>-1.300202485686349</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.049098382516526</v>
+        <v>-0.7867142793996678</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.145730188227105</v>
+        <v>-0.9776936851235263</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.076721668534816</v>
+        <v>-0.9301046671857947</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.690085518928797</v>
+        <v>-1.476194079947753</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.406507409027505</v>
+        <v>-1.225379018676307</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.89434059394366</v>
+        <v>-1.743983612794707</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.325581395348827</v>
+        <v>-2.015547176837508</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.374775889481661</v>
+        <v>-2.131075357841162</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.960074304730163</v>
+        <v>-2.683669762372737</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.498397401780238</v>
+        <v>-2.228841929752576</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.742550714586478</v>
+        <v>-2.444559611551931</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.015168542910246</v>
+        <v>-1.73352354884446</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.263083451202263</v>
+        <v>-1.981757610277569</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.856063841514654</v>
+        <v>-1.629219356739618</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.040229885057471</v>
+        <v>-1.737422337311315</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.174147022034944</v>
+        <v>-1.902167021708259</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.431164973607288</v>
+        <v>-2.095915399541802</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.865444785503499</v>
+        <v>-1.516267536364374</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.144913599502772</v>
+        <v>-1.849459545352872</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.337264416104816</v>
+        <v>-2.051718410701952</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.314046855896642</v>
+        <v>-2.066016659985294</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.569710555690818</v>
+        <v>-2.431024901426333</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.420681395513078</v>
+        <v>-2.22797825968415</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.004171</t>
+          <t>X &lt; 0.004256</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1867</v>
+        <v>1918</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6217793168218009</v>
+        <v>-0.6869673303951274</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3455232228575582</v>
+        <v>-0.2300920053729101</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.065816873856257</v>
+        <v>-0.9371985596769434</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.325535972297949</v>
+        <v>-1.137449937317186</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.791474501635058</v>
+        <v>-1.696827962990298</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.787901351676204</v>
+        <v>-1.615784851504642</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.052683446876308</v>
+        <v>-1.966003077514912</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.620637216720446</v>
+        <v>-2.450921783907724</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.603243149604346</v>
+        <v>-2.451041187534173</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.791052442662107</v>
+        <v>-2.569303318832759</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.700459560773304</v>
+        <v>-2.557756521121014</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.7368860192338</v>
+        <v>-2.417237328564156</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.498660332423682</v>
+        <v>-2.176550718173431</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.529607971458127</v>
+        <v>-2.268371849470988</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.388177708271087</v>
+        <v>-2.06418629392121</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.403030303030306</v>
+        <v>-2.076396352265263</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.293048471669103</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.580852034200909</v>
+        <v>-2.313160869151872</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-2.067349754357629</v>
+        <v>-1.838010425113495</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-2.384285230506535</v>
+        <v>-2.092662770461196</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.682488386499784</v>
+        <v>-2.451556698327849</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.834757154007825</v>
+        <v>-2.630994507040171</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.904453023648387</v>
+        <v>-2.752323525411427</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.789205907823536</v>
+        <v>-2.653774302808301</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.006614</t>
+          <t>X &lt; 0.006694</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2136</v>
+        <v>2188</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.8360256020735974</v>
+        <v>-0.8559236315714287</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4969597188318744</v>
+        <v>-0.4855722881880453</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.7036661626689167</v>
+        <v>-0.6676579300633918</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6948421056037049</v>
+        <v>-0.6424698097947115</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.330014020382905</v>
+        <v>-1.349144208993167</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.396239110571578</v>
+        <v>-1.441155357081982</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.0269143485502</v>
+        <v>-1.206870657423586</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.744186046511622</v>
+        <v>-1.806289745988245</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.630301751824078</v>
+        <v>-1.836017158466717</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.937884714970856</v>
+        <v>-2.037918745093734</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.196358068537741</v>
+        <v>-2.222722121714263</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.12318078722619</v>
+        <v>-2.133673363205666</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.241711671014485</v>
+        <v>-2.151673341716773</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.15652334464216</v>
+        <v>-1.9885728510475</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.068745896301969</v>
+        <v>-1.893761967850295</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.007010402532792</v>
+        <v>-1.789496340255496</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.880795627906366</v>
+        <v>-1.664857556368069</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.145429600411596</v>
+        <v>-1.88914933977464</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.042773611729167</v>
+        <v>-1.811798629996332</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.829082105584575</v>
+        <v>-1.642916024059836</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.344757476208848</v>
+        <v>-2.164656686318082</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.580798242897949</v>
+        <v>-2.514042243008284</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.794230263450025</v>
+        <v>-2.727446148954769</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.65617890020652</v>
+        <v>-2.661065947631805</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.009057</t>
+          <t>X &lt; 0.009131</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2427</v>
+        <v>2476</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7020716032278855</v>
+        <v>-0.6843336524262185</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4844030052893373</v>
+        <v>-0.3853922025579237</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4299828300938131</v>
+        <v>-0.2487071177608442</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8344024563486911</v>
+        <v>-0.5368793606851767</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.311120077496163</v>
+        <v>-1.112800907839414</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.469695295335264</v>
+        <v>-1.216134188853523</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.073556529973828</v>
+        <v>-0.8996188967239434</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.53352245142743</v>
+        <v>-1.30318701170539</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.346338275678193</v>
+        <v>-1.112434568159181</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.686669864890533</v>
+        <v>-1.423833397788862</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.799343689931646</v>
+        <v>-1.474700160244304</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.686135895119136</v>
+        <v>-1.307017171258408</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.637691906292055</v>
+        <v>-1.250665346867493</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.506884377399572</v>
+        <v>-1.054634464843417</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.484445139587415</v>
+        <v>-1.009809848343977</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.646288345466992</v>
+        <v>-1.175484827908811</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.592110409057348</v>
+        <v>-1.077426628971466</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.632005981888959</v>
+        <v>-1.129535289868123</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.721181850623928</v>
+        <v>-1.197787117649646</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.469436253910139</v>
+        <v>-1.023588394723141</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.453202059174245</v>
+        <v>-1.06599250838174</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.71085326482855</v>
+        <v>-1.423869085264329</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.989009006842309</v>
+        <v>-1.70527498770808</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.835067619344677</v>
+        <v>-1.625087649202719</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.0115</t>
+          <t>X &lt; 0.01157</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2651</v>
+        <v>2695</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4620886990714652</v>
+        <v>-0.4904624661794088</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2906257823392053</v>
+        <v>-0.1615905586331223</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.1366968530283401</v>
+        <v>0.04747947979561218</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1176115815284362</v>
+        <v>0.2162219873375832</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5447844565481077</v>
+        <v>-0.2609471746765948</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5991380145510377</v>
+        <v>-0.3428385350128593</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.2257807451984561</v>
+        <v>-0.04210615500841897</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.7076586356937895</v>
+        <v>-0.5115268839304505</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8324813102083155</v>
+        <v>-0.6224318406766542</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.284026775024088</v>
+        <v>-1.121637324764265</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.176343640702093</v>
+        <v>-0.960719564334326</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.095871637238098</v>
+        <v>-0.8291382534994938</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.033096127830689</v>
+        <v>-0.7195405750319068</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8565230818459497</v>
+        <v>-0.4853998683759571</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.9287455457752998</v>
+        <v>-0.5367564766060937</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.139497646643193</v>
+        <v>-0.7175674856157457</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.213847364763232</v>
+        <v>-0.7843421459492887</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.259075811624719</v>
+        <v>-0.8430147483279598</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.360033309089367</v>
+        <v>-0.9625042837053783</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.377280708115514</v>
+        <v>-1.007658098386649</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.219778482369605</v>
+        <v>-0.9071990747210137</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.386605037331208</v>
+        <v>-1.204996105025081</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.693375609648683</v>
+        <v>-1.5179478906187</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.370129681269979</v>
+        <v>-1.271923619602035</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.01394</t>
+          <t>X &lt; 0.014</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2792</v>
+        <v>2832</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4614510210696281</v>
+        <v>-0.4462157499262247</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3153538336012502</v>
+        <v>-0.2510467633920825</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2412291677093279</v>
+        <v>-0.1136502009173128</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2233252875101286</v>
+        <v>0.05299288997674267</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6815265492097566</v>
+        <v>-0.4495953337186052</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8661685976662667</v>
+        <v>-0.6255973665393881</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5147960808912444</v>
+        <v>-0.3786735053475425</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.8084873782548172</v>
+        <v>-0.6637806637806705</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.9249919690451023</v>
+        <v>-0.76302519227918</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.07197781534375</v>
+        <v>-0.8686554722664965</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.312362012014582</v>
+        <v>-1.10607662857759</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.143012061598348</v>
+        <v>-0.8529975660997309</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.104233818932833</v>
+        <v>-0.767324711799084</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8763188952728171</v>
+        <v>-0.5212084907463179</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.013744727055887</v>
+        <v>-0.6383911212189517</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.076839826839823</v>
+        <v>-0.7126803227382723</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.189894921251081</v>
+        <v>-0.78125</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.166639227936649</v>
+        <v>-0.7375804328452205</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.21583836700426</v>
+        <v>-0.8056040814056615</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.079680423608998</v>
+        <v>-0.6969498397365044</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.993165397587191</v>
+        <v>-0.6641118552415364</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.22690144547088</v>
+        <v>-0.9864495184397555</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.39686024236817</v>
+        <v>-1.20185458118398</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.236928607771205</v>
+        <v>-1.152129168693783</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01639</t>
+          <t>X &lt; 0.01644</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2902</v>
+        <v>2941</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3075137800986312</v>
+        <v>-0.3605007971695073</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.282053460345395</v>
+        <v>-0.28362330306269</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1964004017980585</v>
+        <v>-0.1313035464648564</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1717715182431903</v>
+        <v>0.006525337112293528</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6253453439359546</v>
+        <v>-0.4535608859695373</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.727476061225957</v>
+        <v>-0.5151903090936472</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4869040376118576</v>
+        <v>-0.4095806442268071</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.7114621355818755</v>
+        <v>-0.559720037154726</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.719130209320312</v>
+        <v>-0.5145153172815071</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.8896573517477151</v>
+        <v>-0.6802741766341995</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.179176662403037</v>
+        <v>-0.9322096425790676</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.163964578690802</v>
+        <v>-0.849866033073944</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.237728178306249</v>
+        <v>-0.8774322925566409</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.09550103361984</v>
+        <v>-0.7858770233747379</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.115269051378881</v>
+        <v>-0.7884527440297546</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.119181505779437</v>
+        <v>-0.7368327211326218</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.129911803477469</v>
+        <v>-0.7727552667346274</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.111480945296172</v>
+        <v>-0.7697236396502234</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.253829339444025</v>
+        <v>-0.8950507431194623</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.150177358075396</v>
+        <v>-0.7824010972449855</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.9842362488429615</v>
+        <v>-0.6362880043341832</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.246423798565175</v>
+        <v>-0.997395606077589</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.399548918687188</v>
+        <v>-1.127656430112609</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.317472803158637</v>
+        <v>-1.236041689320722</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01883</t>
+          <t>X &lt; 0.01888</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3014</v>
+        <v>3050</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.36458764685311</v>
+        <v>-0.3941764834123873</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.451249735233695</v>
+        <v>-0.3616406134228214</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4548291222625238</v>
+        <v>-0.3256305387063776</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3915936842766143</v>
+        <v>-0.1490198057291607</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6760373044348285</v>
+        <v>-0.4717891153617302</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7015426387370667</v>
+        <v>-0.4928164901187841</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5973534543898893</v>
+        <v>-0.4852631843036193</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6259114283521328</v>
+        <v>-0.4775400458853767</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5326911100996981</v>
+        <v>-0.3638811012623222</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7254378947546414</v>
+        <v>-0.5524841518339727</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.828870300166308</v>
+        <v>-0.6216665201141041</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8574696441473151</v>
+        <v>-0.5850105970788277</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9038699820756193</v>
+        <v>-0.5675929484691409</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8741945623133702</v>
+        <v>-0.5210350020411241</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.9506204447329125</v>
+        <v>-0.5808507006638237</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.9323045143693705</v>
+        <v>-0.5436213624861495</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.8151334711232963</v>
+        <v>-0.450973768970421</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.834282625065164</v>
+        <v>-0.4855938715116466</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.9632490870737769</v>
+        <v>-0.5986783197671102</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.8564134446529721</v>
+        <v>-0.5478652124087446</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.7498216264821309</v>
+        <v>-0.4602163629869978</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.8723856110473633</v>
+        <v>-0.6798986598752137</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.075837358221065</v>
+        <v>-0.8758639362717773</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.032700202791958</v>
+        <v>-0.9205139051946674</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.02127</t>
+          <t>X &lt; 0.02132</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3095</v>
+        <v>3126</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3695193392177245</v>
+        <v>-0.3917674028400668</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5267949095360365</v>
+        <v>-0.4297306348109657</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7281487374494873</v>
+        <v>-0.5846289395913971</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5888762739954814</v>
+        <v>-0.3951074051323005</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7141536698869189</v>
+        <v>-0.5255920836448382</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5735259888383979</v>
+        <v>-0.446635654592562</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5885010559942145</v>
+        <v>-0.5544384516645664</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5592683127387374</v>
+        <v>-0.4906204906205005</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3709109336913698</v>
+        <v>-0.2489826988803543</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.450062317904198</v>
+        <v>-0.3567235189494511</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4470429114013683</v>
+        <v>-0.3216642208454843</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5142262037016536</v>
+        <v>-0.3245545495728166</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.5885964246314828</v>
+        <v>-0.3349092319341125</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5653608839144795</v>
+        <v>-0.2768771670440557</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6890838916399602</v>
+        <v>-0.3837678864171181</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.655646051230967</v>
+        <v>-0.3338093453858946</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.706128613444271</v>
+        <v>-0.4057306647491217</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6952332690573826</v>
+        <v>-0.410778400463613</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.7506279457003302</v>
+        <v>-0.4519889122120588</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.6416324308326935</v>
+        <v>-0.3652388366001773</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.4873858017720138</v>
+        <v>-0.1976242136600419</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.6086431684165632</v>
+        <v>-0.3817419021581756</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.831805579132002</v>
+        <v>-0.5669276011178823</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.9209438648407868</v>
+        <v>-0.7103044509085592</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.02371</t>
+          <t>X &lt; 0.02375</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3164</v>
+        <v>3192</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2677689835292369</v>
+        <v>-0.3173228951408262</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3974694861697259</v>
+        <v>-0.3284338131910189</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5941767127751021</v>
+        <v>-0.5062772447518782</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4419236134213449</v>
+        <v>-0.301880644302166</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.6973858819576719</v>
+        <v>-0.5601739640519838</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5557481051717872</v>
+        <v>-0.4795977194644649</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5871373193477254</v>
+        <v>-0.601787238197609</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6589147286821699</v>
+        <v>-0.639391145324943</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5052329363029529</v>
+        <v>-0.4314201032731617</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.5680231053296509</v>
+        <v>-0.5223794397920969</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5906304487566061</v>
+        <v>-0.5136642751408687</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5365107338801138</v>
+        <v>-0.3972704697153375</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.4762003002899746</v>
+        <v>-0.2743992290460184</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4582405310474229</v>
+        <v>-0.2227687037244124</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.5305194415926877</v>
+        <v>-0.2605828402714963</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.5794069318659538</v>
+        <v>-0.2939580076803168</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.5686093763054743</v>
+        <v>-0.3039417057903009</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4655526022937266</v>
+        <v>-0.2177334791835079</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4518565819853109</v>
+        <v>-0.1910646792677824</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.4042024680881227</v>
+        <v>-0.1642716614388533</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2650620193343727</v>
+        <v>-0.01184135843773504</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.3852594647080281</v>
+        <v>-0.1936494590062878</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.4711200285974613</v>
+        <v>-0.2446384073857217</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6546708295426384</v>
+        <v>-0.4822871908678579</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.02616</t>
+          <t>X &lt; 0.02619</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3233</v>
+        <v>3258</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.01676848935334618</v>
+        <v>-0.07697787314876336</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3350709163900731</v>
+        <v>-0.2760106560563713</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4351549460617008</v>
+        <v>-0.383893721312532</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4856501619339681</v>
+        <v>-0.3789061481328559</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6198290272185289</v>
+        <v>-0.5152846111559484</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6617639305011593</v>
+        <v>-0.6166397197164386</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5550622582880607</v>
+        <v>-0.5995046580186241</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5696564953796113</v>
+        <v>-0.5813070378553888</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4799070213159027</v>
+        <v>-0.4361534725801022</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.5577798309550701</v>
+        <v>-0.5413629058055633</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5124634943820254</v>
+        <v>-0.4660709182964808</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4653976476750259</v>
+        <v>-0.3576087326002337</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4302377965277273</v>
+        <v>-0.2597613104717595</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4790210750954742</v>
+        <v>-0.2755055321787481</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.4712399681359472</v>
+        <v>-0.234380445487794</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4755593578487733</v>
+        <v>-0.2250543475512927</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4678116375386381</v>
+        <v>-0.2369384391291049</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4000262831723802</v>
+        <v>-0.1858299039963143</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.351118092943743</v>
+        <v>-0.1246948770958625</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3313586452442934</v>
+        <v>-0.124766512380333</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.2376333796582983</v>
+        <v>-0.01757133268164068</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2641406608794838</v>
+        <v>-0.1051975687673021</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.280432810151261</v>
+        <v>-0.08882425924196014</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.4616256565615728</v>
+        <v>-0.3248955533948035</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.0286</t>
+          <t>X &lt; 0.02863</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3271</v>
+        <v>3297</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.02821809096688099</v>
+        <v>-0.06056462379947192</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2252443187055562</v>
+        <v>-0.1395588955394373</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4014922925260223</v>
+        <v>-0.292096443986587</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3988546526954977</v>
+        <v>-0.2946521940254385</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.504940644292148</v>
+        <v>-0.3724014063642826</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4529828355713263</v>
+        <v>-0.4100515000648031</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4171996342940574</v>
+        <v>-0.4333593646386333</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.4347995273841221</v>
+        <v>-0.4192115370363183</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2847028561608553</v>
+        <v>-0.21378639123337</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4009977129104954</v>
+        <v>-0.3579296211705696</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4138881279420801</v>
+        <v>-0.3405586979425195</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4010234399738692</v>
+        <v>-0.2974462828653444</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4097246060954376</v>
+        <v>-0.275506545521317</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3995401064031938</v>
+        <v>-0.2336782244025031</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.3994497452984902</v>
+        <v>-0.2017374884146648</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.3968088940641579</v>
+        <v>-0.1675775430498803</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3906793903840224</v>
+        <v>-0.1806039269129798</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.3248722654849416</v>
+        <v>-0.131779976350785</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.3045292415371108</v>
+        <v>-0.0990258049288073</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2828168562444944</v>
+        <v>-0.07864294078275691</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2270053880580036</v>
+        <v>0.008076126268484529</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.2540822512698782</v>
+        <v>-0.07939499241492598</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.2975567968875552</v>
+        <v>-0.09064782345030409</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4469591882216051</v>
+        <v>-0.29551452672343</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.03104</t>
+          <t>X &lt; 0.03106</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3309</v>
+        <v>3334</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.06941854200339748</v>
+        <v>-0.1138849272757767</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1179235215085939</v>
+        <v>-0.04561677288097599</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3085378557076695</v>
+        <v>-0.2102921048468644</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3440797078013205</v>
+        <v>-0.2193362208258165</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3926759143412468</v>
+        <v>-0.2693969598374863</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3691994452446323</v>
+        <v>-0.3048665216373152</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2824872085632819</v>
+        <v>-0.3068035554121593</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3331001923413197</v>
+        <v>-0.3260226146392924</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2142987862379826</v>
+        <v>-0.1513130013569679</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2177080537799867</v>
+        <v>-0.1830670332151101</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2272609035398858</v>
+        <v>-0.1628238510250739</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2477881783086389</v>
+        <v>-0.1531098675441882</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2691990670104047</v>
+        <v>-0.1437130512690104</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2917495726674204</v>
+        <v>-0.1349887453133576</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.2991652659618396</v>
+        <v>-0.1109290961166209</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.3198627821781201</v>
+        <v>-0.1008496721324335</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3153149510652753</v>
+        <v>-0.1148828241988653</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.2514412358349887</v>
+        <v>-0.06807241004330677</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2590088127939936</v>
+        <v>-0.06325378876755394</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2353886126609268</v>
+        <v>-0.0407075619762125</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1562348020620519</v>
+        <v>0.06873667239500492</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1838500087186645</v>
+        <v>-0.01857974646073757</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.2538646437471002</v>
+        <v>-0.05697151424287483</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.341967743028782</v>
+        <v>-0.2013659315107148</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.03349</t>
+          <t>X &lt; 0.0335</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3330</v>
+        <v>3355</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.04705051337231936</v>
+        <v>-0.07698691768406007</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1271752244309425</v>
+        <v>-0.04038541566632148</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2957676996966825</v>
+        <v>-0.1825281991974492</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.335552204136107</v>
+        <v>-0.1953689691688751</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4158063838269754</v>
+        <v>-0.3062057982079125</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3614427720817588</v>
+        <v>-0.2811010316620894</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.309993195292499</v>
+        <v>-0.3178824049135187</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3620428418521158</v>
+        <v>-0.338970419112897</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2736308352577481</v>
+        <v>-0.2239526476606386</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2519859660256429</v>
+        <v>-0.2310221484347963</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2597674773416045</v>
+        <v>-0.2091462077189448</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2819270594939809</v>
+        <v>-0.2013177615312713</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3102732710399252</v>
+        <v>-0.1992879382513237</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3041441868737778</v>
+        <v>-0.1625257669877769</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.3456053052368517</v>
+        <v>-0.1728397780246596</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.3924051782050526</v>
+        <v>-0.1889236892370079</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3887504566894222</v>
+        <v>-0.2035449518992394</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2959847865148149</v>
+        <v>-0.128157709247688</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3021586319700944</v>
+        <v>-0.1044337827777326</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.2475292572757368</v>
+        <v>-0.05092844178884093</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2022991911096597</v>
+        <v>0.02450004382402682</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.2302321979579887</v>
+        <v>-0.06275352272122348</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.2980889542387715</v>
+        <v>-0.09939368813805061</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.3260678903202248</v>
+        <v>-0.1842993001275985</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.03593</t>
+          <t>X &lt; 0.03594</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3343</v>
+        <v>3368</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.04607587160190008</v>
+        <v>-0.06180076940853496</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1569017721086752</v>
+        <v>-0.05586906101128619</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2709556837616418</v>
+        <v>-0.1435818569693268</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3133350117749956</v>
+        <v>-0.1883313702715768</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3350822773120044</v>
+        <v>-0.2112470713590326</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.3099348043430155</v>
+        <v>-0.2446532169316242</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2616556648814736</v>
+        <v>-0.2550101697134863</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3443369773672842</v>
+        <v>-0.3363733189331839</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2561013605455074</v>
+        <v>-0.2213013331002571</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2673167110375019</v>
+        <v>-0.2612141040925948</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2740110339594679</v>
+        <v>-0.2383101056611352</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2971690993408984</v>
+        <v>-0.2316686702775854</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.329763327630701</v>
+        <v>-0.2342768748481348</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3245209698422755</v>
+        <v>-0.1987065709800149</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3683798343607307</v>
+        <v>-0.211817366968269</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4126990586256483</v>
+        <v>-0.2255177364231429</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3797335096595233</v>
+        <v>-0.2108796296296305</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2877322067333026</v>
+        <v>-0.1188367331007427</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2930413268233849</v>
+        <v>-0.09437491191246039</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2378956895166198</v>
+        <v>-0.04024557530559747</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1949463936661289</v>
+        <v>0.0327068895524576</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.2230634111607586</v>
+        <v>-0.05449759971521928</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2895871896063937</v>
+        <v>-0.09005381547871849</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3177496708144503</v>
+        <v>-0.1752547641954791</v>
       </c>
     </row>
   </sheetData>
